--- a/Data/FlightPlan/FPL_19AUG26.xlsx
+++ b/Data/FlightPlan/FPL_19AUG26.xlsx
@@ -164,6 +164,9 @@
     <t>08:50</t>
   </si>
   <si>
+    <t>10:00</t>
+  </si>
+  <si>
     <t>09:50</t>
   </si>
   <si>
@@ -353,9 +356,6 @@
     <t>05:30</t>
   </si>
   <si>
-    <t>10:00</t>
-  </si>
-  <si>
     <t>11:20</t>
   </si>
   <si>
@@ -938,6 +938,12 @@
     <t>VN-A649</t>
   </si>
   <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
     <t>22:30</t>
   </si>
   <si>
@@ -1082,9 +1088,6 @@
     <t>VN-A671</t>
   </si>
   <si>
-    <t>08:25</t>
-  </si>
-  <si>
     <t>10:05</t>
   </si>
   <si>
@@ -1151,9 +1154,6 @@
     <t>VN-A687</t>
   </si>
   <si>
-    <t>07:05</t>
-  </si>
-  <si>
     <t>11:35</t>
   </si>
   <si>
@@ -1229,7 +1229,7 @@
     <t>Total Record(s): 387</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 19, 2026 03:12</t>
+    <t xml:space="preserve">Generated on  Aug 19, 2026 03:53</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2217,7 +2217,9 @@
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
+      <c t="s" r="M21" s="7">
+        <v>51</v>
+      </c>
     </row>
     <row r="22" ht="14.25" customHeight="1">
       <c t="s" r="A22" s="6">
@@ -2243,10 +2245,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I22" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c t="s" r="J22" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="7"/>
@@ -2276,10 +2278,10 @@
         <v>45</v>
       </c>
       <c t="s" r="I23" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="J23" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
@@ -2309,7 +2311,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I24" s="7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="J24" s="7">
         <v>37</v>
@@ -2342,10 +2344,10 @@
         <v>45</v>
       </c>
       <c t="s" r="I25" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="J25" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7"/>
@@ -2378,7 +2380,7 @@
       </c>
       <c r="D27" s="7"/>
       <c t="s" r="E27" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F27" s="7">
         <v>321</v>
@@ -2387,10 +2389,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H27" s="8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="I27" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J27" s="7">
         <v>41</v>
@@ -2411,22 +2413,22 @@
       </c>
       <c r="D28" s="7"/>
       <c t="s" r="E28" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F28" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G28" s="8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="H28" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I28" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c t="s" r="J28" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -2444,7 +2446,7 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
@@ -2456,10 +2458,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J29" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -2477,7 +2479,7 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
@@ -2486,13 +2488,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H30" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c t="s" r="J30" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -2525,7 +2527,7 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
@@ -2537,10 +2539,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c t="s" r="J32" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -2573,7 +2575,7 @@
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
@@ -2585,10 +2587,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I34" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -2606,7 +2608,7 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
@@ -2618,10 +2620,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2639,7 +2641,7 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
@@ -2654,7 +2656,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2672,7 +2674,7 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
@@ -2684,10 +2686,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2720,7 +2722,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -2732,7 +2734,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J39" s="7">
         <v>50</v>
@@ -2753,7 +2755,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -2762,13 +2764,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H40" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2786,22 +2788,22 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G41" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H41" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2819,7 +2821,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -2831,10 +2833,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2852,7 +2854,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -2861,13 +2863,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -2885,22 +2887,22 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2933,7 +2935,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -2945,10 +2947,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -2966,7 +2968,7 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
@@ -2978,7 +2980,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J47" s="7">
         <v>43</v>
@@ -2999,7 +3001,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3008,13 +3010,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
@@ -3032,22 +3034,22 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3080,7 +3082,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3092,7 +3094,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J51" s="7">
         <v>20</v>
@@ -3113,7 +3115,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3125,10 +3127,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3146,7 +3148,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3155,10 +3157,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H53" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J53" s="7">
         <v>38</v>
@@ -3194,7 +3196,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3203,13 +3205,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H55" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3227,22 +3229,22 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G56" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H56" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3260,7 +3262,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3269,13 +3271,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H57" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3293,22 +3295,22 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G58" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="H58" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3326,7 +3328,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3338,10 +3340,10 @@
         <v>45</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3374,7 +3376,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3383,13 +3385,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3407,13 +3409,13 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>16</v>
@@ -3422,7 +3424,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3440,7 +3442,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3455,7 +3457,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3473,7 +3475,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3571,7 +3573,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3700,10 +3702,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3748,10 +3750,10 @@
         <v>123</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3814,10 +3816,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3916,7 +3918,7 @@
         <v>137</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3949,7 +3951,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4027,10 +4029,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4063,7 +4065,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4090,7 +4092,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I84" s="7">
         <v>141</v>
@@ -4120,16 +4122,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>143</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4156,7 +4158,7 @@
         <v>143</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I86" s="7">
         <v>144</v>
@@ -4186,7 +4188,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>45</v>
@@ -4234,7 +4236,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>17</v>
@@ -4270,7 +4272,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I90" s="7">
         <v>34</v>
@@ -4300,7 +4302,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H91" s="8">
         <v>45</v>
@@ -4357,7 +4359,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4390,7 +4392,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4456,7 +4458,7 @@
         <v>137</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4495,7 +4497,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>155</v>
@@ -4531,10 +4533,10 @@
         <v>155</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>157</v>
@@ -4561,16 +4563,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>158</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4597,7 +4599,7 @@
         <v>158</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I101" s="7">
         <v>159</v>
@@ -4627,7 +4629,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>42</v>
@@ -4663,13 +4665,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4714,10 +4716,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4810,13 +4812,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="I108" s="7">
         <v>166</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4864,7 +4866,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -4891,7 +4893,7 @@
         <v>155</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I111" s="7">
         <v>168</v>
@@ -4921,7 +4923,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>155</v>
@@ -5068,13 +5070,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>155</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>178</v>
@@ -5140,7 +5142,7 @@
         <v>180</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>181</v>
@@ -5224,7 +5226,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5254,7 +5256,7 @@
         <v>184</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>44</v>
@@ -5398,13 +5400,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I128" s="7">
         <v>189</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5428,13 +5430,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>190</v>
@@ -5461,10 +5463,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I130" s="7">
         <v>191</v>
@@ -5494,13 +5496,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>158</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J131" s="7">
         <v>43</v>
@@ -5536,7 +5538,7 @@
         <v>193</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5596,13 +5598,13 @@
         <v>158</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I134" s="7">
         <v>175</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5782,7 +5784,7 @@
         <v>200</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -5857,7 +5859,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="I143" s="7">
         <v>203</v>
@@ -5887,13 +5889,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>204</v>
@@ -6001,7 +6003,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G148" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H148" s="8">
         <v>29</v>
@@ -6157,7 +6159,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6253,7 +6255,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>221</v>
@@ -6334,7 +6336,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>211</v>
@@ -6514,7 +6516,7 @@
         <v>229</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>230</v>
@@ -6628,17 +6630,17 @@
         <v>155</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>204</v>
       </c>
       <c t="s" r="K169" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -6749,7 +6751,7 @@
         <v>208</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6791,7 +6793,7 @@
         <v>45</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I175" s="7">
         <v>238</v>
@@ -6821,13 +6823,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>240</v>
@@ -6854,10 +6856,10 @@
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I177" s="7">
         <v>31</v>
@@ -6887,7 +6889,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>16</v>
@@ -6974,10 +6976,10 @@
         <v>143</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7076,7 +7078,7 @@
         <v>194</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7115,13 +7117,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>245</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>43</v>
@@ -7151,7 +7153,7 @@
         <v>245</v>
       </c>
       <c t="s" r="H187" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I187" s="7">
         <v>44</v>
@@ -7181,13 +7183,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G188" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H188" s="8">
         <v>245</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>247</v>
@@ -7217,7 +7219,7 @@
         <v>245</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>248</v>
@@ -7304,7 +7306,7 @@
         <v>252</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7364,13 +7366,13 @@
         <v>155</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="I194" s="7">
         <v>253</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7448,7 +7450,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>256</v>
@@ -7478,7 +7480,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I198" s="7">
         <v>257</v>
@@ -7508,16 +7510,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7544,7 +7546,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I200" s="7">
         <v>179</v>
@@ -7574,7 +7576,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>16</v>
@@ -7646,7 +7648,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>181</v>
@@ -7688,7 +7690,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>16</v>
@@ -7730,7 +7732,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7790,10 +7792,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>43</v>
@@ -7820,7 +7822,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H209" s="8">
         <v>16</v>
@@ -7922,7 +7924,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I212" s="7">
         <v>201</v>
@@ -7952,7 +7954,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>16</v>
@@ -8150,13 +8152,13 @@
         <v>45</v>
       </c>
       <c t="s" r="H220" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I220" s="7">
         <v>261</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8180,7 +8182,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H221" s="8">
         <v>272</v>
@@ -8255,7 +8257,7 @@
         <v>175</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8363,7 +8365,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I227" s="7">
         <v>157</v>
@@ -8393,7 +8395,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>245</v>
@@ -8429,10 +8431,10 @@
         <v>245</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>278</v>
@@ -8459,7 +8461,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>16</v>
@@ -8468,7 +8470,7 @@
         <v>279</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8510,7 +8512,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I232" s="7">
         <v>281</v>
@@ -8540,13 +8542,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>50</v>
@@ -8579,7 +8581,7 @@
         <v>123</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>168</v>
@@ -8615,7 +8617,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8648,7 +8650,7 @@
         <v>273</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8708,7 +8710,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I238" s="7">
         <v>46</v>
@@ -8738,7 +8740,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>29</v>
@@ -8792,10 +8794,10 @@
         <v>286</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8858,10 +8860,10 @@
         <v>268</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9251,7 +9253,7 @@
         <v>272</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>299</v>
@@ -9287,7 +9289,7 @@
         <v>282</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9317,7 +9319,7 @@
         <v>300</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>236</v>
@@ -9395,7 +9397,7 @@
         <v>272</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>294</v>
@@ -9425,7 +9427,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>16</v>
@@ -9592,7 +9594,7 @@
         <v>13</v>
       </c>
       <c r="B268" s="7">
-        <v>350</v>
+        <v>628</v>
       </c>
       <c t="s" r="C268" s="7">
         <v>14</v>
@@ -9608,13 +9610,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>26</v>
+        <v>309</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>91</v>
+        <v>310</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9625,7 +9627,7 @@
         <v>13</v>
       </c>
       <c r="B269" s="7">
-        <v>351</v>
+        <v>627</v>
       </c>
       <c t="s" r="C269" s="7">
         <v>14</v>
@@ -9638,16 +9640,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>38</v>
+        <v>236</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>157</v>
+        <v>256</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9776,7 +9778,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>295</v>
@@ -9806,13 +9808,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>289</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9836,16 +9838,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9878,7 +9880,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
@@ -9911,7 +9913,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -9923,7 +9925,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>294</v>
@@ -9944,7 +9946,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -9959,7 +9961,7 @@
         <v>153</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9977,7 +9979,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -9989,7 +9991,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>264</v>
@@ -10010,7 +10012,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10019,13 +10021,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="I281" s="7">
         <v>138</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10043,22 +10045,22 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10091,7 +10093,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10103,10 +10105,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10124,7 +10126,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10136,10 +10138,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10157,7 +10159,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10172,7 +10174,7 @@
         <v>115</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10190,7 +10192,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10223,7 +10225,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10271,7 +10273,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10283,7 +10285,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>157</v>
@@ -10319,7 +10321,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10328,13 +10330,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="I292" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10352,13 +10354,13 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>16</v>
@@ -10385,7 +10387,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10394,13 +10396,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>225</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10418,19 +10420,19 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>130</v>
@@ -10466,7 +10468,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -10475,10 +10477,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>50</v>
@@ -10499,22 +10501,22 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10532,7 +10534,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10541,10 +10543,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>199</v>
@@ -10565,13 +10567,13 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>16</v>
@@ -10613,7 +10615,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -10646,7 +10648,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
@@ -10658,10 +10660,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10679,7 +10681,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -10712,7 +10714,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10745,7 +10747,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -10778,7 +10780,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10793,7 +10795,7 @@
         <v>144</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -10811,7 +10813,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -10823,10 +10825,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10859,7 +10861,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -10892,7 +10894,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -10901,7 +10903,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>211</v>
@@ -10925,13 +10927,13 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>29</v>
@@ -10940,7 +10942,7 @@
         <v>213</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10958,7 +10960,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -10967,13 +10969,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>130</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -10991,13 +10993,13 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>29</v>
@@ -11006,7 +11008,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11039,7 +11041,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11048,13 +11050,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="I316" s="7">
         <v>217</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11072,13 +11074,13 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>29</v>
@@ -11087,7 +11089,7 @@
         <v>255</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11105,7 +11107,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11138,7 +11140,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11171,7 +11173,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11186,7 +11188,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11204,7 +11206,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11237,7 +11239,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11246,7 +11248,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>295</v>
@@ -11270,19 +11272,19 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>24</v>
@@ -11318,7 +11320,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11330,7 +11332,7 @@
         <v>155</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>120</v>
@@ -11351,7 +11353,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11363,7 +11365,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>239</v>
@@ -11384,7 +11386,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11393,13 +11395,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>134</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11417,19 +11419,19 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>264</v>
@@ -11450,7 +11452,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11459,10 +11461,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>30</v>
@@ -11498,7 +11500,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11531,7 +11533,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11546,7 +11548,7 @@
         <v>199</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11564,7 +11566,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11573,13 +11575,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I333" s="7">
         <v>170</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11597,13 +11599,13 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>29</v>
@@ -11630,7 +11632,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11642,7 +11644,7 @@
         <v>303</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>47</v>
@@ -11663,7 +11665,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -11675,10 +11677,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11711,7 +11713,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11720,7 +11722,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I338" s="7">
         <v>150</v>
@@ -11744,13 +11746,13 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>29</v>
@@ -11759,7 +11761,7 @@
         <v>218</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11777,7 +11779,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11786,13 +11788,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>124</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11810,13 +11812,13 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>29</v>
@@ -11843,7 +11845,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -11852,7 +11854,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>129</v>
@@ -11876,22 +11878,22 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11909,7 +11911,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -11942,7 +11944,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -11954,7 +11956,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>166</v>
@@ -11990,7 +11992,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -11999,13 +12001,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12023,13 +12025,13 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>16</v>
@@ -12056,7 +12058,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12065,13 +12067,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12089,19 +12091,19 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>199</v>
@@ -12122,7 +12124,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12134,7 +12136,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>20</v>
@@ -12155,7 +12157,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12167,10 +12169,10 @@
         <v>286</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12188,7 +12190,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12200,7 +12202,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>295</v>
@@ -12221,7 +12223,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12269,7 +12271,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -12281,7 +12283,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>236</v>
@@ -12302,7 +12304,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12314,7 +12316,7 @@
         <v>163</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>41</v>
@@ -12335,7 +12337,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12347,7 +12349,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>44</v>
@@ -12368,7 +12370,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12380,7 +12382,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>283</v>
@@ -12401,7 +12403,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12434,7 +12436,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12443,13 +12445,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="I361" s="7">
         <v>226</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12482,7 +12484,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
@@ -12491,10 +12493,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>357</v>
+        <v>310</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>203</v>
@@ -12515,22 +12517,22 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12548,7 +12550,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
@@ -12581,7 +12583,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F366" s="7">
         <v>320</v>
@@ -12596,7 +12598,7 @@
         <v>299</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12614,7 +12616,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -12623,10 +12625,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>173</v>
@@ -12647,13 +12649,13 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>16</v>
@@ -12680,7 +12682,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -12713,7 +12715,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -12728,7 +12730,7 @@
         <v>248</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12761,7 +12763,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -12773,10 +12775,10 @@
         <v>155</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12794,7 +12796,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -12827,7 +12829,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -12836,7 +12838,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="I374" s="7">
         <v>225</v>
@@ -12860,13 +12862,13 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>29</v>
@@ -12875,7 +12877,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12893,7 +12895,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -12905,10 +12907,10 @@
         <v>274</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12926,7 +12928,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -12938,10 +12940,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12974,13 +12976,13 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>16</v>
@@ -13007,7 +13009,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13016,7 +13018,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I380" s="7">
         <v>157</v>
@@ -13040,22 +13042,22 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13073,7 +13075,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13082,7 +13084,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I382" s="7">
         <v>41</v>
@@ -13106,13 +13108,13 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>45</v>
@@ -13139,7 +13141,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13148,13 +13150,13 @@
         <v>45</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13187,7 +13189,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -13196,7 +13198,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="I386" s="7">
         <v>234</v>
@@ -13220,13 +13222,13 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>16</v>
@@ -13253,7 +13255,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -13286,7 +13288,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13319,7 +13321,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -13352,7 +13354,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13385,7 +13387,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -13394,13 +13396,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13433,7 +13435,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13466,7 +13468,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13478,10 +13480,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13499,7 +13501,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13532,7 +13534,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13565,7 +13567,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13577,10 +13579,10 @@
         <v>155</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13598,7 +13600,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -13613,7 +13615,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13646,16 +13648,16 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I401" s="7">
         <v>189</v>
@@ -13679,13 +13681,13 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>29</v>
@@ -13712,7 +13714,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -13724,7 +13726,7 @@
         <v>155</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>279</v>
@@ -13745,7 +13747,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -13760,7 +13762,7 @@
         <v>263</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -13778,7 +13780,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -13790,10 +13792,10 @@
         <v>45</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13826,7 +13828,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -13838,7 +13840,7 @@
         <v>270</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>50</v>
@@ -13859,7 +13861,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -13871,7 +13873,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>115</v>
@@ -13892,7 +13894,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -13904,7 +13906,7 @@
         <v>251</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>21</v>
@@ -13925,7 +13927,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -13958,7 +13960,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -13967,13 +13969,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -13991,22 +13993,22 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14039,13 +14041,13 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>29</v>
@@ -14054,7 +14056,7 @@
         <v>255</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14072,7 +14074,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14084,7 +14086,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>19</v>
@@ -14105,7 +14107,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
@@ -14120,7 +14122,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14138,7 +14140,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14147,10 +14149,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>35</v>
@@ -14171,19 +14173,19 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="J418" s="7">
         <v>207</v>
@@ -14204,7 +14206,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14213,10 +14215,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>121</v>
@@ -14245,14 +14247,14 @@
         <v>13</v>
       </c>
       <c r="B421" s="7">
-        <v>628</v>
+        <v>350</v>
       </c>
       <c t="s" r="C421" s="7">
         <v>14</v>
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14261,13 +14263,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>380</v>
+        <v>26</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>357</v>
+        <v>92</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14278,29 +14280,29 @@
         <v>13</v>
       </c>
       <c r="B422" s="7">
-        <v>627</v>
+        <v>351</v>
       </c>
       <c t="s" r="C422" s="7">
         <v>14</v>
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>236</v>
+        <v>38</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>256</v>
+        <v>157</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14318,7 +14320,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -14351,7 +14353,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
@@ -14360,7 +14362,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I424" s="7">
         <v>246</v>
@@ -14384,13 +14386,13 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H425" s="8">
         <v>29</v>
@@ -14399,7 +14401,7 @@
         <v>288</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -14417,7 +14419,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -14429,10 +14431,10 @@
         <v>155</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14450,7 +14452,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -14576,7 +14578,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c t="s" r="J431" s="7">
         <v>278</v>
@@ -14606,7 +14608,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I432" s="7">
         <v>194</v>
@@ -14636,16 +14638,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14684,7 +14686,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>29</v>
@@ -14807,7 +14809,7 @@
         <v>292</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14921,7 +14923,7 @@
         <v>242</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -14948,7 +14950,7 @@
         <v>184</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="I444" s="7">
         <v>386</v>
@@ -14978,16 +14980,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="H445" s="8">
         <v>184</v>
       </c>
       <c t="s" r="I445" s="7">
+        <v>329</v>
+      </c>
+      <c t="s" r="J445" s="7">
         <v>327</v>
-      </c>
-      <c t="s" r="J445" s="7">
-        <v>325</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15017,7 +15019,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>41</v>
@@ -15083,7 +15085,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J448" s="7">
         <v>213</v>
@@ -15113,10 +15115,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="J449" s="7">
         <v>166</v>
@@ -15143,13 +15145,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="H450" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="J450" s="7">
         <v>242</v>
@@ -15191,7 +15193,7 @@
         <v>330</v>
       </c>
       <c t="s" r="G452" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H452" s="8">
         <v>389</v>
@@ -15248,7 +15250,7 @@
         <v>256</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15323,13 +15325,13 @@
         <v>155</v>
       </c>
       <c t="s" r="H457" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
@@ -15353,7 +15355,7 @@
         <v>330</v>
       </c>
       <c t="s" r="G458" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H458" s="8">
         <v>393</v>
@@ -15389,7 +15391,7 @@
         <v>393</v>
       </c>
       <c t="s" r="H459" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I459" s="7">
         <v>207</v>
@@ -15443,7 +15445,7 @@
         <v>261</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15485,10 +15487,10 @@
         <v>155</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J463" s="7">
         <v>127</v>
@@ -15515,7 +15517,7 @@
         <v>330</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>398</v>
@@ -15551,7 +15553,7 @@
         <v>398</v>
       </c>
       <c t="s" r="H465" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I465" s="7">
         <v>207</v>
@@ -15596,13 +15598,13 @@
         <v>330</v>
       </c>
       <c t="s" r="G467" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="H467" s="8">
         <v>400</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J467" s="7">
         <v>401</v>
@@ -15632,7 +15634,7 @@
         <v>400</v>
       </c>
       <c t="s" r="H468" s="8">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="I468" s="7">
         <v>193</v>
@@ -15686,7 +15688,7 @@
         <v>256</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>

--- a/Data/FlightPlan/FPL_19AUG26.xlsx
+++ b/Data/FlightPlan/FPL_19AUG26.xlsx
@@ -842,159 +842,159 @@
     <t>VN-A641</t>
   </si>
   <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>03:55</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
     <t>15:00</t>
   </si>
   <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>04:30</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>03:55</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
     <t>VN-A658</t>
   </si>
   <si>
@@ -1229,7 +1229,7 @@
     <t>Total Record(s): 387</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 19, 2026 03:53</t>
+    <t xml:space="preserve">Generated on  Aug 19, 2026 04:06</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -8316,7 +8316,7 @@
         <v>13</v>
       </c>
       <c r="B226" s="7">
-        <v>121</v>
+        <v>503</v>
       </c>
       <c t="s" r="C226" s="7">
         <v>14</v>
@@ -8332,13 +8332,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>255</v>
+        <v>50</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8349,7 +8349,7 @@
         <v>13</v>
       </c>
       <c r="B227" s="7">
-        <v>272</v>
+        <v>524</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
@@ -8362,16 +8362,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>190</v>
+        <v>277</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8382,7 +8382,7 @@
         <v>13</v>
       </c>
       <c r="B228" s="7">
-        <v>7078</v>
+        <v>507</v>
       </c>
       <c t="s" r="C228" s="7">
         <v>14</v>
@@ -8395,16 +8395,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>277</v>
+        <v>199</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8415,7 +8415,7 @@
         <v>13</v>
       </c>
       <c r="B229" s="7">
-        <v>7079</v>
+        <v>643</v>
       </c>
       <c t="s" r="C229" s="7">
         <v>14</v>
@@ -8428,65 +8428,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c r="M229" s="7"/>
     </row>
     <row r="230" ht="15" customHeight="1">
-      <c t="s" r="A230" s="6">
-        <v>13</v>
-      </c>
-      <c r="B230" s="7">
-        <v>273</v>
-      </c>
-      <c t="s" r="C230" s="7">
-        <v>14</v>
-      </c>
+      <c r="A230" s="6"/>
+      <c r="B230" s="7"/>
+      <c r="C230" s="7"/>
       <c r="D230" s="7"/>
-      <c t="s" r="E230" s="7">
-        <v>276</v>
-      </c>
-      <c r="F230" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G230" s="8">
-        <v>113</v>
-      </c>
-      <c t="s" r="H230" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I230" s="7">
-        <v>279</v>
-      </c>
-      <c t="s" r="J230" s="7">
-        <v>76</v>
-      </c>
+      <c r="E230" s="7"/>
+      <c r="F230" s="7"/>
+      <c r="G230" s="8"/>
+      <c r="H230" s="8"/>
+      <c r="I230" s="7"/>
+      <c r="J230" s="7"/>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c r="M230" s="7"/>
     </row>
     <row r="231" ht="14.25" customHeight="1">
-      <c r="A231" s="6"/>
-      <c r="B231" s="7"/>
-      <c r="C231" s="7"/>
+      <c t="s" r="A231" s="6">
+        <v>13</v>
+      </c>
+      <c r="B231" s="7">
+        <v>501</v>
+      </c>
+      <c t="s" r="C231" s="7">
+        <v>14</v>
+      </c>
       <c r="D231" s="7"/>
-      <c r="E231" s="7"/>
-      <c r="F231" s="7"/>
-      <c r="G231" s="8"/>
-      <c r="H231" s="8"/>
-      <c r="I231" s="7"/>
-      <c r="J231" s="7"/>
+      <c t="s" r="E231" s="7">
+        <v>278</v>
+      </c>
+      <c r="F231" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G231" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H231" s="8">
+        <v>80</v>
+      </c>
+      <c t="s" r="I231" s="7">
+        <v>279</v>
+      </c>
+      <c t="s" r="J231" s="7">
+        <v>261</v>
+      </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c r="M231" s="7"/>
@@ -8496,29 +8496,29 @@
         <v>13</v>
       </c>
       <c r="B232" s="7">
-        <v>501</v>
+        <v>514</v>
       </c>
       <c t="s" r="C232" s="7">
         <v>14</v>
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>281</v>
+        <v>92</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>261</v>
+        <v>50</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8529,29 +8529,29 @@
         <v>13</v>
       </c>
       <c r="B233" s="7">
-        <v>514</v>
+        <v>563</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>50</v>
+        <v>168</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8562,29 +8562,29 @@
         <v>13</v>
       </c>
       <c r="B234" s="7">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c t="s" r="C234" s="7">
         <v>14</v>
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>168</v>
+        <v>54</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8595,29 +8595,29 @@
         <v>13</v>
       </c>
       <c r="B235" s="7">
-        <v>564</v>
+        <v>787</v>
       </c>
       <c t="s" r="C235" s="7">
         <v>14</v>
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>133</v>
+        <v>273</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8628,29 +8628,29 @@
         <v>13</v>
       </c>
       <c r="B236" s="7">
-        <v>787</v>
+        <v>774</v>
       </c>
       <c t="s" r="C236" s="7">
         <v>14</v>
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
+        <v>278</v>
+      </c>
+      <c r="F236" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G236" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="H236" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I236" s="7">
         <v>280</v>
       </c>
-      <c r="F236" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G236" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H236" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="I236" s="7">
-        <v>273</v>
-      </c>
       <c t="s" r="J236" s="7">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8661,29 +8661,29 @@
         <v>13</v>
       </c>
       <c r="B237" s="7">
-        <v>774</v>
+        <v>517</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>282</v>
+        <v>46</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>164</v>
+        <v>281</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8694,78 +8694,78 @@
         <v>13</v>
       </c>
       <c r="B238" s="7">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c t="s" r="C238" s="7">
         <v>14</v>
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>46</v>
+        <v>282</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>283</v>
+        <v>259</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c r="M238" s="7"/>
     </row>
     <row r="239" ht="14.25" customHeight="1">
-      <c t="s" r="A239" s="6">
-        <v>13</v>
-      </c>
-      <c r="B239" s="7">
-        <v>520</v>
-      </c>
-      <c t="s" r="C239" s="7">
-        <v>14</v>
-      </c>
+      <c r="A239" s="6"/>
+      <c r="B239" s="7"/>
+      <c r="C239" s="7"/>
       <c r="D239" s="7"/>
-      <c t="s" r="E239" s="7">
-        <v>280</v>
-      </c>
-      <c r="F239" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G239" s="8">
-        <v>80</v>
-      </c>
-      <c t="s" r="H239" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I239" s="7">
-        <v>284</v>
-      </c>
-      <c t="s" r="J239" s="7">
-        <v>259</v>
-      </c>
+      <c r="E239" s="7"/>
+      <c r="F239" s="7"/>
+      <c r="G239" s="8"/>
+      <c r="H239" s="8"/>
+      <c r="I239" s="7"/>
+      <c r="J239" s="7"/>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c r="M239" s="7"/>
     </row>
     <row r="240" ht="15" customHeight="1">
-      <c r="A240" s="6"/>
-      <c r="B240" s="7"/>
-      <c r="C240" s="7"/>
+      <c t="s" r="A240" s="6">
+        <v>13</v>
+      </c>
+      <c r="B240" s="7">
+        <v>392</v>
+      </c>
+      <c t="s" r="C240" s="7">
+        <v>14</v>
+      </c>
       <c r="D240" s="7"/>
-      <c r="E240" s="7"/>
-      <c r="F240" s="7"/>
-      <c r="G240" s="8"/>
-      <c r="H240" s="8"/>
-      <c r="I240" s="7"/>
-      <c r="J240" s="7"/>
+      <c t="s" r="E240" s="7">
+        <v>283</v>
+      </c>
+      <c r="F240" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G240" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H240" s="8">
+        <v>284</v>
+      </c>
+      <c t="s" r="I240" s="7">
+        <v>68</v>
+      </c>
+      <c t="s" r="J240" s="7">
+        <v>78</v>
+      </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c r="M240" s="7"/>
@@ -8775,29 +8775,29 @@
         <v>13</v>
       </c>
       <c r="B241" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c t="s" r="C241" s="7">
         <v>14</v>
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>16</v>
+        <v>284</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>286</v>
+        <v>16</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8808,29 +8808,29 @@
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>393</v>
+        <v>1813</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>286</v>
+        <v>16</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>16</v>
+        <v>268</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>196</v>
+        <v>104</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8841,29 +8841,29 @@
         <v>13</v>
       </c>
       <c r="B243" s="7">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c t="s" r="C243" s="7">
         <v>14</v>
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>16</v>
+        <v>268</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>268</v>
+        <v>16</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>74</v>
+        <v>219</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8874,29 +8874,29 @@
         <v>13</v>
       </c>
       <c r="B244" s="7">
-        <v>1814</v>
+        <v>1831</v>
       </c>
       <c t="s" r="C244" s="7">
         <v>14</v>
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
+        <v>283</v>
+      </c>
+      <c r="F244" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G244" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H244" s="8">
         <v>285</v>
       </c>
-      <c r="F244" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G244" s="8">
-        <v>268</v>
-      </c>
-      <c t="s" r="H244" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I244" s="7">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>219</v>
+        <v>286</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8907,29 +8907,29 @@
         <v>13</v>
       </c>
       <c r="B245" s="7">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
+        <v>283</v>
+      </c>
+      <c r="F245" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G245" s="8">
         <v>285</v>
       </c>
-      <c r="F245" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G245" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="H245" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I245" s="7">
+        <v>23</v>
+      </c>
+      <c t="s" r="J245" s="7">
         <v>287</v>
-      </c>
-      <c t="s" r="I245" s="7">
-        <v>137</v>
-      </c>
-      <c t="s" r="J245" s="7">
-        <v>288</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8940,78 +8940,78 @@
         <v>13</v>
       </c>
       <c r="B246" s="7">
-        <v>1832</v>
+        <v>162</v>
       </c>
       <c t="s" r="C246" s="7">
         <v>14</v>
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>287</v>
+        <v>16</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>23</v>
+        <v>249</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c r="M246" s="7"/>
     </row>
     <row r="247" ht="14.25" customHeight="1">
-      <c t="s" r="A247" s="6">
-        <v>13</v>
-      </c>
-      <c r="B247" s="7">
-        <v>162</v>
-      </c>
-      <c t="s" r="C247" s="7">
-        <v>14</v>
-      </c>
+      <c r="A247" s="6"/>
+      <c r="B247" s="7"/>
+      <c r="C247" s="7"/>
       <c r="D247" s="7"/>
-      <c t="s" r="E247" s="7">
-        <v>285</v>
-      </c>
-      <c r="F247" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G247" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H247" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I247" s="7">
-        <v>249</v>
-      </c>
-      <c t="s" r="J247" s="7">
-        <v>290</v>
-      </c>
+      <c r="E247" s="7"/>
+      <c r="F247" s="7"/>
+      <c r="G247" s="8"/>
+      <c r="H247" s="8"/>
+      <c r="I247" s="7"/>
+      <c r="J247" s="7"/>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c r="M247" s="7"/>
     </row>
     <row r="248" ht="14.25" customHeight="1">
-      <c r="A248" s="6"/>
-      <c r="B248" s="7"/>
-      <c r="C248" s="7"/>
+      <c t="s" r="A248" s="6">
+        <v>13</v>
+      </c>
+      <c r="B248" s="7">
+        <v>449</v>
+      </c>
+      <c t="s" r="C248" s="7">
+        <v>14</v>
+      </c>
       <c r="D248" s="7"/>
-      <c r="E248" s="7"/>
-      <c r="F248" s="7"/>
-      <c r="G248" s="8"/>
-      <c r="H248" s="8"/>
-      <c r="I248" s="7"/>
-      <c r="J248" s="7"/>
+      <c t="s" r="E248" s="7">
+        <v>289</v>
+      </c>
+      <c r="F248" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G248" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H248" s="8">
+        <v>42</v>
+      </c>
+      <c t="s" r="I248" s="7">
+        <v>26</v>
+      </c>
+      <c t="s" r="J248" s="7">
+        <v>290</v>
+      </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c r="M248" s="7"/>
@@ -9021,26 +9021,26 @@
         <v>13</v>
       </c>
       <c r="B249" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c t="s" r="C249" s="7">
         <v>14</v>
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
+        <v>289</v>
+      </c>
+      <c r="F249" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G249" s="8">
+        <v>42</v>
+      </c>
+      <c t="s" r="H249" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I249" s="7">
         <v>291</v>
-      </c>
-      <c r="F249" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G249" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H249" s="8">
-        <v>42</v>
-      </c>
-      <c t="s" r="I249" s="7">
-        <v>26</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>292</v>
@@ -9054,29 +9054,29 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>450</v>
+        <v>775</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>293</v>
+        <v>159</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>294</v>
+        <v>178</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9087,29 +9087,29 @@
         <v>13</v>
       </c>
       <c r="B251" s="7">
-        <v>775</v>
+        <v>5530</v>
       </c>
       <c t="s" r="C251" s="7">
         <v>14</v>
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>155</v>
+        <v>245</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9120,29 +9120,29 @@
         <v>13</v>
       </c>
       <c r="B252" s="7">
-        <v>5530</v>
+        <v>5531</v>
       </c>
       <c t="s" r="C252" s="7">
         <v>14</v>
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
+        <v>245</v>
+      </c>
+      <c t="s" r="H252" s="8">
         <v>155</v>
       </c>
-      <c t="s" r="H252" s="8">
-        <v>245</v>
-      </c>
       <c t="s" r="I252" s="7">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>194</v>
+        <v>293</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9153,26 +9153,26 @@
         <v>13</v>
       </c>
       <c r="B253" s="7">
-        <v>5531</v>
+        <v>836</v>
       </c>
       <c t="s" r="C253" s="7">
         <v>14</v>
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>245</v>
+        <v>155</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>155</v>
+        <v>45</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>186</v>
+        <v>294</v>
       </c>
       <c t="s" r="J253" s="7">
         <v>295</v>
@@ -9182,49 +9182,49 @@
       <c r="M253" s="7"/>
     </row>
     <row r="254" ht="14.25" customHeight="1">
-      <c t="s" r="A254" s="6">
-        <v>13</v>
-      </c>
-      <c r="B254" s="7">
-        <v>836</v>
-      </c>
-      <c t="s" r="C254" s="7">
-        <v>14</v>
-      </c>
+      <c r="A254" s="6"/>
+      <c r="B254" s="7"/>
+      <c r="C254" s="7"/>
       <c r="D254" s="7"/>
-      <c t="s" r="E254" s="7">
-        <v>291</v>
-      </c>
-      <c r="F254" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G254" s="8">
-        <v>155</v>
-      </c>
-      <c t="s" r="H254" s="8">
-        <v>45</v>
-      </c>
-      <c t="s" r="I254" s="7">
-        <v>296</v>
-      </c>
-      <c t="s" r="J254" s="7">
-        <v>297</v>
-      </c>
+      <c r="E254" s="7"/>
+      <c r="F254" s="7"/>
+      <c r="G254" s="8"/>
+      <c r="H254" s="8"/>
+      <c r="I254" s="7"/>
+      <c r="J254" s="7"/>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c r="M254" s="7"/>
     </row>
     <row r="255" ht="15" customHeight="1">
-      <c r="A255" s="6"/>
-      <c r="B255" s="7"/>
-      <c r="C255" s="7"/>
+      <c t="s" r="A255" s="6">
+        <v>13</v>
+      </c>
+      <c r="B255" s="7">
+        <v>887</v>
+      </c>
+      <c t="s" r="C255" s="7">
+        <v>14</v>
+      </c>
       <c r="D255" s="7"/>
-      <c r="E255" s="7"/>
-      <c r="F255" s="7"/>
-      <c r="G255" s="8"/>
-      <c r="H255" s="8"/>
-      <c r="I255" s="7"/>
-      <c r="J255" s="7"/>
+      <c t="s" r="E255" s="7">
+        <v>296</v>
+      </c>
+      <c r="F255" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G255" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H255" s="8">
+        <v>272</v>
+      </c>
+      <c t="s" r="I255" s="7">
+        <v>82</v>
+      </c>
+      <c t="s" r="J255" s="7">
+        <v>297</v>
+      </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c r="M255" s="7"/>
@@ -9234,29 +9234,29 @@
         <v>13</v>
       </c>
       <c r="B256" s="7">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c t="s" r="C256" s="7">
         <v>14</v>
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>272</v>
+        <v>16</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>299</v>
+        <v>95</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9264,81 +9264,81 @@
     </row>
     <row r="257" ht="14.25" customHeight="1">
       <c t="s" r="A257" s="6">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B257" s="7">
-        <v>882</v>
+        <v>91</v>
       </c>
       <c t="s" r="C257" s="7">
         <v>14</v>
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
+        <v>296</v>
+      </c>
+      <c r="F257" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G257" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H257" s="8">
         <v>298</v>
       </c>
-      <c r="F257" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G257" s="8">
-        <v>272</v>
-      </c>
-      <c t="s" r="H257" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I257" s="7">
-        <v>282</v>
+        <v>96</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>95</v>
+        <v>236</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c r="M257" s="7"/>
     </row>
     <row r="258" ht="14.25" customHeight="1">
-      <c t="s" r="A258" s="6">
-        <v>36</v>
-      </c>
-      <c r="B258" s="7">
-        <v>91</v>
-      </c>
-      <c t="s" r="C258" s="7">
-        <v>14</v>
-      </c>
+      <c r="A258" s="6"/>
+      <c r="B258" s="7"/>
+      <c r="C258" s="7"/>
       <c r="D258" s="7"/>
-      <c t="s" r="E258" s="7">
-        <v>298</v>
-      </c>
-      <c r="F258" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G258" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H258" s="8">
-        <v>300</v>
-      </c>
-      <c t="s" r="I258" s="7">
-        <v>96</v>
-      </c>
-      <c t="s" r="J258" s="7">
-        <v>236</v>
-      </c>
+      <c r="E258" s="7"/>
+      <c r="F258" s="7"/>
+      <c r="G258" s="8"/>
+      <c r="H258" s="8"/>
+      <c r="I258" s="7"/>
+      <c r="J258" s="7"/>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c r="M258" s="7"/>
     </row>
     <row r="259" ht="14.25" customHeight="1">
-      <c r="A259" s="6"/>
-      <c r="B259" s="7"/>
-      <c r="C259" s="7"/>
+      <c t="s" r="A259" s="6">
+        <v>13</v>
+      </c>
+      <c r="B259" s="7">
+        <v>813</v>
+      </c>
+      <c t="s" r="C259" s="7">
+        <v>14</v>
+      </c>
       <c r="D259" s="7"/>
-      <c r="E259" s="7"/>
-      <c r="F259" s="7"/>
-      <c r="G259" s="8"/>
-      <c r="H259" s="8"/>
-      <c r="I259" s="7"/>
-      <c r="J259" s="7"/>
+      <c t="s" r="E259" s="7">
+        <v>299</v>
+      </c>
+      <c r="F259" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G259" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H259" s="8">
+        <v>272</v>
+      </c>
+      <c t="s" r="I259" s="7">
+        <v>121</v>
+      </c>
+      <c t="s" r="J259" s="7">
+        <v>256</v>
+      </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c r="M259" s="7"/>
@@ -9348,29 +9348,29 @@
         <v>13</v>
       </c>
       <c r="B260" s="7">
-        <v>813</v>
+        <v>970</v>
       </c>
       <c t="s" r="C260" s="7">
         <v>14</v>
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>16</v>
+        <v>272</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>272</v>
+        <v>80</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>121</v>
+        <v>292</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9381,29 +9381,29 @@
         <v>13</v>
       </c>
       <c r="B261" s="7">
-        <v>970</v>
+        <v>633</v>
       </c>
       <c t="s" r="C261" s="7">
         <v>14</v>
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>272</v>
+        <v>80</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>294</v>
+        <v>43</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9414,29 +9414,29 @@
         <v>13</v>
       </c>
       <c r="B262" s="7">
-        <v>633</v>
+        <v>394</v>
       </c>
       <c t="s" r="C262" s="7">
         <v>14</v>
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
+        <v>299</v>
+      </c>
+      <c r="F262" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G262" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H262" s="8">
+        <v>284</v>
+      </c>
+      <c t="s" r="I262" s="7">
+        <v>204</v>
+      </c>
+      <c t="s" r="J262" s="7">
         <v>301</v>
-      </c>
-      <c r="F262" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G262" s="8">
-        <v>80</v>
-      </c>
-      <c t="s" r="H262" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I262" s="7">
-        <v>43</v>
-      </c>
-      <c t="s" r="J262" s="7">
-        <v>302</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9447,29 +9447,29 @@
         <v>13</v>
       </c>
       <c r="B263" s="7">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="C263" s="7">
         <v>14</v>
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>16</v>
+        <v>284</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>286</v>
+        <v>16</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>204</v>
+        <v>263</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>279</v>
+        <v>174</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9480,29 +9480,29 @@
         <v>13</v>
       </c>
       <c r="B264" s="7">
-        <v>395</v>
+        <v>3908</v>
       </c>
       <c t="s" r="C264" s="7">
         <v>14</v>
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>286</v>
+        <v>16</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>16</v>
+        <v>302</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>263</v>
+        <v>303</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>174</v>
+        <v>304</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9510,81 +9510,81 @@
     </row>
     <row r="265" ht="15" customHeight="1">
       <c t="s" r="A265" s="6">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B265" s="7">
-        <v>3908</v>
+        <v>3909</v>
       </c>
       <c t="s" r="C265" s="7">
         <v>14</v>
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>16</v>
+        <v>302</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>303</v>
+        <v>16</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c r="M265" s="7"/>
     </row>
     <row r="266" ht="14.25" customHeight="1">
-      <c t="s" r="A266" s="6">
-        <v>36</v>
-      </c>
-      <c r="B266" s="7">
-        <v>3909</v>
-      </c>
-      <c t="s" r="C266" s="7">
-        <v>14</v>
-      </c>
+      <c r="A266" s="6"/>
+      <c r="B266" s="7"/>
+      <c r="C266" s="7"/>
       <c r="D266" s="7"/>
-      <c t="s" r="E266" s="7">
-        <v>301</v>
-      </c>
-      <c r="F266" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G266" s="8">
-        <v>303</v>
-      </c>
-      <c t="s" r="H266" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I266" s="7">
-        <v>306</v>
-      </c>
-      <c t="s" r="J266" s="7">
-        <v>307</v>
-      </c>
+      <c r="E266" s="7"/>
+      <c r="F266" s="7"/>
+      <c r="G266" s="8"/>
+      <c r="H266" s="8"/>
+      <c r="I266" s="7"/>
+      <c r="J266" s="7"/>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c r="M266" s="7"/>
     </row>
     <row r="267" ht="14.25" customHeight="1">
-      <c r="A267" s="6"/>
-      <c r="B267" s="7"/>
-      <c r="C267" s="7"/>
+      <c t="s" r="A267" s="6">
+        <v>13</v>
+      </c>
+      <c r="B267" s="7">
+        <v>628</v>
+      </c>
+      <c t="s" r="C267" s="7">
+        <v>14</v>
+      </c>
       <c r="D267" s="7"/>
-      <c r="E267" s="7"/>
-      <c r="F267" s="7"/>
-      <c r="G267" s="8"/>
-      <c r="H267" s="8"/>
-      <c r="I267" s="7"/>
-      <c r="J267" s="7"/>
+      <c t="s" r="E267" s="7">
+        <v>307</v>
+      </c>
+      <c r="F267" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G267" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H267" s="8">
+        <v>80</v>
+      </c>
+      <c t="s" r="I267" s="7">
+        <v>308</v>
+      </c>
+      <c t="s" r="J267" s="7">
+        <v>309</v>
+      </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c r="M267" s="7"/>
@@ -9594,29 +9594,29 @@
         <v>13</v>
       </c>
       <c r="B268" s="7">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c t="s" r="C268" s="7">
         <v>14</v>
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>309</v>
+        <v>236</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>310</v>
+        <v>256</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9627,29 +9627,29 @@
         <v>13</v>
       </c>
       <c r="B269" s="7">
-        <v>627</v>
+        <v>803</v>
       </c>
       <c t="s" r="C269" s="7">
         <v>14</v>
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>236</v>
+        <v>292</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9660,29 +9660,29 @@
         <v>13</v>
       </c>
       <c r="B270" s="7">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c t="s" r="C270" s="7">
         <v>14</v>
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>16</v>
+        <v>163</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>163</v>
+        <v>16</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>294</v>
+        <v>127</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9693,29 +9693,29 @@
         <v>13</v>
       </c>
       <c r="B271" s="7">
-        <v>804</v>
+        <v>310</v>
       </c>
       <c t="s" r="C271" s="7">
         <v>14</v>
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>163</v>
+        <v>16</v>
       </c>
       <c t="s" r="H271" s="8">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>127</v>
+        <v>170</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>193</v>
+        <v>46</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9726,29 +9726,29 @@
         <v>13</v>
       </c>
       <c r="B272" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c t="s" r="C272" s="7">
         <v>14</v>
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>46</v>
+        <v>293</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9759,29 +9759,29 @@
         <v>13</v>
       </c>
       <c r="B273" s="7">
-        <v>309</v>
+        <v>652</v>
       </c>
       <c t="s" r="C273" s="7">
         <v>14</v>
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>63</v>
+        <v>287</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9792,78 +9792,78 @@
         <v>13</v>
       </c>
       <c r="B274" s="7">
-        <v>652</v>
+        <v>631</v>
       </c>
       <c t="s" r="C274" s="7">
         <v>14</v>
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c r="M274" s="7"/>
     </row>
     <row r="275" ht="15" customHeight="1">
-      <c t="s" r="A275" s="6">
-        <v>13</v>
-      </c>
-      <c r="B275" s="7">
-        <v>631</v>
-      </c>
-      <c t="s" r="C275" s="7">
-        <v>14</v>
-      </c>
+      <c r="A275" s="6"/>
+      <c r="B275" s="7"/>
+      <c r="C275" s="7"/>
       <c r="D275" s="7"/>
-      <c t="s" r="E275" s="7">
-        <v>308</v>
-      </c>
-      <c r="F275" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G275" s="8">
-        <v>80</v>
-      </c>
-      <c t="s" r="H275" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I275" s="7">
-        <v>312</v>
-      </c>
-      <c t="s" r="J275" s="7">
-        <v>313</v>
-      </c>
+      <c r="E275" s="7"/>
+      <c r="F275" s="7"/>
+      <c r="G275" s="8"/>
+      <c r="H275" s="8"/>
+      <c r="I275" s="7"/>
+      <c r="J275" s="7"/>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c r="M275" s="7"/>
     </row>
     <row r="276" ht="14.25" customHeight="1">
-      <c r="A276" s="6"/>
-      <c r="B276" s="7"/>
-      <c r="C276" s="7"/>
+      <c t="s" r="A276" s="6">
+        <v>13</v>
+      </c>
+      <c r="B276" s="7">
+        <v>1771</v>
+      </c>
+      <c t="s" r="C276" s="7">
+        <v>14</v>
+      </c>
       <c r="D276" s="7"/>
-      <c r="E276" s="7"/>
-      <c r="F276" s="7"/>
-      <c r="G276" s="8"/>
-      <c r="H276" s="8"/>
-      <c r="I276" s="7"/>
-      <c r="J276" s="7"/>
+      <c t="s" r="E276" s="7">
+        <v>313</v>
+      </c>
+      <c r="F276" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G276" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H276" s="8">
+        <v>155</v>
+      </c>
+      <c t="s" r="I276" s="7">
+        <v>261</v>
+      </c>
+      <c t="s" r="J276" s="7">
+        <v>50</v>
+      </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c r="M276" s="7"/>
@@ -9873,29 +9873,29 @@
         <v>13</v>
       </c>
       <c r="B277" s="7">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c t="s" r="C277" s="7">
         <v>14</v>
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F277" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>29</v>
+        <v>155</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>261</v>
+        <v>81</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>50</v>
+        <v>292</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9906,29 +9906,29 @@
         <v>13</v>
       </c>
       <c r="B278" s="7">
-        <v>1772</v>
+        <v>143</v>
       </c>
       <c t="s" r="C278" s="7">
         <v>14</v>
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>155</v>
+        <v>29</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>81</v>
+        <v>153</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -9939,29 +9939,29 @@
         <v>13</v>
       </c>
       <c r="B279" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="C279" s="7">
         <v>14</v>
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>153</v>
+        <v>315</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>315</v>
+        <v>264</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -9972,29 +9972,29 @@
         <v>13</v>
       </c>
       <c r="B280" s="7">
-        <v>146</v>
+        <v>7712</v>
       </c>
       <c t="s" r="C280" s="7">
         <v>14</v>
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>29</v>
+        <v>316</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>316</v>
+        <v>138</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>264</v>
+        <v>312</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10002,81 +10002,81 @@
     </row>
     <row r="281" ht="14.25" customHeight="1">
       <c t="s" r="A281" s="6">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B281" s="7">
-        <v>7712</v>
+        <v>7713</v>
       </c>
       <c t="s" r="C281" s="7">
         <v>14</v>
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>29</v>
+        <v>316</v>
       </c>
       <c t="s" r="H281" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I281" s="7">
+        <v>77</v>
+      </c>
+      <c t="s" r="J281" s="7">
         <v>317</v>
-      </c>
-      <c t="s" r="I281" s="7">
-        <v>138</v>
-      </c>
-      <c t="s" r="J281" s="7">
-        <v>313</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c r="M281" s="7"/>
     </row>
     <row r="282" ht="14.25" customHeight="1">
-      <c t="s" r="A282" s="6">
-        <v>36</v>
-      </c>
-      <c r="B282" s="7">
-        <v>7713</v>
-      </c>
-      <c t="s" r="C282" s="7">
-        <v>14</v>
-      </c>
+      <c r="A282" s="6"/>
+      <c r="B282" s="7"/>
+      <c r="C282" s="7"/>
       <c r="D282" s="7"/>
-      <c t="s" r="E282" s="7">
-        <v>314</v>
-      </c>
-      <c r="F282" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G282" s="8">
-        <v>317</v>
-      </c>
-      <c t="s" r="H282" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I282" s="7">
-        <v>77</v>
-      </c>
-      <c t="s" r="J282" s="7">
-        <v>318</v>
-      </c>
+      <c r="E282" s="7"/>
+      <c r="F282" s="7"/>
+      <c r="G282" s="8"/>
+      <c r="H282" s="8"/>
+      <c r="I282" s="7"/>
+      <c r="J282" s="7"/>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c r="M282" s="7"/>
     </row>
     <row r="283" ht="14.25" customHeight="1">
-      <c r="A283" s="6"/>
-      <c r="B283" s="7"/>
-      <c r="C283" s="7"/>
+      <c t="s" r="A283" s="6">
+        <v>13</v>
+      </c>
+      <c r="B283" s="7">
+        <v>123</v>
+      </c>
+      <c t="s" r="C283" s="7">
+        <v>14</v>
+      </c>
       <c r="D283" s="7"/>
-      <c r="E283" s="7"/>
-      <c r="F283" s="7"/>
-      <c r="G283" s="8"/>
-      <c r="H283" s="8"/>
-      <c r="I283" s="7"/>
-      <c r="J283" s="7"/>
+      <c t="s" r="E283" s="7">
+        <v>318</v>
+      </c>
+      <c r="F283" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G283" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H283" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I283" s="7">
+        <v>114</v>
+      </c>
+      <c t="s" r="J283" s="7">
+        <v>319</v>
+      </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c r="M283" s="7"/>
@@ -10086,29 +10086,29 @@
         <v>13</v>
       </c>
       <c r="B284" s="7">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c t="s" r="C284" s="7">
         <v>14</v>
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>320</v>
+        <v>53</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10119,29 +10119,29 @@
         <v>13</v>
       </c>
       <c r="B285" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="C285" s="7">
         <v>14</v>
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>61</v>
+        <v>115</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10152,29 +10152,29 @@
         <v>13</v>
       </c>
       <c r="B286" s="7">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c t="s" r="C286" s="7">
         <v>14</v>
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>115</v>
+        <v>161</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>74</v>
+        <v>170</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10185,126 +10185,126 @@
         <v>13</v>
       </c>
       <c r="B287" s="7">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c t="s" r="C287" s="7">
         <v>14</v>
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>161</v>
+        <v>320</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c r="M287" s="7"/>
     </row>
     <row r="288" ht="14.25" customHeight="1">
-      <c t="s" r="A288" s="6">
-        <v>13</v>
-      </c>
-      <c r="B288" s="7">
-        <v>151</v>
-      </c>
-      <c t="s" r="C288" s="7">
-        <v>14</v>
-      </c>
+      <c r="A288" s="6"/>
+      <c r="B288" s="7"/>
+      <c r="C288" s="7"/>
       <c r="D288" s="7"/>
-      <c t="s" r="E288" s="7">
-        <v>319</v>
-      </c>
-      <c r="F288" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G288" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H288" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I288" s="7">
-        <v>278</v>
-      </c>
-      <c t="s" r="J288" s="7">
-        <v>34</v>
-      </c>
+      <c r="E288" s="7"/>
+      <c r="F288" s="7"/>
+      <c r="G288" s="8"/>
+      <c r="H288" s="8"/>
+      <c r="I288" s="7"/>
+      <c r="J288" s="7"/>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c r="M288" s="7"/>
     </row>
     <row r="289" ht="14.25" customHeight="1">
-      <c r="A289" s="6"/>
-      <c r="B289" s="7"/>
-      <c r="C289" s="7"/>
+      <c t="s" r="A289" s="6">
+        <v>13</v>
+      </c>
+      <c r="B289" s="7">
+        <v>156</v>
+      </c>
+      <c t="s" r="C289" s="7">
+        <v>14</v>
+      </c>
       <c r="D289" s="7"/>
-      <c r="E289" s="7"/>
-      <c r="F289" s="7"/>
-      <c r="G289" s="8"/>
-      <c r="H289" s="8"/>
-      <c r="I289" s="7"/>
-      <c r="J289" s="7"/>
+      <c t="s" r="E289" s="7">
+        <v>321</v>
+      </c>
+      <c r="F289" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G289" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H289" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I289" s="7">
+        <v>322</v>
+      </c>
+      <c t="s" r="J289" s="7">
+        <v>157</v>
+      </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c r="M289" s="7"/>
     </row>
     <row r="290" ht="15" customHeight="1">
-      <c t="s" r="A290" s="6">
-        <v>13</v>
-      </c>
-      <c r="B290" s="7">
-        <v>156</v>
-      </c>
-      <c t="s" r="C290" s="7">
-        <v>14</v>
-      </c>
+      <c r="A290" s="6"/>
+      <c r="B290" s="7"/>
+      <c r="C290" s="7"/>
       <c r="D290" s="7"/>
-      <c t="s" r="E290" s="7">
-        <v>321</v>
-      </c>
-      <c r="F290" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G290" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H290" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I290" s="7">
-        <v>322</v>
-      </c>
-      <c t="s" r="J290" s="7">
-        <v>157</v>
-      </c>
+      <c r="E290" s="7"/>
+      <c r="F290" s="7"/>
+      <c r="G290" s="8"/>
+      <c r="H290" s="8"/>
+      <c r="I290" s="7"/>
+      <c r="J290" s="7"/>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c r="M290" s="7"/>
     </row>
     <row r="291" ht="14.25" customHeight="1">
-      <c r="A291" s="6"/>
-      <c r="B291" s="7"/>
-      <c r="C291" s="7"/>
+      <c t="s" r="A291" s="6">
+        <v>13</v>
+      </c>
+      <c r="B291" s="7">
+        <v>809</v>
+      </c>
+      <c t="s" r="C291" s="7">
+        <v>14</v>
+      </c>
       <c r="D291" s="7"/>
-      <c r="E291" s="7"/>
-      <c r="F291" s="7"/>
-      <c r="G291" s="8"/>
-      <c r="H291" s="8"/>
-      <c r="I291" s="7"/>
-      <c r="J291" s="7"/>
+      <c t="s" r="E291" s="7">
+        <v>323</v>
+      </c>
+      <c r="F291" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G291" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H291" s="8">
+        <v>324</v>
+      </c>
+      <c t="s" r="I291" s="7">
+        <v>50</v>
+      </c>
+      <c t="s" r="J291" s="7">
+        <v>105</v>
+      </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c r="M291" s="7"/>
@@ -10314,7 +10314,7 @@
         <v>13</v>
       </c>
       <c r="B292" s="7">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c t="s" r="C292" s="7">
         <v>14</v>
@@ -10327,16 +10327,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>16</v>
+        <v>324</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>324</v>
+        <v>16</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>50</v>
+        <v>125</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10347,7 +10347,7 @@
         <v>13</v>
       </c>
       <c r="B293" s="7">
-        <v>808</v>
+        <v>376</v>
       </c>
       <c t="s" r="C293" s="7">
         <v>14</v>
@@ -10360,16 +10360,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>324</v>
+        <v>16</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>16</v>
+        <v>325</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>127</v>
+        <v>75</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10380,7 +10380,7 @@
         <v>13</v>
       </c>
       <c r="B294" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="C294" s="7">
         <v>14</v>
@@ -10393,65 +10393,65 @@
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>16</v>
+        <v>325</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>325</v>
+        <v>16</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>225</v>
+        <v>87</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c r="M294" s="7"/>
     </row>
     <row r="295" ht="15" customHeight="1">
-      <c t="s" r="A295" s="6">
-        <v>13</v>
-      </c>
-      <c r="B295" s="7">
-        <v>377</v>
-      </c>
-      <c t="s" r="C295" s="7">
-        <v>14</v>
-      </c>
+      <c r="A295" s="6"/>
+      <c r="B295" s="7"/>
+      <c r="C295" s="7"/>
       <c r="D295" s="7"/>
-      <c t="s" r="E295" s="7">
-        <v>323</v>
-      </c>
-      <c r="F295" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G295" s="8">
-        <v>325</v>
-      </c>
-      <c t="s" r="H295" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I295" s="7">
-        <v>87</v>
-      </c>
-      <c t="s" r="J295" s="7">
-        <v>130</v>
-      </c>
+      <c r="E295" s="7"/>
+      <c r="F295" s="7"/>
+      <c r="G295" s="8"/>
+      <c r="H295" s="8"/>
+      <c r="I295" s="7"/>
+      <c r="J295" s="7"/>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c r="M295" s="7"/>
     </row>
     <row r="296" ht="14.25" customHeight="1">
-      <c r="A296" s="6"/>
-      <c r="B296" s="7"/>
-      <c r="C296" s="7"/>
+      <c t="s" r="A296" s="6">
+        <v>13</v>
+      </c>
+      <c r="B296" s="7">
+        <v>121</v>
+      </c>
+      <c t="s" r="C296" s="7">
+        <v>14</v>
+      </c>
       <c r="D296" s="7"/>
-      <c r="E296" s="7"/>
-      <c r="F296" s="7"/>
-      <c r="G296" s="8"/>
-      <c r="H296" s="8"/>
-      <c r="I296" s="7"/>
-      <c r="J296" s="7"/>
+      <c t="s" r="E296" s="7">
+        <v>326</v>
+      </c>
+      <c r="F296" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G296" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H296" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I296" s="7">
+        <v>150</v>
+      </c>
+      <c t="s" r="J296" s="7">
+        <v>255</v>
+      </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c r="M296" s="7"/>
@@ -10461,7 +10461,7 @@
         <v>13</v>
       </c>
       <c r="B297" s="7">
-        <v>503</v>
+        <v>272</v>
       </c>
       <c t="s" r="C297" s="7">
         <v>14</v>
@@ -10474,16 +10474,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>92</v>
+        <v>157</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10494,7 +10494,7 @@
         <v>13</v>
       </c>
       <c r="B298" s="7">
-        <v>524</v>
+        <v>7078</v>
       </c>
       <c t="s" r="C298" s="7">
         <v>14</v>
@@ -10507,13 +10507,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>29</v>
+        <v>245</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>327</v>
@@ -10527,7 +10527,7 @@
         <v>13</v>
       </c>
       <c r="B299" s="7">
-        <v>507</v>
+        <v>7079</v>
       </c>
       <c t="s" r="C299" s="7">
         <v>14</v>
@@ -10540,16 +10540,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>29</v>
+        <v>245</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>199</v>
+        <v>320</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10560,7 +10560,7 @@
         <v>13</v>
       </c>
       <c r="B300" s="7">
-        <v>643</v>
+        <v>273</v>
       </c>
       <c t="s" r="C300" s="7">
         <v>14</v>
@@ -10573,16 +10573,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>116</v>
+        <v>301</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>265</v>
+        <v>76</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10624,7 +10624,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c t="s" r="I302" s="7">
         <v>121</v>
@@ -10654,7 +10654,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>29</v>
@@ -11056,7 +11056,7 @@
         <v>217</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11251,7 +11251,7 @@
         <v>80</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>187</v>
@@ -11611,7 +11611,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>247</v>
@@ -11641,10 +11641,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>47</v>
@@ -11671,7 +11671,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>29</v>
@@ -11926,7 +11926,7 @@
         <v>138</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12073,7 +12073,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12166,7 +12166,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c t="s" r="I352" s="7">
         <v>110</v>
@@ -12196,7 +12196,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>29</v>
@@ -12205,7 +12205,7 @@
         <v>346</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12385,7 +12385,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12415,10 +12415,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12496,7 +12496,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>203</v>
@@ -12595,10 +12595,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12628,7 +12628,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>173</v>
@@ -12661,7 +12661,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>174</v>
@@ -13123,7 +13123,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13450,7 +13450,7 @@
         <v>261</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13729,7 +13729,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14056,7 +14056,7 @@
         <v>255</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14398,7 +14398,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>89</v>
@@ -14581,7 +14581,7 @@
         <v>344</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>278</v>
+        <v>320</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14614,7 +14614,7 @@
         <v>194</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -14806,7 +14806,7 @@
         <v>163</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c t="s" r="J439" s="7">
         <v>359</v>
@@ -14989,7 +14989,7 @@
         <v>329</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>327</v>
+        <v>277</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15115,7 +15115,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c t="s" r="I449" s="7">
         <v>346</v>
@@ -15145,7 +15145,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c t="s" r="H450" s="8">
         <v>16</v>
@@ -15640,7 +15640,7 @@
         <v>193</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>

--- a/Data/FlightPlan/FPL_19AUG26.xlsx
+++ b/Data/FlightPlan/FPL_19AUG26.xlsx
@@ -731,7 +731,7 @@
     <t>08:15</t>
   </si>
   <si>
-    <t>10:49</t>
+    <t>11:12</t>
   </si>
   <si>
     <t>15:15</t>
@@ -767,9 +767,6 @@
     <t>DPS</t>
   </si>
   <si>
-    <t>13:49</t>
-  </si>
-  <si>
     <t>DEL</t>
   </si>
   <si>
@@ -881,6 +878,9 @@
     <t>10:15</t>
   </si>
   <si>
+    <t>10:46</t>
+  </si>
+  <si>
     <t>PXU</t>
   </si>
   <si>
@@ -998,6 +998,9 @@
     <t>11:15</t>
   </si>
   <si>
+    <t>11:31</t>
+  </si>
+  <si>
     <t>21:50</t>
   </si>
   <si>
@@ -1085,9 +1088,6 @@
     <t>HKT</t>
   </si>
   <si>
-    <t>11:11</t>
-  </si>
-  <si>
     <t>VCL</t>
   </si>
   <si>
@@ -1097,6 +1097,9 @@
     <t>07:58</t>
   </si>
   <si>
+    <t>11:22</t>
+  </si>
+  <si>
     <t>15:00</t>
   </si>
   <si>
@@ -1151,123 +1154,126 @@
     <t>VN-A667</t>
   </si>
   <si>
-    <t>12:28</t>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>07:52</t>
+  </si>
+  <si>
+    <t>10:13</t>
+  </si>
+  <si>
+    <t>TBB</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:48</t>
+  </si>
+  <si>
+    <t>08:44</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>09:31</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>08:31</t>
+  </si>
+  <si>
+    <t>10:39</t>
+  </si>
+  <si>
+    <t>01:25</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>06:53</t>
+  </si>
+  <si>
+    <t>10:22</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>09:02</t>
+  </si>
+  <si>
+    <t>11:08</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
   </si>
   <si>
     <t>SAI</t>
   </si>
   <si>
-    <t>18:05</t>
-  </si>
-  <si>
     <t>02:10</t>
   </si>
   <si>
     <t>03:05</t>
   </si>
   <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>07:52</t>
-  </si>
-  <si>
-    <t>10:13</t>
-  </si>
-  <si>
-    <t>TBB</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:48</t>
-  </si>
-  <si>
-    <t>08:44</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>08:52</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>09:31</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>08:31</t>
-  </si>
-  <si>
-    <t>01:25</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>06:53</t>
-  </si>
-  <si>
-    <t>09:54</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>09:02</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
     <t>VN-A684</t>
   </si>
   <si>
@@ -1295,6 +1301,9 @@
     <t>08:57</t>
   </si>
   <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
     <t>VN-A693</t>
   </si>
   <si>
@@ -1319,6 +1328,9 @@
     <t>08:43</t>
   </si>
   <si>
+    <t>10:38</t>
+  </si>
+  <si>
     <t>P</t>
   </si>
   <si>
@@ -1334,9 +1346,6 @@
     <t>SYD</t>
   </si>
   <si>
-    <t>16:27</t>
-  </si>
-  <si>
     <t>VN-A814</t>
   </si>
   <si>
@@ -1379,7 +1388,7 @@
     <t>Total Record(s): 386</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 19, 2026 09:06</t>
+    <t xml:space="preserve">Generated on  Aug 19, 2026 09:39</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -6693,7 +6702,7 @@
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>252</v>
+        <v>114</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -6750,13 +6759,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c t="s" r="I166" s="7">
         <v>59</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6780,7 +6789,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>16</v>
@@ -6789,7 +6798,7 @@
         <v>183</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6822,13 +6831,13 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
+        <v>255</v>
+      </c>
+      <c r="F169" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G169" s="8">
         <v>256</v>
-      </c>
-      <c r="F169" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G169" s="8">
-        <v>257</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>29</v>
@@ -6855,7 +6864,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6892,7 +6901,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6904,10 +6913,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6940,7 +6949,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6952,7 +6961,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>186</v>
@@ -6975,7 +6984,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7023,7 +7032,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7035,15 +7044,15 @@
         <v>119</v>
       </c>
       <c t="s" r="I176" s="7">
+        <v>261</v>
+      </c>
+      <c t="s" r="J176" s="7">
         <v>262</v>
-      </c>
-      <c t="s" r="J176" s="7">
-        <v>263</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7058,7 +7067,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7067,13 +7076,13 @@
         <v>119</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="I177" s="7">
         <v>195</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7091,13 +7100,13 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>119</v>
@@ -7124,7 +7133,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7172,7 +7181,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7184,7 +7193,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>128</v>
@@ -7192,7 +7201,7 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7207,7 +7216,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7226,7 +7235,9 @@
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
-      <c r="M182" s="7"/>
+      <c t="s" r="M182" s="7">
+        <v>132</v>
+      </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c t="s" r="A183" s="6">
@@ -7240,7 +7251,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7255,7 +7266,7 @@
         <v>195</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7273,7 +7284,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7282,7 +7293,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="I184" s="7">
         <v>210</v>
@@ -7306,29 +7317,29 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="H185" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>212</v>
       </c>
       <c t="s" r="K185" s="7">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7343,7 +7354,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7352,7 +7363,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="I186" s="7">
         <v>149</v>
@@ -7380,19 +7391,19 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>139</v>
@@ -7402,7 +7413,7 @@
       </c>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -7432,7 +7443,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7441,10 +7452,10 @@
         <v>88</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>45</v>
@@ -7465,13 +7476,13 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
+        <v>275</v>
+      </c>
+      <c r="F190" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G190" s="8">
         <v>276</v>
-      </c>
-      <c r="F190" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G190" s="8">
-        <v>277</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>88</v>
@@ -7480,7 +7491,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7498,7 +7509,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7507,13 +7518,13 @@
         <v>88</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="I191" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7531,22 +7542,22 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
+        <v>275</v>
+      </c>
+      <c r="F192" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G192" s="8">
         <v>276</v>
-      </c>
-      <c r="F192" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G192" s="8">
-        <v>277</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>88</v>
       </c>
       <c t="s" r="I192" s="7">
+        <v>279</v>
+      </c>
+      <c t="s" r="J192" s="7">
         <v>280</v>
-      </c>
-      <c t="s" r="J192" s="7">
-        <v>281</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7579,7 +7590,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7599,7 +7610,7 @@
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -7614,7 +7625,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7623,10 +7634,10 @@
         <v>170</v>
       </c>
       <c t="s" r="H195" s="8">
+        <v>283</v>
+      </c>
+      <c t="s" r="I195" s="7">
         <v>284</v>
-      </c>
-      <c t="s" r="I195" s="7">
-        <v>285</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>82</v>
@@ -7647,13 +7658,13 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>170</v>
@@ -7680,7 +7691,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7692,7 +7703,7 @@
         <v>71</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>54</v>
@@ -7728,7 +7739,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7740,10 +7751,10 @@
         <v>189</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7763,7 +7774,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7778,11 +7789,13 @@
         <v>65</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
-      <c r="M200" s="7"/>
+      <c t="s" r="M200" s="7">
+        <v>289</v>
+      </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
       <c t="s" r="A201" s="6">
@@ -7796,7 +7809,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7829,7 +7842,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7889,7 +7902,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>294</v>
@@ -8322,7 +8335,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8421,7 +8434,7 @@
         <v>138</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -9282,7 +9295,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>323</v>
@@ -9372,7 +9385,9 @@
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
-      <c r="M252" s="7"/>
+      <c t="s" r="M252" s="7">
+        <v>329</v>
+      </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
       <c t="s" r="A253" s="6">
@@ -9428,7 +9443,7 @@
         <v>170</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="I254" s="7">
         <v>198</v>
@@ -9458,7 +9473,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>170</v>
@@ -9497,10 +9512,10 @@
         <v>47</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9533,7 +9548,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9548,7 +9563,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9566,7 +9581,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9599,7 +9614,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9608,13 +9623,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I260" s="7">
         <v>103</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9647,7 +9662,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9662,7 +9677,7 @@
         <v>128</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9682,7 +9697,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9715,7 +9730,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9730,7 +9745,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9748,7 +9763,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9760,7 +9775,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>292</v>
@@ -9781,7 +9796,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9793,7 +9808,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>192</v>
@@ -9814,7 +9829,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9826,7 +9841,7 @@
         <v>88</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>312</v>
@@ -9847,7 +9862,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9862,7 +9877,7 @@
         <v>228</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9895,7 +9910,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -9915,7 +9930,7 @@
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -9930,7 +9945,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9942,10 +9957,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9963,7 +9978,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9996,7 +10011,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10029,7 +10044,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10062,7 +10077,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10095,7 +10110,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10110,7 +10125,7 @@
         <v>322</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10128,7 +10143,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10140,10 +10155,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10176,7 +10191,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10196,7 +10211,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10211,7 +10226,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10230,7 +10245,9 @@
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
-      <c r="M280" s="7"/>
+      <c t="s" r="M280" s="7">
+        <v>329</v>
+      </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
       <c t="s" r="A281" s="6">
@@ -10244,7 +10261,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10259,7 +10276,7 @@
         <v>168</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10277,7 +10294,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10289,10 +10306,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10310,7 +10327,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10319,13 +10336,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="I283" s="7">
         <v>150</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10343,13 +10360,13 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>29</v>
@@ -10358,7 +10375,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10391,7 +10408,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10411,7 +10428,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10426,7 +10443,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10446,7 +10463,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>195</v>
+        <v>240</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10461,7 +10478,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10494,7 +10511,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10527,7 +10544,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10539,7 +10556,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>35</v>
@@ -10575,7 +10592,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10587,7 +10604,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>173</v>
@@ -10595,7 +10612,7 @@
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -10625,7 +10642,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10634,7 +10651,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="I294" s="7">
         <v>52</v>
@@ -10645,7 +10662,7 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>358</v>
+        <v>166</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -10660,13 +10677,13 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>16</v>
@@ -10693,7 +10710,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10726,7 +10743,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10789,7 +10806,7 @@
         <v>164</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10828,7 +10845,9 @@
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
-      <c r="M300" s="7"/>
+      <c t="s" r="M300" s="7">
+        <v>362</v>
+      </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
       <c t="s" r="A301" s="6">
@@ -10851,13 +10870,13 @@
         <v>119</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="I301" s="7">
         <v>134</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10881,16 +10900,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>119</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10956,7 +10975,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
@@ -10991,7 +11010,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11024,7 +11043,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11033,13 +11052,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="I307" s="7">
         <v>113</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11057,13 +11076,13 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>29</v>
@@ -11072,7 +11091,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -11090,7 +11109,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11102,10 +11121,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -11138,7 +11157,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11147,7 +11166,7 @@
         <v>29</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>238</v>
@@ -11158,7 +11177,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11173,19 +11192,19 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>54</v>
@@ -11208,7 +11227,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11241,7 +11260,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11274,7 +11293,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11307,7 +11326,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11322,7 +11341,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11340,7 +11359,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11373,7 +11392,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11421,7 +11440,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11433,7 +11452,7 @@
         <v>170</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="J320" s="7">
         <v>121</v>
@@ -11456,7 +11475,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -11468,15 +11487,15 @@
         <v>29</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -11491,7 +11510,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11524,7 +11543,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11557,7 +11576,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11590,7 +11609,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11605,7 +11624,7 @@
         <v>155</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11623,7 +11642,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -11632,10 +11651,10 @@
         <v>29</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>30</v>
@@ -11671,7 +11690,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -11683,7 +11702,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>56</v>
@@ -11691,7 +11710,7 @@
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -11706,7 +11725,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11739,7 +11758,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11751,10 +11770,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11772,7 +11791,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11805,7 +11824,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -11846,14 +11865,14 @@
         <v>13</v>
       </c>
       <c r="B334" s="7">
-        <v>905</v>
+        <v>137</v>
       </c>
       <c t="s" r="C334" s="7">
         <v>14</v>
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -11862,72 +11881,64 @@
         <v>29</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>302</v>
+        <v>16</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>161</v>
-      </c>
-      <c t="s" r="K334" s="7">
-        <v>239</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="K334" s="7"/>
       <c r="L334" s="7"/>
-      <c t="s" r="M334" s="7">
-        <v>380</v>
-      </c>
+      <c r="M334" s="7"/>
     </row>
     <row r="335" ht="15" customHeight="1">
       <c t="s" r="A335" s="6">
         <v>13</v>
       </c>
       <c r="B335" s="7">
-        <v>906</v>
+        <v>144</v>
       </c>
       <c t="s" r="C335" s="7">
         <v>14</v>
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>302</v>
+        <v>16</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>217</v>
+        <v>154</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>378</v>
-      </c>
-      <c t="s" r="K335" s="7">
-        <v>31</v>
-      </c>
+        <v>381</v>
+      </c>
+      <c r="K335" s="7"/>
       <c r="L335" s="7"/>
-      <c t="s" r="M335" s="7">
-        <v>241</v>
-      </c>
+      <c r="M335" s="7"/>
     </row>
     <row r="336" ht="14.25" customHeight="1">
       <c t="s" r="A336" s="6">
         <v>13</v>
       </c>
       <c r="B336" s="7">
-        <v>913</v>
+        <v>519</v>
       </c>
       <c t="s" r="C336" s="7">
         <v>14</v>
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -11936,13 +11947,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>381</v>
+        <v>88</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>187</v>
+        <v>59</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>382</v>
+        <v>36</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11953,128 +11964,132 @@
         <v>13</v>
       </c>
       <c r="B337" s="7">
-        <v>914</v>
+        <v>522</v>
       </c>
       <c t="s" r="C337" s="7">
         <v>14</v>
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>381</v>
+        <v>88</v>
       </c>
       <c t="s" r="H337" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>279</v>
+        <v>228</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c r="M337" s="7"/>
     </row>
     <row r="338" ht="14.25" customHeight="1">
-      <c t="s" r="A338" s="6">
-        <v>13</v>
-      </c>
-      <c r="B338" s="7">
-        <v>7526</v>
-      </c>
-      <c t="s" r="C338" s="7">
-        <v>14</v>
-      </c>
+      <c r="A338" s="6"/>
+      <c r="B338" s="7"/>
+      <c r="C338" s="7"/>
       <c r="D338" s="7"/>
-      <c t="s" r="E338" s="7">
-        <v>379</v>
-      </c>
-      <c r="F338" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G338" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H338" s="8">
-        <v>220</v>
-      </c>
-      <c t="s" r="I338" s="7">
-        <v>342</v>
-      </c>
-      <c t="s" r="J338" s="7">
-        <v>49</v>
-      </c>
+      <c r="E338" s="7"/>
+      <c r="F338" s="7"/>
+      <c r="G338" s="8"/>
+      <c r="H338" s="8"/>
+      <c r="I338" s="7"/>
+      <c r="J338" s="7"/>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c r="M338" s="7"/>
     </row>
     <row r="339" ht="14.25" customHeight="1">
       <c t="s" r="A339" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B339" s="7">
-        <v>7527</v>
+        <v>491</v>
       </c>
       <c t="s" r="C339" s="7">
         <v>14</v>
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="F339" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>220</v>
+        <v>29</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>29</v>
+        <v>264</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>383</v>
+        <v>164</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>384</v>
+        <v>208</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
-      <c r="M339" s="7"/>
+      <c t="s" r="M339" s="7">
+        <v>383</v>
+      </c>
     </row>
     <row r="340" ht="15" customHeight="1">
-      <c r="A340" s="6"/>
-      <c r="B340" s="7"/>
-      <c r="C340" s="7"/>
+      <c t="s" r="A340" s="6">
+        <v>13</v>
+      </c>
+      <c r="B340" s="7">
+        <v>492</v>
+      </c>
+      <c t="s" r="C340" s="7">
+        <v>14</v>
+      </c>
       <c r="D340" s="7"/>
-      <c r="E340" s="7"/>
-      <c r="F340" s="7"/>
-      <c r="G340" s="8"/>
-      <c r="H340" s="8"/>
-      <c r="I340" s="7"/>
-      <c r="J340" s="7"/>
+      <c t="s" r="E340" s="7">
+        <v>382</v>
+      </c>
+      <c r="F340" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G340" s="8">
+        <v>264</v>
+      </c>
+      <c t="s" r="H340" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I340" s="7">
+        <v>239</v>
+      </c>
+      <c t="s" r="J340" s="7">
+        <v>122</v>
+      </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
-      <c r="M340" s="7"/>
+      <c t="s" r="M340" s="7">
+        <v>384</v>
+      </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
       <c t="s" r="A341" s="6">
         <v>13</v>
       </c>
       <c r="B341" s="7">
-        <v>491</v>
+        <v>1491</v>
       </c>
       <c t="s" r="C341" s="7">
         <v>14</v>
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12083,68 +12098,64 @@
         <v>29</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>208</v>
+        <v>269</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
-      <c t="s" r="M341" s="7">
-        <v>386</v>
-      </c>
+      <c r="M341" s="7"/>
     </row>
     <row r="342" ht="14.25" customHeight="1">
       <c t="s" r="A342" s="6">
         <v>13</v>
       </c>
       <c r="B342" s="7">
-        <v>492</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C342" s="7">
         <v>14</v>
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>239</v>
+        <v>162</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
-      <c t="s" r="M342" s="7">
-        <v>387</v>
-      </c>
+      <c r="M342" s="7"/>
     </row>
     <row r="343" ht="14.25" customHeight="1">
       <c t="s" r="A343" s="6">
         <v>13</v>
       </c>
       <c r="B343" s="7">
-        <v>1491</v>
+        <v>419</v>
       </c>
       <c t="s" r="C343" s="7">
         <v>14</v>
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12153,13 +12164,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>265</v>
+        <v>385</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12170,29 +12181,29 @@
         <v>13</v>
       </c>
       <c r="B344" s="7">
-        <v>1492</v>
+        <v>420</v>
       </c>
       <c t="s" r="C344" s="7">
         <v>14</v>
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>265</v>
+        <v>385</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>19</v>
+        <v>219</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12203,14 +12214,14 @@
         <v>13</v>
       </c>
       <c r="B345" s="7">
-        <v>419</v>
+        <v>1785</v>
       </c>
       <c t="s" r="C345" s="7">
         <v>14</v>
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12219,13 +12230,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>388</v>
+        <v>170</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>234</v>
+        <v>96</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12236,63 +12247,45 @@
         <v>13</v>
       </c>
       <c r="B346" s="7">
-        <v>420</v>
+        <v>1786</v>
       </c>
       <c t="s" r="C346" s="7">
         <v>14</v>
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>388</v>
+        <v>170</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>149</v>
+        <v>386</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c r="M346" s="7"/>
     </row>
     <row r="347" ht="14.25" customHeight="1">
-      <c t="s" r="A347" s="6">
-        <v>13</v>
-      </c>
-      <c r="B347" s="7">
-        <v>1785</v>
-      </c>
-      <c t="s" r="C347" s="7">
-        <v>14</v>
-      </c>
+      <c r="A347" s="6"/>
+      <c r="B347" s="7"/>
+      <c r="C347" s="7"/>
       <c r="D347" s="7"/>
-      <c t="s" r="E347" s="7">
-        <v>385</v>
-      </c>
-      <c r="F347" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G347" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="H347" s="8">
-        <v>170</v>
-      </c>
-      <c t="s" r="I347" s="7">
-        <v>150</v>
-      </c>
-      <c t="s" r="J347" s="7">
-        <v>96</v>
-      </c>
+      <c r="E347" s="7"/>
+      <c r="F347" s="7"/>
+      <c r="G347" s="8"/>
+      <c r="H347" s="8"/>
+      <c r="I347" s="7"/>
+      <c r="J347" s="7"/>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c r="M347" s="7"/>
@@ -12302,62 +12295,84 @@
         <v>13</v>
       </c>
       <c r="B348" s="7">
-        <v>1786</v>
+        <v>1372</v>
       </c>
       <c t="s" r="C348" s="7">
         <v>14</v>
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>170</v>
+        <v>16</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>29</v>
+        <v>359</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>183</v>
+        <v>73</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
-      <c r="M348" s="7"/>
+      <c t="s" r="M348" s="7">
+        <v>389</v>
+      </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
-      <c r="A349" s="6"/>
-      <c r="B349" s="7"/>
-      <c r="C349" s="7"/>
+      <c t="s" r="A349" s="6">
+        <v>13</v>
+      </c>
+      <c r="B349" s="7">
+        <v>1373</v>
+      </c>
+      <c t="s" r="C349" s="7">
+        <v>14</v>
+      </c>
       <c r="D349" s="7"/>
-      <c r="E349" s="7"/>
-      <c r="F349" s="7"/>
-      <c r="G349" s="8"/>
-      <c r="H349" s="8"/>
-      <c r="I349" s="7"/>
-      <c r="J349" s="7"/>
+      <c t="s" r="E349" s="7">
+        <v>387</v>
+      </c>
+      <c r="F349" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G349" s="8">
+        <v>359</v>
+      </c>
+      <c t="s" r="H349" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I349" s="7">
+        <v>128</v>
+      </c>
+      <c t="s" r="J349" s="7">
+        <v>243</v>
+      </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
-      <c r="M349" s="7"/>
+      <c t="s" r="M349" s="7">
+        <v>390</v>
+      </c>
     </row>
     <row r="350" ht="15" customHeight="1">
       <c t="s" r="A350" s="6">
         <v>13</v>
       </c>
       <c r="B350" s="7">
-        <v>1372</v>
+        <v>372</v>
       </c>
       <c t="s" r="C350" s="7">
         <v>14</v>
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12369,15 +12384,15 @@
         <v>359</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>391</v>
+        <v>79</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>73</v>
+        <v>311</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>392</v>
+        <v>195</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -12385,14 +12400,14 @@
         <v>13</v>
       </c>
       <c r="B351" s="7">
-        <v>1373</v>
+        <v>373</v>
       </c>
       <c t="s" r="C351" s="7">
         <v>14</v>
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12404,30 +12419,28 @@
         <v>16</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
-      <c t="s" r="M351" s="7">
-        <v>393</v>
-      </c>
+      <c r="M351" s="7"/>
     </row>
     <row r="352" ht="14.25" customHeight="1">
       <c t="s" r="A352" s="6">
         <v>13</v>
       </c>
       <c r="B352" s="7">
-        <v>372</v>
+        <v>142</v>
       </c>
       <c t="s" r="C352" s="7">
         <v>14</v>
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12436,13 +12449,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>359</v>
+        <v>29</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>79</v>
+        <v>210</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>311</v>
+        <v>20</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12453,29 +12466,29 @@
         <v>13</v>
       </c>
       <c r="B353" s="7">
-        <v>373</v>
+        <v>423</v>
       </c>
       <c t="s" r="C353" s="7">
         <v>14</v>
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>359</v>
+        <v>29</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>16</v>
+        <v>290</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>90</v>
+        <v>271</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>217</v>
+        <v>272</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12486,29 +12499,29 @@
         <v>13</v>
       </c>
       <c r="B354" s="7">
-        <v>142</v>
+        <v>424</v>
       </c>
       <c t="s" r="C354" s="7">
         <v>14</v>
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>16</v>
+        <v>290</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>210</v>
+        <v>381</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12519,14 +12532,14 @@
         <v>13</v>
       </c>
       <c r="B355" s="7">
-        <v>423</v>
+        <v>161</v>
       </c>
       <c t="s" r="C355" s="7">
         <v>14</v>
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12535,47 +12548,29 @@
         <v>29</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>290</v>
+        <v>16</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>272</v>
+        <v>296</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c r="M355" s="7"/>
     </row>
     <row r="356" ht="14.25" customHeight="1">
-      <c t="s" r="A356" s="6">
-        <v>13</v>
-      </c>
-      <c r="B356" s="7">
-        <v>424</v>
-      </c>
-      <c t="s" r="C356" s="7">
-        <v>14</v>
-      </c>
+      <c r="A356" s="6"/>
+      <c r="B356" s="7"/>
+      <c r="C356" s="7"/>
       <c r="D356" s="7"/>
-      <c t="s" r="E356" s="7">
-        <v>390</v>
-      </c>
-      <c r="F356" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G356" s="8">
-        <v>290</v>
-      </c>
-      <c t="s" r="H356" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I356" s="7">
-        <v>382</v>
-      </c>
-      <c t="s" r="J356" s="7">
-        <v>95</v>
-      </c>
+      <c r="E356" s="7"/>
+      <c r="F356" s="7"/>
+      <c r="G356" s="8"/>
+      <c r="H356" s="8"/>
+      <c r="I356" s="7"/>
+      <c r="J356" s="7"/>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c r="M356" s="7"/>
@@ -12585,45 +12580,65 @@
         <v>13</v>
       </c>
       <c r="B357" s="7">
-        <v>161</v>
+        <v>963</v>
       </c>
       <c t="s" r="C357" s="7">
         <v>14</v>
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F357" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H357" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H357" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I357" s="7">
-        <v>296</v>
+        <v>392</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>235</v>
+        <v>259</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
-      <c r="M357" s="7"/>
+      <c t="s" r="M357" s="7">
+        <v>393</v>
+      </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
-      <c r="A358" s="6"/>
-      <c r="B358" s="7"/>
-      <c r="C358" s="7"/>
+      <c t="s" r="A358" s="6">
+        <v>13</v>
+      </c>
+      <c r="B358" s="7">
+        <v>901</v>
+      </c>
+      <c t="s" r="C358" s="7">
+        <v>14</v>
+      </c>
       <c r="D358" s="7"/>
-      <c r="E358" s="7"/>
-      <c r="F358" s="7"/>
-      <c r="G358" s="8"/>
-      <c r="H358" s="8"/>
-      <c r="I358" s="7"/>
-      <c r="J358" s="7"/>
+      <c t="s" r="E358" s="7">
+        <v>391</v>
+      </c>
+      <c r="F358" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G358" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H358" s="8">
+        <v>180</v>
+      </c>
+      <c t="s" r="I358" s="7">
+        <v>90</v>
+      </c>
+      <c t="s" r="J358" s="7">
+        <v>42</v>
+      </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c r="M358" s="7"/>
@@ -12633,49 +12648,47 @@
         <v>13</v>
       </c>
       <c r="B359" s="7">
-        <v>963</v>
+        <v>902</v>
       </c>
       <c t="s" r="C359" s="7">
         <v>14</v>
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>395</v>
+        <v>67</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>260</v>
+        <v>46</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
-      <c t="s" r="M359" s="7">
-        <v>396</v>
-      </c>
+      <c r="M359" s="7"/>
     </row>
     <row r="360" ht="15" customHeight="1">
       <c t="s" r="A360" s="6">
         <v>13</v>
       </c>
       <c r="B360" s="7">
-        <v>901</v>
+        <v>1511</v>
       </c>
       <c t="s" r="C360" s="7">
         <v>14</v>
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12684,13 +12697,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>180</v>
+        <v>88</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>90</v>
+        <v>277</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>42</v>
+        <v>190</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12701,29 +12714,29 @@
         <v>13</v>
       </c>
       <c r="B361" s="7">
-        <v>902</v>
+        <v>1518</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>180</v>
+        <v>88</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>67</v>
+        <v>321</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>46</v>
+        <v>273</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12734,14 +12747,14 @@
         <v>13</v>
       </c>
       <c r="B362" s="7">
-        <v>1511</v>
+        <v>783</v>
       </c>
       <c t="s" r="C362" s="7">
         <v>14</v>
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12750,13 +12763,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>278</v>
+        <v>374</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>190</v>
+        <v>386</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12767,29 +12780,29 @@
         <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>1518</v>
+        <v>784</v>
       </c>
       <c t="s" r="C363" s="7">
         <v>14</v>
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>321</v>
+        <v>24</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>274</v>
+        <v>201</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12797,17 +12810,17 @@
     </row>
     <row r="364" ht="14.25" customHeight="1">
       <c t="s" r="A364" s="6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B364" s="7">
-        <v>783</v>
+        <v>958</v>
       </c>
       <c t="s" r="C364" s="7">
         <v>14</v>
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12816,129 +12829,129 @@
         <v>29</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>170</v>
+        <v>394</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>373</v>
+        <v>249</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>389</v>
+        <v>107</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c r="M364" s="7"/>
     </row>
     <row r="365" ht="15" customHeight="1">
-      <c t="s" r="A365" s="6">
-        <v>13</v>
-      </c>
-      <c r="B365" s="7">
-        <v>784</v>
-      </c>
-      <c t="s" r="C365" s="7">
-        <v>14</v>
-      </c>
+      <c r="A365" s="6"/>
+      <c r="B365" s="7"/>
+      <c r="C365" s="7"/>
       <c r="D365" s="7"/>
-      <c t="s" r="E365" s="7">
-        <v>394</v>
-      </c>
-      <c r="F365" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G365" s="8">
-        <v>170</v>
-      </c>
-      <c t="s" r="H365" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I365" s="7">
-        <v>24</v>
-      </c>
-      <c t="s" r="J365" s="7">
-        <v>201</v>
-      </c>
+      <c r="E365" s="7"/>
+      <c r="F365" s="7"/>
+      <c r="G365" s="8"/>
+      <c r="H365" s="8"/>
+      <c r="I365" s="7"/>
+      <c r="J365" s="7"/>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c r="M365" s="7"/>
     </row>
     <row r="366" ht="14.25" customHeight="1">
-      <c r="A366" s="6"/>
-      <c r="B366" s="7"/>
-      <c r="C366" s="7"/>
+      <c t="s" r="A366" s="6">
+        <v>13</v>
+      </c>
+      <c r="B366" s="7">
+        <v>382</v>
+      </c>
+      <c t="s" r="C366" s="7">
+        <v>14</v>
+      </c>
       <c r="D366" s="7"/>
-      <c r="E366" s="7"/>
-      <c r="F366" s="7"/>
-      <c r="G366" s="8"/>
-      <c r="H366" s="8"/>
-      <c r="I366" s="7"/>
-      <c r="J366" s="7"/>
+      <c t="s" r="E366" s="7">
+        <v>395</v>
+      </c>
+      <c r="F366" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G366" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H366" s="8">
+        <v>270</v>
+      </c>
+      <c t="s" r="I366" s="7">
+        <v>246</v>
+      </c>
+      <c t="s" r="J366" s="7">
+        <v>225</v>
+      </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
-      <c r="M366" s="7"/>
+      <c t="s" r="M366" s="7">
+        <v>396</v>
+      </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
       <c t="s" r="A367" s="6">
         <v>13</v>
       </c>
       <c r="B367" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c t="s" r="C367" s="7">
         <v>14</v>
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>16</v>
+        <v>270</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>271</v>
+        <v>16</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>246</v>
+        <v>397</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>225</v>
+        <v>90</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
-      <c t="s" r="M367" s="7">
-        <v>398</v>
-      </c>
+      <c r="M367" s="7"/>
     </row>
     <row r="368" ht="14.25" customHeight="1">
       <c t="s" r="A368" s="6">
         <v>13</v>
       </c>
       <c r="B368" s="7">
-        <v>383</v>
+        <v>246</v>
       </c>
       <c t="s" r="C368" s="7">
         <v>14</v>
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>271</v>
+        <v>16</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>16</v>
+        <v>304</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>399</v>
+        <v>175</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12949,29 +12962,29 @@
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>16</v>
+        <v>304</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>304</v>
+        <v>16</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>175</v>
+        <v>333</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>114</v>
+        <v>347</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12982,29 +12995,29 @@
         <v>13</v>
       </c>
       <c r="B370" s="7">
-        <v>247</v>
+        <v>384</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>304</v>
+        <v>16</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>16</v>
+        <v>270</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>346</v>
+        <v>190</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13015,29 +13028,29 @@
         <v>13</v>
       </c>
       <c r="B371" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c t="s" r="C371" s="7">
         <v>14</v>
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>16</v>
+        <v>270</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>271</v>
+        <v>16</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -13048,29 +13061,29 @@
         <v>13</v>
       </c>
       <c r="B372" s="7">
-        <v>385</v>
+        <v>1312</v>
       </c>
       <c t="s" r="C372" s="7">
         <v>14</v>
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>271</v>
+        <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>321</v>
+        <v>192</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13081,78 +13094,78 @@
         <v>13</v>
       </c>
       <c r="B373" s="7">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c t="s" r="C373" s="7">
         <v>14</v>
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>131</v>
+        <v>16</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>192</v>
+        <v>279</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>182</v>
+        <v>398</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c r="M373" s="7"/>
     </row>
     <row r="374" ht="14.25" customHeight="1">
-      <c t="s" r="A374" s="6">
-        <v>13</v>
-      </c>
-      <c r="B374" s="7">
-        <v>1311</v>
-      </c>
-      <c t="s" r="C374" s="7">
-        <v>14</v>
-      </c>
+      <c r="A374" s="6"/>
+      <c r="B374" s="7"/>
+      <c r="C374" s="7"/>
       <c r="D374" s="7"/>
-      <c t="s" r="E374" s="7">
-        <v>397</v>
-      </c>
-      <c r="F374" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G374" s="8">
-        <v>131</v>
-      </c>
-      <c t="s" r="H374" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I374" s="7">
-        <v>280</v>
-      </c>
-      <c t="s" r="J374" s="7">
-        <v>400</v>
-      </c>
+      <c r="E374" s="7"/>
+      <c r="F374" s="7"/>
+      <c r="G374" s="8"/>
+      <c r="H374" s="8"/>
+      <c r="I374" s="7"/>
+      <c r="J374" s="7"/>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c r="M374" s="7"/>
     </row>
     <row r="375" ht="15" customHeight="1">
-      <c r="A375" s="6"/>
-      <c r="B375" s="7"/>
-      <c r="C375" s="7"/>
+      <c t="s" r="A375" s="6">
+        <v>13</v>
+      </c>
+      <c r="B375" s="7">
+        <v>1773</v>
+      </c>
+      <c t="s" r="C375" s="7">
+        <v>14</v>
+      </c>
       <c r="D375" s="7"/>
-      <c r="E375" s="7"/>
-      <c r="F375" s="7"/>
-      <c r="G375" s="8"/>
-      <c r="H375" s="8"/>
-      <c r="I375" s="7"/>
-      <c r="J375" s="7"/>
+      <c t="s" r="E375" s="7">
+        <v>399</v>
+      </c>
+      <c r="F375" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G375" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H375" s="8">
+        <v>170</v>
+      </c>
+      <c t="s" r="I375" s="7">
+        <v>122</v>
+      </c>
+      <c t="s" r="J375" s="7">
+        <v>400</v>
+      </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c r="M375" s="7"/>
@@ -13162,29 +13175,29 @@
         <v>13</v>
       </c>
       <c r="B376" s="7">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c t="s" r="C376" s="7">
         <v>14</v>
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G376" s="8">
+        <v>170</v>
+      </c>
+      <c t="s" r="H376" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H376" s="8">
-        <v>170</v>
-      </c>
       <c t="s" r="I376" s="7">
-        <v>122</v>
+        <v>217</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>402</v>
+        <v>303</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13195,29 +13208,29 @@
         <v>13</v>
       </c>
       <c r="B377" s="7">
-        <v>1774</v>
+        <v>439</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>14</v>
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>29</v>
+        <v>270</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>217</v>
+        <v>248</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>303</v>
+        <v>181</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13228,29 +13241,29 @@
         <v>13</v>
       </c>
       <c r="B378" s="7">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c t="s" r="C378" s="7">
         <v>14</v>
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
+        <v>270</v>
+      </c>
+      <c t="s" r="H378" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H378" s="8">
-        <v>271</v>
-      </c>
       <c t="s" r="I378" s="7">
-        <v>248</v>
+        <v>48</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>181</v>
+        <v>59</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13261,29 +13274,29 @@
         <v>13</v>
       </c>
       <c r="B379" s="7">
-        <v>438</v>
+        <v>7238</v>
       </c>
       <c t="s" r="C379" s="7">
         <v>14</v>
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>271</v>
+        <v>29</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>29</v>
+        <v>308</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>59</v>
+        <v>401</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13291,29 +13304,29 @@
     </row>
     <row r="380" ht="15" customHeight="1">
       <c t="s" r="A380" s="6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B380" s="7">
-        <v>7238</v>
+        <v>7239</v>
       </c>
       <c t="s" r="C380" s="7">
         <v>14</v>
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
+        <v>308</v>
+      </c>
+      <c t="s" r="H380" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H380" s="8">
-        <v>308</v>
-      </c>
       <c t="s" r="I380" s="7">
-        <v>60</v>
+        <v>402</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>403</v>
@@ -13323,86 +13336,88 @@
       <c r="M380" s="7"/>
     </row>
     <row r="381" ht="14.25" customHeight="1">
-      <c t="s" r="A381" s="6">
-        <v>37</v>
-      </c>
-      <c r="B381" s="7">
-        <v>7239</v>
-      </c>
-      <c t="s" r="C381" s="7">
-        <v>14</v>
-      </c>
+      <c r="A381" s="6"/>
+      <c r="B381" s="7"/>
+      <c r="C381" s="7"/>
       <c r="D381" s="7"/>
-      <c t="s" r="E381" s="7">
-        <v>401</v>
-      </c>
-      <c r="F381" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G381" s="8">
-        <v>308</v>
-      </c>
-      <c t="s" r="H381" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I381" s="7">
-        <v>404</v>
-      </c>
-      <c t="s" r="J381" s="7">
-        <v>405</v>
-      </c>
+      <c r="E381" s="7"/>
+      <c r="F381" s="7"/>
+      <c r="G381" s="8"/>
+      <c r="H381" s="8"/>
+      <c r="I381" s="7"/>
+      <c r="J381" s="7"/>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c r="M381" s="7"/>
     </row>
     <row r="382" ht="14.25" customHeight="1">
-      <c r="A382" s="6"/>
-      <c r="B382" s="7"/>
-      <c r="C382" s="7"/>
+      <c t="s" r="A382" s="6">
+        <v>13</v>
+      </c>
+      <c r="B382" s="7">
+        <v>625</v>
+      </c>
+      <c t="s" r="C382" s="7">
+        <v>14</v>
+      </c>
       <c r="D382" s="7"/>
-      <c r="E382" s="7"/>
-      <c r="F382" s="7"/>
-      <c r="G382" s="8"/>
-      <c r="H382" s="8"/>
-      <c r="I382" s="7"/>
-      <c r="J382" s="7"/>
+      <c t="s" r="E382" s="7">
+        <v>404</v>
+      </c>
+      <c r="F382" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G382" s="8">
+        <v>88</v>
+      </c>
+      <c t="s" r="H382" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I382" s="7">
+        <v>128</v>
+      </c>
+      <c t="s" r="J382" s="7">
+        <v>243</v>
+      </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
-      <c r="M382" s="7"/>
+      <c t="s" r="M382" s="7">
+        <v>405</v>
+      </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
       <c t="s" r="A383" s="6">
         <v>13</v>
       </c>
       <c r="B383" s="7">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c t="s" r="C383" s="7">
         <v>14</v>
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H383" s="8">
         <v>88</v>
       </c>
-      <c t="s" r="H383" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I383" s="7">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>243</v>
+        <v>56</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -13410,29 +13425,29 @@
         <v>13</v>
       </c>
       <c r="B384" s="7">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c t="s" r="C384" s="7">
         <v>14</v>
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>56</v>
+        <v>269</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13443,29 +13458,29 @@
         <v>13</v>
       </c>
       <c r="B385" s="7">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c t="s" r="C385" s="7">
         <v>14</v>
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H385" s="8">
         <v>88</v>
       </c>
-      <c t="s" r="H385" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I385" s="7">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>270</v>
+        <v>303</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13476,29 +13491,29 @@
         <v>13</v>
       </c>
       <c r="B386" s="7">
-        <v>636</v>
+        <v>874</v>
       </c>
       <c t="s" r="C386" s="7">
         <v>14</v>
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>88</v>
+        <v>47</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>303</v>
+        <v>96</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13509,115 +13524,117 @@
         <v>13</v>
       </c>
       <c r="B387" s="7">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c t="s" r="C387" s="7">
         <v>14</v>
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="H387" s="8">
         <v>88</v>
       </c>
-      <c t="s" r="H387" s="8">
-        <v>47</v>
-      </c>
       <c t="s" r="I387" s="7">
-        <v>20</v>
+        <v>366</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>96</v>
+        <v>407</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c r="M387" s="7"/>
     </row>
     <row r="388" ht="14.25" customHeight="1">
-      <c t="s" r="A388" s="6">
-        <v>13</v>
-      </c>
-      <c r="B388" s="7">
-        <v>875</v>
-      </c>
-      <c t="s" r="C388" s="7">
-        <v>14</v>
-      </c>
+      <c r="A388" s="6"/>
+      <c r="B388" s="7"/>
+      <c r="C388" s="7"/>
       <c r="D388" s="7"/>
-      <c t="s" r="E388" s="7">
-        <v>406</v>
-      </c>
-      <c r="F388" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G388" s="8">
-        <v>47</v>
-      </c>
-      <c t="s" r="H388" s="8">
-        <v>88</v>
-      </c>
-      <c t="s" r="I388" s="7">
-        <v>365</v>
-      </c>
-      <c t="s" r="J388" s="7">
-        <v>408</v>
-      </c>
+      <c r="E388" s="7"/>
+      <c r="F388" s="7"/>
+      <c r="G388" s="8"/>
+      <c r="H388" s="8"/>
+      <c r="I388" s="7"/>
+      <c r="J388" s="7"/>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c r="M388" s="7"/>
     </row>
     <row r="389" ht="14.25" customHeight="1">
-      <c r="A389" s="6"/>
-      <c r="B389" s="7"/>
-      <c r="C389" s="7"/>
+      <c t="s" r="A389" s="6">
+        <v>13</v>
+      </c>
+      <c r="B389" s="7">
+        <v>1382</v>
+      </c>
+      <c t="s" r="C389" s="7">
+        <v>14</v>
+      </c>
       <c r="D389" s="7"/>
-      <c r="E389" s="7"/>
-      <c r="F389" s="7"/>
-      <c r="G389" s="8"/>
-      <c r="H389" s="8"/>
-      <c r="I389" s="7"/>
-      <c r="J389" s="7"/>
+      <c t="s" r="E389" s="7">
+        <v>408</v>
+      </c>
+      <c r="F389" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G389" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H389" s="8">
+        <v>270</v>
+      </c>
+      <c t="s" r="I389" s="7">
+        <v>257</v>
+      </c>
+      <c t="s" r="J389" s="7">
+        <v>245</v>
+      </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
-      <c r="M389" s="7"/>
+      <c t="s" r="M389" s="7">
+        <v>409</v>
+      </c>
     </row>
     <row r="390" ht="15" customHeight="1">
       <c t="s" r="A390" s="6">
         <v>13</v>
       </c>
       <c r="B390" s="7">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c t="s" r="C390" s="7">
         <v>14</v>
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>16</v>
+        <v>270</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>271</v>
+        <v>16</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>410</v>
+        <v>243</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -13625,34 +13642,34 @@
         <v>13</v>
       </c>
       <c r="B391" s="7">
-        <v>1383</v>
+        <v>304</v>
       </c>
       <c t="s" r="C391" s="7">
         <v>14</v>
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>271</v>
+        <v>16</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>262</v>
+        <v>52</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>214</v>
+        <v>288</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>243</v>
+        <v>410</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -13660,64 +13677,62 @@
         <v>13</v>
       </c>
       <c r="B392" s="7">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c t="s" r="C392" s="7">
         <v>14</v>
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>131</v>
+        <v>16</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>52</v>
+        <v>411</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>289</v>
+        <v>113</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
-      <c t="s" r="M392" s="7">
-        <v>411</v>
-      </c>
+      <c r="M392" s="7"/>
     </row>
     <row r="393" ht="14.25" customHeight="1">
       <c t="s" r="A393" s="6">
         <v>13</v>
       </c>
       <c r="B393" s="7">
-        <v>303</v>
+        <v>807</v>
       </c>
       <c t="s" r="C393" s="7">
         <v>14</v>
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>131</v>
+        <v>16</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>412</v>
+        <v>176</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>113</v>
+        <v>34</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13728,29 +13743,29 @@
         <v>13</v>
       </c>
       <c r="B394" s="7">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c t="s" r="C394" s="7">
         <v>14</v>
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>180</v>
+        <v>16</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>176</v>
+        <v>242</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>34</v>
+        <v>181</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13761,110 +13776,112 @@
         <v>13</v>
       </c>
       <c r="B395" s="7">
-        <v>800</v>
+        <v>642</v>
       </c>
       <c t="s" r="C395" s="7">
         <v>14</v>
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>180</v>
+        <v>16</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>242</v>
+        <v>412</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>181</v>
+        <v>83</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c r="M395" s="7"/>
     </row>
     <row r="396" ht="14.25" customHeight="1">
-      <c t="s" r="A396" s="6">
-        <v>13</v>
-      </c>
-      <c r="B396" s="7">
-        <v>642</v>
-      </c>
-      <c t="s" r="C396" s="7">
-        <v>14</v>
-      </c>
+      <c r="A396" s="6"/>
+      <c r="B396" s="7"/>
+      <c r="C396" s="7"/>
       <c r="D396" s="7"/>
-      <c t="s" r="E396" s="7">
-        <v>409</v>
-      </c>
-      <c r="F396" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G396" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H396" s="8">
-        <v>88</v>
-      </c>
-      <c t="s" r="I396" s="7">
-        <v>413</v>
-      </c>
-      <c t="s" r="J396" s="7">
-        <v>83</v>
-      </c>
+      <c r="E396" s="7"/>
+      <c r="F396" s="7"/>
+      <c r="G396" s="8"/>
+      <c r="H396" s="8"/>
+      <c r="I396" s="7"/>
+      <c r="J396" s="7"/>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c r="M396" s="7"/>
     </row>
     <row r="397" ht="14.25" customHeight="1">
-      <c r="A397" s="6"/>
-      <c r="B397" s="7"/>
-      <c r="C397" s="7"/>
+      <c t="s" r="A397" s="6">
+        <v>13</v>
+      </c>
+      <c r="B397" s="7">
+        <v>125</v>
+      </c>
+      <c t="s" r="C397" s="7">
+        <v>14</v>
+      </c>
       <c r="D397" s="7"/>
-      <c r="E397" s="7"/>
-      <c r="F397" s="7"/>
-      <c r="G397" s="8"/>
-      <c r="H397" s="8"/>
-      <c r="I397" s="7"/>
-      <c r="J397" s="7"/>
+      <c t="s" r="E397" s="7">
+        <v>413</v>
+      </c>
+      <c r="F397" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G397" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H397" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I397" s="7">
+        <v>294</v>
+      </c>
+      <c t="s" r="J397" s="7">
+        <v>327</v>
+      </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
-      <c r="M397" s="7"/>
+      <c t="s" r="M397" s="7">
+        <v>414</v>
+      </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
       <c t="s" r="A398" s="6">
         <v>13</v>
       </c>
       <c r="B398" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c t="s" r="C398" s="7">
         <v>14</v>
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G398" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H398" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H398" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I398" s="7">
-        <v>294</v>
+        <v>62</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>327</v>
+        <v>400</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13877,29 +13894,29 @@
         <v>13</v>
       </c>
       <c r="B399" s="7">
-        <v>128</v>
+        <v>453</v>
       </c>
       <c t="s" r="C399" s="7">
         <v>14</v>
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>402</v>
+        <v>232</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13910,29 +13927,29 @@
         <v>13</v>
       </c>
       <c r="B400" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c t="s" r="C400" s="7">
         <v>14</v>
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G400" s="8">
+        <v>44</v>
+      </c>
+      <c t="s" r="H400" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H400" s="8">
-        <v>44</v>
-      </c>
       <c t="s" r="I400" s="7">
-        <v>42</v>
+        <v>248</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>232</v>
+        <v>48</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13943,29 +13960,29 @@
         <v>13</v>
       </c>
       <c r="B401" s="7">
-        <v>456</v>
+        <v>781</v>
       </c>
       <c t="s" r="C401" s="7">
         <v>14</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>248</v>
+        <v>68</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13976,88 +13993,90 @@
         <v>13</v>
       </c>
       <c r="B402" s="7">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c t="s" r="C402" s="7">
         <v>14</v>
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G402" s="8">
+        <v>170</v>
+      </c>
+      <c t="s" r="H402" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H402" s="8">
-        <v>170</v>
-      </c>
       <c t="s" r="I402" s="7">
-        <v>68</v>
+        <v>124</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>69</v>
+        <v>416</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c r="M402" s="7"/>
     </row>
     <row r="403" ht="14.25" customHeight="1">
-      <c t="s" r="A403" s="6">
-        <v>13</v>
-      </c>
-      <c r="B403" s="7">
-        <v>780</v>
-      </c>
-      <c t="s" r="C403" s="7">
-        <v>14</v>
-      </c>
+      <c r="A403" s="6"/>
+      <c r="B403" s="7"/>
+      <c r="C403" s="7"/>
       <c r="D403" s="7"/>
-      <c t="s" r="E403" s="7">
-        <v>414</v>
-      </c>
-      <c r="F403" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G403" s="8">
-        <v>170</v>
-      </c>
-      <c t="s" r="H403" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I403" s="7">
-        <v>124</v>
-      </c>
-      <c t="s" r="J403" s="7">
-        <v>416</v>
-      </c>
+      <c r="E403" s="7"/>
+      <c r="F403" s="7"/>
+      <c r="G403" s="8"/>
+      <c r="H403" s="8"/>
+      <c r="I403" s="7"/>
+      <c r="J403" s="7"/>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c r="M403" s="7"/>
     </row>
     <row r="404" ht="14.25" customHeight="1">
-      <c r="A404" s="6"/>
-      <c r="B404" s="7"/>
-      <c r="C404" s="7"/>
+      <c t="s" r="A404" s="6">
+        <v>13</v>
+      </c>
+      <c r="B404" s="7">
+        <v>989</v>
+      </c>
+      <c t="s" r="C404" s="7">
+        <v>14</v>
+      </c>
       <c r="D404" s="7"/>
-      <c r="E404" s="7"/>
-      <c r="F404" s="7"/>
-      <c r="G404" s="8"/>
-      <c r="H404" s="8"/>
-      <c r="I404" s="7"/>
-      <c r="J404" s="7"/>
+      <c t="s" r="E404" s="7">
+        <v>417</v>
+      </c>
+      <c r="F404" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G404" s="8">
+        <v>71</v>
+      </c>
+      <c t="s" r="H404" s="8">
+        <v>88</v>
+      </c>
+      <c t="s" r="I404" s="7">
+        <v>208</v>
+      </c>
+      <c t="s" r="J404" s="7">
+        <v>18</v>
+      </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
-      <c r="M404" s="7"/>
+      <c t="s" r="M404" s="7">
+        <v>384</v>
+      </c>
     </row>
     <row r="405" ht="15" customHeight="1">
       <c t="s" r="A405" s="6">
         <v>13</v>
       </c>
       <c r="B405" s="7">
-        <v>989</v>
+        <v>510</v>
       </c>
       <c t="s" r="C405" s="7">
         <v>14</v>
@@ -14070,29 +14089,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>18</v>
+        <v>198</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
-      <c t="s" r="M405" s="7">
-        <v>387</v>
-      </c>
+      <c r="M405" s="7"/>
     </row>
     <row r="406" ht="14.25" customHeight="1">
       <c t="s" r="A406" s="6">
         <v>13</v>
       </c>
       <c r="B406" s="7">
-        <v>510</v>
+        <v>913</v>
       </c>
       <c t="s" r="C406" s="7">
         <v>14</v>
@@ -14105,16 +14122,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>88</v>
+        <v>29</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>29</v>
+        <v>418</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>198</v>
+        <v>381</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14125,7 +14142,7 @@
         <v>13</v>
       </c>
       <c r="B407" s="7">
-        <v>773</v>
+        <v>914</v>
       </c>
       <c t="s" r="C407" s="7">
         <v>14</v>
@@ -14138,16 +14155,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G407" s="8">
+        <v>418</v>
+      </c>
+      <c t="s" r="H407" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H407" s="8">
-        <v>170</v>
-      </c>
       <c t="s" r="I407" s="7">
-        <v>272</v>
+        <v>94</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14158,7 +14175,7 @@
         <v>13</v>
       </c>
       <c r="B408" s="7">
-        <v>776</v>
+        <v>7526</v>
       </c>
       <c t="s" r="C408" s="7">
         <v>14</v>
@@ -14171,16 +14188,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>170</v>
+        <v>29</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>29</v>
+        <v>220</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>292</v>
+        <v>343</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>299</v>
+        <v>49</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14191,7 +14208,7 @@
         <v>37</v>
       </c>
       <c r="B409" s="7">
-        <v>958</v>
+        <v>7527</v>
       </c>
       <c t="s" r="C409" s="7">
         <v>14</v>
@@ -14204,16 +14221,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
+        <v>220</v>
+      </c>
+      <c t="s" r="H409" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H409" s="8">
-        <v>418</v>
-      </c>
       <c t="s" r="I409" s="7">
-        <v>249</v>
+        <v>419</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>107</v>
+        <v>420</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14246,7 +14263,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14258,7 +14275,7 @@
         <v>304</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>52</v>
@@ -14266,7 +14283,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14281,7 +14298,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14300,7 +14317,9 @@
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
-      <c r="M412" s="7"/>
+      <c t="s" r="M412" s="7">
+        <v>91</v>
+      </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
       <c t="s" r="A413" s="6">
@@ -14314,7 +14333,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14323,7 +14342,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>81</v>
@@ -14347,13 +14366,13 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>16</v>
@@ -14380,7 +14399,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -14389,13 +14408,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c t="s" r="I415" s="7">
         <v>416</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14413,22 +14432,22 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14461,7 +14480,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14473,7 +14492,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c t="s" r="J418" s="7">
         <v>311</v>
@@ -14489,14 +14508,14 @@
         <v>13</v>
       </c>
       <c r="B419" s="7">
-        <v>137</v>
+        <v>905</v>
       </c>
       <c t="s" r="C419" s="7">
         <v>14</v>
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14505,64 +14524,72 @@
         <v>29</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>16</v>
+        <v>302</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>19</v>
-      </c>
-      <c r="K419" s="7"/>
+        <v>161</v>
+      </c>
+      <c t="s" r="K419" s="7">
+        <v>55</v>
+      </c>
       <c r="L419" s="7"/>
-      <c r="M419" s="7"/>
+      <c t="s" r="M419" s="7">
+        <v>179</v>
+      </c>
     </row>
     <row r="420" ht="15" customHeight="1">
       <c t="s" r="A420" s="6">
         <v>13</v>
       </c>
       <c r="B420" s="7">
-        <v>144</v>
+        <v>906</v>
       </c>
       <c t="s" r="C420" s="7">
         <v>14</v>
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>16</v>
+        <v>302</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>382</v>
-      </c>
-      <c r="K420" s="7"/>
+        <v>379</v>
+      </c>
+      <c t="s" r="K420" s="7">
+        <v>248</v>
+      </c>
       <c r="L420" s="7"/>
-      <c r="M420" s="7"/>
+      <c t="s" r="M420" s="7">
+        <v>291</v>
+      </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
       <c t="s" r="A421" s="6">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="B421" s="7">
-        <v>519</v>
+        <v>982</v>
       </c>
       <c t="s" r="C421" s="7">
         <v>14</v>
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14571,112 +14598,116 @@
         <v>29</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>59</v>
+        <v>427</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c r="M421" s="7"/>
     </row>
     <row r="422" ht="14.25" customHeight="1">
-      <c t="s" r="A422" s="6">
-        <v>13</v>
-      </c>
-      <c r="B422" s="7">
-        <v>522</v>
-      </c>
-      <c t="s" r="C422" s="7">
-        <v>14</v>
-      </c>
+      <c r="A422" s="6"/>
+      <c r="B422" s="7"/>
+      <c r="C422" s="7"/>
       <c r="D422" s="7"/>
-      <c t="s" r="E422" s="7">
-        <v>424</v>
-      </c>
-      <c r="F422" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G422" s="8">
-        <v>88</v>
-      </c>
-      <c t="s" r="H422" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I422" s="7">
-        <v>60</v>
-      </c>
-      <c t="s" r="J422" s="7">
-        <v>228</v>
-      </c>
+      <c r="E422" s="7"/>
+      <c r="F422" s="7"/>
+      <c r="G422" s="8"/>
+      <c r="H422" s="8"/>
+      <c r="I422" s="7"/>
+      <c r="J422" s="7"/>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c r="M422" s="7"/>
     </row>
     <row r="423" ht="14.25" customHeight="1">
       <c t="s" r="A423" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B423" s="7">
-        <v>982</v>
+        <v>350</v>
       </c>
       <c t="s" r="C423" s="7">
         <v>14</v>
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>71</v>
+        <v>264</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>425</v>
+        <v>26</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
-      <c r="M423" s="7"/>
+      <c t="s" r="M423" s="7">
+        <v>268</v>
+      </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
-      <c r="A424" s="6"/>
-      <c r="B424" s="7"/>
-      <c r="C424" s="7"/>
+      <c t="s" r="A424" s="6">
+        <v>13</v>
+      </c>
+      <c r="B424" s="7">
+        <v>351</v>
+      </c>
+      <c t="s" r="C424" s="7">
+        <v>14</v>
+      </c>
       <c r="D424" s="7"/>
-      <c r="E424" s="7"/>
-      <c r="F424" s="7"/>
-      <c r="G424" s="8"/>
-      <c r="H424" s="8"/>
-      <c r="I424" s="7"/>
-      <c r="J424" s="7"/>
+      <c t="s" r="E424" s="7">
+        <v>428</v>
+      </c>
+      <c r="F424" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G424" s="8">
+        <v>264</v>
+      </c>
+      <c t="s" r="H424" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I424" s="7">
+        <v>39</v>
+      </c>
+      <c t="s" r="J424" s="7">
+        <v>173</v>
+      </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
-      <c r="M424" s="7"/>
+      <c t="s" r="M424" s="7">
+        <v>429</v>
+      </c>
     </row>
     <row r="425" ht="15" customHeight="1">
       <c t="s" r="A425" s="6">
         <v>13</v>
       </c>
       <c r="B425" s="7">
-        <v>350</v>
+        <v>634</v>
       </c>
       <c t="s" r="C425" s="7">
         <v>14</v>
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14685,83 +14716,79 @@
         <v>16</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>265</v>
+        <v>88</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>26</v>
+        <v>411</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
-      <c t="s" r="M425" s="7">
-        <v>269</v>
-      </c>
+      <c r="M425" s="7"/>
     </row>
     <row r="426" ht="14.25" customHeight="1">
       <c t="s" r="A426" s="6">
         <v>13</v>
       </c>
       <c r="B426" s="7">
-        <v>351</v>
+        <v>1504</v>
       </c>
       <c t="s" r="C426" s="7">
         <v>14</v>
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>265</v>
+        <v>88</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>173</v>
+        <v>67</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
-      <c t="s" r="M426" s="7">
-        <v>427</v>
-      </c>
+      <c r="M426" s="7"/>
     </row>
     <row r="427" ht="14.25" customHeight="1">
       <c t="s" r="A427" s="6">
         <v>13</v>
       </c>
       <c r="B427" s="7">
-        <v>634</v>
+        <v>1505</v>
       </c>
       <c t="s" r="C427" s="7">
         <v>14</v>
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G427" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c t="s" r="H427" s="8">
         <v>88</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>412</v>
+        <v>198</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14772,14 +14799,14 @@
         <v>13</v>
       </c>
       <c r="B428" s="7">
-        <v>1504</v>
+        <v>637</v>
       </c>
       <c t="s" r="C428" s="7">
         <v>14</v>
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -14788,13 +14815,13 @@
         <v>88</v>
       </c>
       <c t="s" r="H428" s="8">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14805,63 +14832,45 @@
         <v>13</v>
       </c>
       <c r="B429" s="7">
-        <v>1505</v>
+        <v>160</v>
       </c>
       <c t="s" r="C429" s="7">
         <v>14</v>
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G429" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H429" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H429" s="8">
-        <v>88</v>
-      </c>
       <c t="s" r="I429" s="7">
-        <v>198</v>
+        <v>339</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
       <c r="M429" s="7"/>
     </row>
     <row r="430" ht="15" customHeight="1">
-      <c t="s" r="A430" s="6">
-        <v>13</v>
-      </c>
-      <c r="B430" s="7">
-        <v>637</v>
-      </c>
-      <c t="s" r="C430" s="7">
-        <v>14</v>
-      </c>
+      <c r="A430" s="6"/>
+      <c r="B430" s="7"/>
+      <c r="C430" s="7"/>
       <c r="D430" s="7"/>
-      <c t="s" r="E430" s="7">
-        <v>426</v>
-      </c>
-      <c r="F430" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G430" s="8">
-        <v>88</v>
-      </c>
-      <c t="s" r="H430" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I430" s="7">
-        <v>116</v>
-      </c>
-      <c t="s" r="J430" s="7">
-        <v>21</v>
-      </c>
+      <c r="E430" s="7"/>
+      <c r="F430" s="7"/>
+      <c r="G430" s="8"/>
+      <c r="H430" s="8"/>
+      <c r="I430" s="7"/>
+      <c r="J430" s="7"/>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
       <c r="M430" s="7"/>
@@ -14871,145 +14880,145 @@
         <v>13</v>
       </c>
       <c r="B431" s="7">
-        <v>160</v>
+        <v>773</v>
       </c>
       <c t="s" r="C431" s="7">
         <v>14</v>
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="F431" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G431" s="8">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>29</v>
+        <v>170</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>338</v>
+        <v>271</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>24</v>
+        <v>291</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
       <c r="M431" s="7"/>
     </row>
     <row r="432" ht="14.25" customHeight="1">
-      <c r="A432" s="6"/>
-      <c r="B432" s="7"/>
-      <c r="C432" s="7"/>
+      <c t="s" r="A432" s="6">
+        <v>13</v>
+      </c>
+      <c r="B432" s="7">
+        <v>776</v>
+      </c>
+      <c t="s" r="C432" s="7">
+        <v>14</v>
+      </c>
       <c r="D432" s="7"/>
-      <c r="E432" s="7"/>
-      <c r="F432" s="7"/>
-      <c r="G432" s="8"/>
-      <c r="H432" s="8"/>
-      <c r="I432" s="7"/>
-      <c r="J432" s="7"/>
+      <c t="s" r="E432" s="7">
+        <v>430</v>
+      </c>
+      <c r="F432" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G432" s="8">
+        <v>170</v>
+      </c>
+      <c t="s" r="H432" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="I432" s="7">
+        <v>292</v>
+      </c>
+      <c t="s" r="J432" s="7">
+        <v>299</v>
+      </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c r="M432" s="7"/>
     </row>
     <row r="433" ht="14.25" customHeight="1">
-      <c t="s" r="A433" s="6">
-        <v>13</v>
-      </c>
-      <c r="B433" s="7">
-        <v>921</v>
-      </c>
-      <c t="s" r="C433" s="7">
-        <v>14</v>
-      </c>
+      <c r="A433" s="6"/>
+      <c r="B433" s="7"/>
+      <c r="C433" s="7"/>
       <c r="D433" s="7"/>
-      <c t="s" r="E433" s="7">
-        <v>428</v>
-      </c>
-      <c r="F433" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G433" s="8">
-        <v>109</v>
-      </c>
-      <c t="s" r="H433" s="8">
-        <v>29</v>
-      </c>
-      <c t="s" r="I433" s="7">
-        <v>225</v>
-      </c>
-      <c t="s" r="J433" s="7">
-        <v>42</v>
-      </c>
+      <c r="E433" s="7"/>
+      <c r="F433" s="7"/>
+      <c r="G433" s="8"/>
+      <c r="H433" s="8"/>
+      <c r="I433" s="7"/>
+      <c r="J433" s="7"/>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
-      <c t="s" r="M433" s="7">
-        <v>217</v>
-      </c>
+      <c r="M433" s="7"/>
     </row>
     <row r="434" ht="14.25" customHeight="1">
       <c t="s" r="A434" s="6">
         <v>13</v>
       </c>
       <c r="B434" s="7">
-        <v>942</v>
+        <v>921</v>
       </c>
       <c t="s" r="C434" s="7">
         <v>14</v>
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G434" s="8">
+        <v>109</v>
+      </c>
+      <c t="s" r="H434" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H434" s="8">
-        <v>284</v>
-      </c>
       <c t="s" r="I434" s="7">
-        <v>146</v>
+        <v>225</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
-      <c r="M434" s="7"/>
+      <c t="s" r="M434" s="7">
+        <v>217</v>
+      </c>
     </row>
     <row r="435" ht="15" customHeight="1">
       <c t="s" r="A435" s="6">
         <v>13</v>
       </c>
       <c r="B435" s="7">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c t="s" r="C435" s="7">
         <v>14</v>
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>284</v>
+        <v>29</v>
       </c>
       <c t="s" r="H435" s="8">
-        <v>29</v>
+        <v>283</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>296</v>
+        <v>21</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -15020,233 +15029,231 @@
         <v>13</v>
       </c>
       <c r="B436" s="7">
-        <v>962</v>
+        <v>943</v>
       </c>
       <c t="s" r="C436" s="7">
         <v>14</v>
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G436" s="8">
+        <v>283</v>
+      </c>
+      <c t="s" r="H436" s="8">
         <v>29</v>
       </c>
-      <c t="s" r="H436" s="8">
-        <v>47</v>
-      </c>
       <c t="s" r="I436" s="7">
-        <v>429</v>
+        <v>35</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>120</v>
+        <v>296</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c r="M436" s="7"/>
     </row>
     <row r="437" ht="14.25" customHeight="1">
-      <c r="A437" s="6"/>
-      <c r="B437" s="7"/>
-      <c r="C437" s="7"/>
+      <c t="s" r="A437" s="6">
+        <v>13</v>
+      </c>
+      <c r="B437" s="7">
+        <v>962</v>
+      </c>
+      <c t="s" r="C437" s="7">
+        <v>14</v>
+      </c>
       <c r="D437" s="7"/>
-      <c r="E437" s="7"/>
-      <c r="F437" s="7"/>
-      <c r="G437" s="8"/>
-      <c r="H437" s="8"/>
-      <c r="I437" s="7"/>
-      <c r="J437" s="7"/>
+      <c t="s" r="E437" s="7">
+        <v>431</v>
+      </c>
+      <c r="F437" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G437" s="8">
+        <v>29</v>
+      </c>
+      <c t="s" r="H437" s="8">
+        <v>47</v>
+      </c>
+      <c t="s" r="I437" s="7">
+        <v>432</v>
+      </c>
+      <c t="s" r="J437" s="7">
+        <v>120</v>
+      </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c r="M437" s="7"/>
     </row>
     <row r="438" ht="14.25" customHeight="1">
-      <c t="s" r="A438" s="6">
-        <v>13</v>
-      </c>
-      <c r="B438" s="7">
-        <v>801</v>
-      </c>
-      <c t="s" r="C438" s="7">
-        <v>14</v>
-      </c>
+      <c r="A438" s="6"/>
+      <c r="B438" s="7"/>
+      <c r="C438" s="7"/>
       <c r="D438" s="7"/>
-      <c t="s" r="E438" s="7">
-        <v>430</v>
-      </c>
-      <c r="F438" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G438" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H438" s="8">
-        <v>180</v>
-      </c>
-      <c t="s" r="I438" s="7">
-        <v>325</v>
-      </c>
-      <c t="s" r="J438" s="7">
-        <v>399</v>
-      </c>
+      <c r="E438" s="7"/>
+      <c r="F438" s="7"/>
+      <c r="G438" s="8"/>
+      <c r="H438" s="8"/>
+      <c r="I438" s="7"/>
+      <c r="J438" s="7"/>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
-      <c t="s" r="M438" s="7">
-        <v>431</v>
-      </c>
+      <c r="M438" s="7"/>
     </row>
     <row r="439" ht="14.25" customHeight="1">
       <c t="s" r="A439" s="6">
         <v>13</v>
       </c>
       <c r="B439" s="7">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c t="s" r="C439" s="7">
         <v>14</v>
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G439" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H439" s="8">
         <v>180</v>
       </c>
-      <c t="s" r="H439" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I439" s="7">
-        <v>161</v>
+        <v>325</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>42</v>
+        <v>397</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
-      <c r="M439" s="7"/>
+      <c t="s" r="M439" s="7">
+        <v>434</v>
+      </c>
     </row>
     <row r="440" ht="15" customHeight="1">
       <c t="s" r="A440" s="6">
         <v>13</v>
       </c>
       <c r="B440" s="7">
-        <v>600</v>
+        <v>802</v>
       </c>
       <c t="s" r="C440" s="7">
         <v>14</v>
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G440" s="8">
-        <v>16</v>
+        <v>180</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>170</v>
+        <v>16</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>147</v>
+        <v>42</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c r="M440" s="7"/>
     </row>
     <row r="441" ht="14.25" customHeight="1">
-      <c r="A441" s="6"/>
-      <c r="B441" s="7"/>
-      <c r="C441" s="7"/>
+      <c t="s" r="A441" s="6">
+        <v>13</v>
+      </c>
+      <c r="B441" s="7">
+        <v>600</v>
+      </c>
+      <c t="s" r="C441" s="7">
+        <v>14</v>
+      </c>
       <c r="D441" s="7"/>
-      <c r="E441" s="7"/>
-      <c r="F441" s="7"/>
-      <c r="G441" s="8"/>
-      <c r="H441" s="8"/>
-      <c r="I441" s="7"/>
-      <c r="J441" s="7"/>
+      <c t="s" r="E441" s="7">
+        <v>433</v>
+      </c>
+      <c r="F441" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G441" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H441" s="8">
+        <v>170</v>
+      </c>
+      <c t="s" r="I441" s="7">
+        <v>198</v>
+      </c>
+      <c t="s" r="J441" s="7">
+        <v>147</v>
+      </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c r="M441" s="7"/>
     </row>
     <row r="442" ht="14.25" customHeight="1">
-      <c t="s" r="A442" s="6">
-        <v>13</v>
-      </c>
-      <c r="B442" s="7">
-        <v>224</v>
-      </c>
-      <c t="s" r="C442" s="7">
-        <v>14</v>
-      </c>
+      <c r="A442" s="6"/>
+      <c r="B442" s="7"/>
+      <c r="C442" s="7"/>
       <c r="D442" s="7"/>
-      <c t="s" r="E442" s="7">
-        <v>432</v>
-      </c>
-      <c r="F442" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G442" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H442" s="8">
-        <v>203</v>
-      </c>
-      <c t="s" r="I442" s="7">
-        <v>268</v>
-      </c>
-      <c t="s" r="J442" s="7">
-        <v>354</v>
-      </c>
+      <c r="E442" s="7"/>
+      <c r="F442" s="7"/>
+      <c r="G442" s="8"/>
+      <c r="H442" s="8"/>
+      <c r="I442" s="7"/>
+      <c r="J442" s="7"/>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
-      <c t="s" r="M442" s="7">
-        <v>433</v>
-      </c>
+      <c r="M442" s="7"/>
     </row>
     <row r="443" ht="14.25" customHeight="1">
       <c t="s" r="A443" s="6">
         <v>13</v>
       </c>
       <c r="B443" s="7">
-        <v>741</v>
+        <v>224</v>
       </c>
       <c t="s" r="C443" s="7">
         <v>14</v>
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F443" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G443" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H443" s="8">
         <v>203</v>
       </c>
-      <c t="s" r="H443" s="8">
-        <v>265</v>
-      </c>
       <c t="s" r="I443" s="7">
-        <v>434</v>
+        <v>267</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>129</v>
+        <v>355</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -15254,95 +15261,99 @@
         <v>13</v>
       </c>
       <c r="B444" s="7">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c t="s" r="C444" s="7">
         <v>14</v>
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F444" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>265</v>
+        <v>203</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>203</v>
+        <v>264</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>53</v>
+        <v>437</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>311</v>
+        <v>129</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
-      <c r="M444" s="7"/>
+      <c t="s" r="M444" s="7">
+        <v>438</v>
+      </c>
     </row>
     <row r="445" ht="15" customHeight="1">
       <c t="s" r="A445" s="6">
         <v>13</v>
       </c>
       <c r="B445" s="7">
-        <v>227</v>
+        <v>740</v>
       </c>
       <c t="s" r="C445" s="7">
         <v>14</v>
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F445" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G445" s="8">
+        <v>264</v>
+      </c>
+      <c t="s" r="H445" s="8">
         <v>203</v>
       </c>
-      <c t="s" r="H445" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I445" s="7">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>42</v>
+        <v>311</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
-      <c r="M445" s="7"/>
+      <c t="s" r="M445" s="7">
+        <v>439</v>
+      </c>
     </row>
     <row r="446" ht="14.25" customHeight="1">
       <c t="s" r="A446" s="6">
         <v>13</v>
       </c>
       <c r="B446" s="7">
-        <v>362</v>
+        <v>227</v>
       </c>
       <c t="s" r="C446" s="7">
         <v>14</v>
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G446" s="8">
-        <v>16</v>
+        <v>203</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>198</v>
+        <v>90</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
@@ -15353,29 +15364,29 @@
         <v>13</v>
       </c>
       <c r="B447" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c t="s" r="C447" s="7">
         <v>14</v>
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G447" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H447" s="8">
         <v>112</v>
       </c>
-      <c t="s" r="H447" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I447" s="7">
-        <v>272</v>
+        <v>198</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>234</v>
+        <v>20</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
@@ -15386,29 +15397,29 @@
         <v>13</v>
       </c>
       <c r="B448" s="7">
-        <v>3948</v>
+        <v>363</v>
       </c>
       <c t="s" r="C448" s="7">
         <v>14</v>
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G448" s="8">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c t="s" r="H448" s="8">
-        <v>348</v>
+        <v>16</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>382</v>
+        <v>271</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15416,212 +15427,212 @@
     </row>
     <row r="449" ht="14.25" customHeight="1">
       <c t="s" r="A449" s="6">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="B449" s="7">
-        <v>3949</v>
+        <v>3948</v>
       </c>
       <c t="s" r="C449" s="7">
         <v>14</v>
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G449" s="8">
-        <v>348</v>
+        <v>16</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>16</v>
+        <v>349</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>425</v>
+        <v>381</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>268</v>
+        <v>183</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c r="M449" s="7"/>
     </row>
     <row r="450" ht="15" customHeight="1">
-      <c r="A450" s="6"/>
-      <c r="B450" s="7"/>
-      <c r="C450" s="7"/>
+      <c t="s" r="A450" s="6">
+        <v>37</v>
+      </c>
+      <c r="B450" s="7">
+        <v>3949</v>
+      </c>
+      <c t="s" r="C450" s="7">
+        <v>14</v>
+      </c>
       <c r="D450" s="7"/>
-      <c r="E450" s="7"/>
-      <c r="F450" s="7"/>
-      <c r="G450" s="8"/>
-      <c r="H450" s="8"/>
-      <c r="I450" s="7"/>
-      <c r="J450" s="7"/>
+      <c t="s" r="E450" s="7">
+        <v>435</v>
+      </c>
+      <c r="F450" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G450" s="8">
+        <v>349</v>
+      </c>
+      <c t="s" r="H450" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I450" s="7">
+        <v>427</v>
+      </c>
+      <c t="s" r="J450" s="7">
+        <v>267</v>
+      </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
       <c r="M450" s="7"/>
     </row>
     <row r="451" ht="14.25" customHeight="1">
-      <c t="s" r="A451" s="6">
-        <v>13</v>
-      </c>
-      <c r="B451" s="7">
-        <v>34</v>
-      </c>
-      <c t="s" r="C451" s="7">
-        <v>436</v>
-      </c>
+      <c r="A451" s="6"/>
+      <c r="B451" s="7"/>
+      <c r="C451" s="7"/>
       <c r="D451" s="7"/>
-      <c t="s" r="E451" s="7">
-        <v>437</v>
-      </c>
-      <c r="F451" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G451" s="8">
-        <v>88</v>
-      </c>
-      <c t="s" r="H451" s="8">
-        <v>438</v>
-      </c>
-      <c t="s" r="I451" s="7">
-        <v>30</v>
-      </c>
-      <c t="s" r="J451" s="7">
-        <v>161</v>
-      </c>
+      <c r="E451" s="7"/>
+      <c r="F451" s="7"/>
+      <c r="G451" s="8"/>
+      <c r="H451" s="8"/>
+      <c r="I451" s="7"/>
+      <c r="J451" s="7"/>
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
       <c r="M451" s="7"/>
     </row>
     <row r="452" ht="14.25" customHeight="1">
-      <c r="A452" s="6"/>
-      <c r="B452" s="7"/>
-      <c r="C452" s="7"/>
+      <c t="s" r="A452" s="6">
+        <v>13</v>
+      </c>
+      <c r="B452" s="7">
+        <v>34</v>
+      </c>
+      <c t="s" r="C452" s="7">
+        <v>440</v>
+      </c>
       <c r="D452" s="7"/>
-      <c r="E452" s="7"/>
-      <c r="F452" s="7"/>
-      <c r="G452" s="8"/>
-      <c r="H452" s="8"/>
-      <c r="I452" s="7"/>
-      <c r="J452" s="7"/>
+      <c t="s" r="E452" s="7">
+        <v>441</v>
+      </c>
+      <c r="F452" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G452" s="8">
+        <v>88</v>
+      </c>
+      <c t="s" r="H452" s="8">
+        <v>442</v>
+      </c>
+      <c t="s" r="I452" s="7">
+        <v>30</v>
+      </c>
+      <c t="s" r="J452" s="7">
+        <v>161</v>
+      </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
       <c r="M452" s="7"/>
     </row>
     <row r="453" ht="14.25" customHeight="1">
-      <c t="s" r="A453" s="6">
-        <v>13</v>
-      </c>
-      <c r="B453" s="7">
-        <v>86</v>
-      </c>
-      <c t="s" r="C453" s="7">
-        <v>14</v>
-      </c>
+      <c r="A453" s="6"/>
+      <c r="B453" s="7"/>
+      <c r="C453" s="7"/>
       <c r="D453" s="7"/>
-      <c t="s" r="E453" s="7">
-        <v>439</v>
-      </c>
-      <c r="F453" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G453" s="8">
-        <v>440</v>
-      </c>
-      <c t="s" r="H453" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I453" s="7">
-        <v>289</v>
-      </c>
-      <c t="s" r="J453" s="7">
-        <v>93</v>
-      </c>
+      <c r="E453" s="7"/>
+      <c r="F453" s="7"/>
+      <c r="G453" s="8"/>
+      <c r="H453" s="8"/>
+      <c r="I453" s="7"/>
+      <c r="J453" s="7"/>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
-      <c t="s" r="M453" s="7">
-        <v>441</v>
-      </c>
+      <c r="M453" s="7"/>
     </row>
     <row r="454" ht="14.25" customHeight="1">
       <c t="s" r="A454" s="6">
         <v>13</v>
       </c>
       <c r="B454" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="C454" s="7">
         <v>14</v>
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>16</v>
+        <v>444</v>
       </c>
       <c t="s" r="H454" s="8">
-        <v>440</v>
+        <v>16</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>150</v>
+        <v>288</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>434</v>
+        <v>93</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
-      <c r="M454" s="7"/>
+      <c t="s" r="M454" s="7">
+        <v>102</v>
+      </c>
     </row>
     <row r="455" ht="15" customHeight="1">
-      <c r="A455" s="6"/>
-      <c r="B455" s="7"/>
-      <c r="C455" s="7"/>
+      <c t="s" r="A455" s="6">
+        <v>13</v>
+      </c>
+      <c r="B455" s="7">
+        <v>85</v>
+      </c>
+      <c t="s" r="C455" s="7">
+        <v>14</v>
+      </c>
       <c r="D455" s="7"/>
-      <c r="E455" s="7"/>
-      <c r="F455" s="7"/>
-      <c r="G455" s="8"/>
-      <c r="H455" s="8"/>
-      <c r="I455" s="7"/>
-      <c r="J455" s="7"/>
+      <c t="s" r="E455" s="7">
+        <v>443</v>
+      </c>
+      <c r="F455" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G455" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H455" s="8">
+        <v>444</v>
+      </c>
+      <c t="s" r="I455" s="7">
+        <v>150</v>
+      </c>
+      <c t="s" r="J455" s="7">
+        <v>437</v>
+      </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c r="M455" s="7"/>
     </row>
     <row r="456" ht="14.25" customHeight="1">
-      <c t="s" r="A456" s="6">
-        <v>13</v>
-      </c>
-      <c r="B456" s="7">
-        <v>1582</v>
-      </c>
-      <c t="s" r="C456" s="7">
-        <v>14</v>
-      </c>
+      <c r="A456" s="6"/>
+      <c r="B456" s="7"/>
+      <c r="C456" s="7"/>
       <c r="D456" s="7"/>
-      <c t="s" r="E456" s="7">
-        <v>442</v>
-      </c>
-      <c r="F456" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G456" s="8">
-        <v>170</v>
-      </c>
-      <c t="s" r="H456" s="8">
-        <v>88</v>
-      </c>
-      <c t="s" r="I456" s="7">
-        <v>122</v>
-      </c>
-      <c t="s" r="J456" s="7">
-        <v>90</v>
-      </c>
+      <c r="E456" s="7"/>
+      <c r="F456" s="7"/>
+      <c r="G456" s="8"/>
+      <c r="H456" s="8"/>
+      <c r="I456" s="7"/>
+      <c r="J456" s="7"/>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
       <c r="M456" s="7"/>
@@ -15631,29 +15642,29 @@
         <v>13</v>
       </c>
       <c r="B457" s="7">
-        <v>51</v>
+        <v>1582</v>
       </c>
       <c t="s" r="C457" s="7">
         <v>14</v>
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F457" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G457" s="8">
+        <v>170</v>
+      </c>
+      <c t="s" r="H457" s="8">
         <v>88</v>
       </c>
-      <c t="s" r="H457" s="8">
-        <v>443</v>
-      </c>
       <c t="s" r="I457" s="7">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>444</v>
+        <v>90</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
@@ -15664,128 +15675,128 @@
         <v>13</v>
       </c>
       <c r="B458" s="7">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c t="s" r="C458" s="7">
         <v>14</v>
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G458" s="8">
-        <v>443</v>
+        <v>88</v>
       </c>
       <c t="s" r="H458" s="8">
-        <v>88</v>
+        <v>446</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>228</v>
+        <v>154</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>142</v>
+        <v>447</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
       <c r="M458" s="7"/>
     </row>
     <row r="459" ht="14.25" customHeight="1">
-      <c r="A459" s="6"/>
-      <c r="B459" s="7"/>
-      <c r="C459" s="7"/>
+      <c t="s" r="A459" s="6">
+        <v>13</v>
+      </c>
+      <c r="B459" s="7">
+        <v>52</v>
+      </c>
+      <c t="s" r="C459" s="7">
+        <v>14</v>
+      </c>
       <c r="D459" s="7"/>
-      <c r="E459" s="7"/>
-      <c r="F459" s="7"/>
-      <c r="G459" s="8"/>
-      <c r="H459" s="8"/>
-      <c r="I459" s="7"/>
-      <c r="J459" s="7"/>
+      <c t="s" r="E459" s="7">
+        <v>445</v>
+      </c>
+      <c r="F459" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G459" s="8">
+        <v>446</v>
+      </c>
+      <c t="s" r="H459" s="8">
+        <v>88</v>
+      </c>
+      <c t="s" r="I459" s="7">
+        <v>228</v>
+      </c>
+      <c t="s" r="J459" s="7">
+        <v>142</v>
+      </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
       <c r="M459" s="7"/>
     </row>
     <row r="460" ht="15" customHeight="1">
-      <c t="s" r="A460" s="6">
-        <v>13</v>
-      </c>
-      <c r="B460" s="7">
-        <v>5061</v>
-      </c>
-      <c t="s" r="C460" s="7">
-        <v>14</v>
-      </c>
+      <c r="A460" s="6"/>
+      <c r="B460" s="7"/>
+      <c r="C460" s="7"/>
       <c r="D460" s="7"/>
-      <c t="s" r="E460" s="7">
-        <v>445</v>
-      </c>
-      <c r="F460" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G460" s="8">
-        <v>446</v>
-      </c>
-      <c t="s" r="H460" s="8">
-        <v>170</v>
-      </c>
-      <c t="s" r="I460" s="7">
-        <v>294</v>
-      </c>
-      <c t="s" r="J460" s="7">
-        <v>378</v>
-      </c>
+      <c r="E460" s="7"/>
+      <c r="F460" s="7"/>
+      <c r="G460" s="8"/>
+      <c r="H460" s="8"/>
+      <c r="I460" s="7"/>
+      <c r="J460" s="7"/>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
-      <c t="s" r="M460" s="7">
-        <v>19</v>
-      </c>
+      <c r="M460" s="7"/>
     </row>
     <row r="461" ht="14.25" customHeight="1">
-      <c r="A461" s="6"/>
-      <c r="B461" s="7"/>
-      <c r="C461" s="7"/>
+      <c t="s" r="A461" s="6">
+        <v>13</v>
+      </c>
+      <c r="B461" s="7">
+        <v>5061</v>
+      </c>
+      <c t="s" r="C461" s="7">
+        <v>14</v>
+      </c>
       <c r="D461" s="7"/>
-      <c r="E461" s="7"/>
-      <c r="F461" s="7"/>
-      <c r="G461" s="8"/>
-      <c r="H461" s="8"/>
-      <c r="I461" s="7"/>
-      <c r="J461" s="7"/>
+      <c t="s" r="E461" s="7">
+        <v>448</v>
+      </c>
+      <c r="F461" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G461" s="8">
+        <v>449</v>
+      </c>
+      <c t="s" r="H461" s="8">
+        <v>170</v>
+      </c>
+      <c t="s" r="I461" s="7">
+        <v>294</v>
+      </c>
+      <c t="s" r="J461" s="7">
+        <v>379</v>
+      </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
-      <c r="M461" s="7"/>
+      <c t="s" r="M461" s="7">
+        <v>19</v>
+      </c>
     </row>
     <row r="462" ht="14.25" customHeight="1">
-      <c t="s" r="A462" s="6">
-        <v>13</v>
-      </c>
-      <c r="B462" s="7">
-        <v>1580</v>
-      </c>
-      <c t="s" r="C462" s="7">
-        <v>14</v>
-      </c>
+      <c r="A462" s="6"/>
+      <c r="B462" s="7"/>
+      <c r="C462" s="7"/>
       <c r="D462" s="7"/>
-      <c t="s" r="E462" s="7">
-        <v>447</v>
-      </c>
-      <c r="F462" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G462" s="8">
-        <v>170</v>
-      </c>
-      <c t="s" r="H462" s="8">
-        <v>88</v>
-      </c>
-      <c t="s" r="I462" s="7">
-        <v>100</v>
-      </c>
-      <c t="s" r="J462" s="7">
-        <v>135</v>
-      </c>
+      <c r="E462" s="7"/>
+      <c r="F462" s="7"/>
+      <c r="G462" s="8"/>
+      <c r="H462" s="8"/>
+      <c r="I462" s="7"/>
+      <c r="J462" s="7"/>
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
       <c r="M462" s="7"/>
@@ -15795,29 +15806,29 @@
         <v>13</v>
       </c>
       <c r="B463" s="7">
-        <v>55</v>
+        <v>1580</v>
       </c>
       <c t="s" r="C463" s="7">
         <v>14</v>
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G463" s="8">
+        <v>170</v>
+      </c>
+      <c t="s" r="H463" s="8">
         <v>88</v>
       </c>
-      <c t="s" r="H463" s="8">
-        <v>448</v>
-      </c>
       <c t="s" r="I463" s="7">
-        <v>211</v>
+        <v>100</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>444</v>
+        <v>135</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -15828,161 +15839,161 @@
         <v>13</v>
       </c>
       <c r="B464" s="7">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c t="s" r="C464" s="7">
         <v>14</v>
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>448</v>
+        <v>88</v>
       </c>
       <c t="s" r="H464" s="8">
-        <v>88</v>
+        <v>451</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>39</v>
+        <v>447</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
       <c r="M464" s="7"/>
     </row>
     <row r="465" ht="15" customHeight="1">
-      <c r="A465" s="6"/>
-      <c r="B465" s="7"/>
-      <c r="C465" s="7"/>
+      <c t="s" r="A465" s="6">
+        <v>13</v>
+      </c>
+      <c r="B465" s="7">
+        <v>56</v>
+      </c>
+      <c t="s" r="C465" s="7">
+        <v>14</v>
+      </c>
       <c r="D465" s="7"/>
-      <c r="E465" s="7"/>
-      <c r="F465" s="7"/>
-      <c r="G465" s="8"/>
-      <c r="H465" s="8"/>
-      <c r="I465" s="7"/>
-      <c r="J465" s="7"/>
+      <c t="s" r="E465" s="7">
+        <v>450</v>
+      </c>
+      <c r="F465" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G465" s="8">
+        <v>451</v>
+      </c>
+      <c t="s" r="H465" s="8">
+        <v>88</v>
+      </c>
+      <c t="s" r="I465" s="7">
+        <v>228</v>
+      </c>
+      <c t="s" r="J465" s="7">
+        <v>39</v>
+      </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
       <c r="M465" s="7"/>
     </row>
     <row r="466" ht="14.25" customHeight="1">
-      <c t="s" r="A466" s="6">
-        <v>13</v>
-      </c>
-      <c r="B466" s="7">
-        <v>2831</v>
-      </c>
-      <c t="s" r="C466" s="7">
-        <v>230</v>
-      </c>
+      <c r="A466" s="6"/>
+      <c r="B466" s="7"/>
+      <c r="C466" s="7"/>
       <c r="D466" s="7"/>
-      <c t="s" r="E466" s="7">
-        <v>449</v>
-      </c>
-      <c r="F466" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G466" s="8">
-        <v>88</v>
-      </c>
-      <c t="s" r="H466" s="8">
-        <v>450</v>
-      </c>
-      <c t="s" r="I466" s="7">
-        <v>85</v>
-      </c>
-      <c t="s" r="J466" s="7">
-        <v>451</v>
-      </c>
+      <c r="E466" s="7"/>
+      <c r="F466" s="7"/>
+      <c r="G466" s="8"/>
+      <c r="H466" s="8"/>
+      <c r="I466" s="7"/>
+      <c r="J466" s="7"/>
       <c r="K466" s="7"/>
       <c r="L466" s="7"/>
-      <c t="s" r="M466" s="7">
-        <v>168</v>
-      </c>
+      <c r="M466" s="7"/>
     </row>
     <row r="467" ht="14.25" customHeight="1">
       <c t="s" r="A467" s="6">
         <v>13</v>
       </c>
       <c r="B467" s="7">
-        <v>2832</v>
+        <v>2831</v>
       </c>
       <c t="s" r="C467" s="7">
         <v>230</v>
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G467" s="8">
-        <v>450</v>
+        <v>88</v>
       </c>
       <c t="s" r="H467" s="8">
-        <v>88</v>
+        <v>453</v>
       </c>
       <c t="s" r="I467" s="7">
-        <v>211</v>
+        <v>85</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>330</v>
+        <v>454</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
-      <c r="M467" s="7"/>
+      <c t="s" r="M467" s="7">
+        <v>168</v>
+      </c>
     </row>
     <row r="468" ht="14.25" customHeight="1">
-      <c r="A468" s="6"/>
-      <c r="B468" s="7"/>
-      <c r="C468" s="7"/>
+      <c t="s" r="A468" s="6">
+        <v>13</v>
+      </c>
+      <c r="B468" s="7">
+        <v>2832</v>
+      </c>
+      <c t="s" r="C468" s="7">
+        <v>230</v>
+      </c>
       <c r="D468" s="7"/>
-      <c r="E468" s="7"/>
-      <c r="F468" s="7"/>
-      <c r="G468" s="8"/>
-      <c r="H468" s="8"/>
-      <c r="I468" s="7"/>
-      <c r="J468" s="7"/>
+      <c t="s" r="E468" s="7">
+        <v>452</v>
+      </c>
+      <c r="F468" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G468" s="8">
+        <v>453</v>
+      </c>
+      <c t="s" r="H468" s="8">
+        <v>88</v>
+      </c>
+      <c t="s" r="I468" s="7">
+        <v>211</v>
+      </c>
+      <c t="s" r="J468" s="7">
+        <v>331</v>
+      </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
       <c r="M468" s="7"/>
     </row>
     <row r="469" ht="14.25" customHeight="1">
-      <c t="s" r="A469" s="6">
-        <v>13</v>
-      </c>
-      <c r="B469" s="7">
-        <v>83</v>
-      </c>
-      <c t="s" r="C469" s="7">
-        <v>14</v>
-      </c>
+      <c r="A469" s="6"/>
+      <c r="B469" s="7"/>
+      <c r="C469" s="7"/>
       <c r="D469" s="7"/>
-      <c t="s" r="E469" s="7">
-        <v>452</v>
-      </c>
-      <c r="F469" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="G469" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H469" s="8">
-        <v>453</v>
-      </c>
-      <c t="s" r="I469" s="7">
-        <v>289</v>
-      </c>
-      <c t="s" r="J469" s="7">
-        <v>139</v>
-      </c>
+      <c r="E469" s="7"/>
+      <c r="F469" s="7"/>
+      <c r="G469" s="8"/>
+      <c r="H469" s="8"/>
+      <c r="I469" s="7"/>
+      <c r="J469" s="7"/>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
       <c r="M469" s="7"/>
@@ -15992,76 +16003,109 @@
         <v>13</v>
       </c>
       <c r="B470" s="7">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c t="s" r="C470" s="7">
         <v>14</v>
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G470" s="8">
-        <v>453</v>
+        <v>16</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>16</v>
+        <v>456</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>454</v>
+        <v>288</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>268</v>
+        <v>139</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
       <c r="M470" s="7"/>
     </row>
-    <row r="471" ht="15.75" customHeight="1">
-      <c t="s" r="A471" s="9">
+    <row r="471" ht="14.25" customHeight="1">
+      <c t="s" r="A471" s="6">
+        <v>13</v>
+      </c>
+      <c r="B471" s="7">
+        <v>84</v>
+      </c>
+      <c t="s" r="C471" s="7">
+        <v>14</v>
+      </c>
+      <c r="D471" s="7"/>
+      <c t="s" r="E471" s="7">
         <v>455</v>
       </c>
-      <c r="B471" s="9"/>
-      <c r="C471" s="9"/>
-      <c r="D471" s="9"/>
-      <c r="E471" s="9"/>
-      <c r="F471" s="9"/>
-      <c r="G471" s="9"/>
-      <c r="H471" s="9"/>
-      <c r="I471" s="9"/>
-      <c r="J471" s="9"/>
-      <c r="K471" s="9"/>
-      <c r="L471" s="9"/>
-      <c r="M471" s="9"/>
-      <c r="N471" s="9"/>
-      <c r="O471" s="9"/>
-    </row>
-    <row r="472" ht="65.25" customHeight="1"/>
-    <row r="473" ht="16.5" customHeight="1">
-      <c t="s" r="A473" s="10">
+      <c r="F471" s="7">
+        <v>330</v>
+      </c>
+      <c t="s" r="G471" s="8">
         <v>456</v>
       </c>
-      <c r="B473" s="10"/>
-      <c r="C473" s="10"/>
-      <c r="D473" s="10"/>
-      <c r="E473" s="10"/>
-      <c r="F473" s="10"/>
-      <c r="G473" s="10"/>
-      <c r="H473" s="10"/>
-      <c r="I473" s="10"/>
-      <c r="J473" s="10"/>
-      <c r="K473" s="10"/>
-      <c t="s" r="L473" s="11">
+      <c t="s" r="H471" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I471" s="7">
         <v>457</v>
       </c>
-      <c r="M473" s="11"/>
-      <c r="N473" s="11"/>
+      <c t="s" r="J471" s="7">
+        <v>267</v>
+      </c>
+      <c r="K471" s="7"/>
+      <c r="L471" s="7"/>
+      <c r="M471" s="7"/>
+    </row>
+    <row r="472" ht="15.75" customHeight="1">
+      <c t="s" r="A472" s="9">
+        <v>458</v>
+      </c>
+      <c r="B472" s="9"/>
+      <c r="C472" s="9"/>
+      <c r="D472" s="9"/>
+      <c r="E472" s="9"/>
+      <c r="F472" s="9"/>
+      <c r="G472" s="9"/>
+      <c r="H472" s="9"/>
+      <c r="I472" s="9"/>
+      <c r="J472" s="9"/>
+      <c r="K472" s="9"/>
+      <c r="L472" s="9"/>
+      <c r="M472" s="9"/>
+      <c r="N472" s="9"/>
+      <c r="O472" s="9"/>
+    </row>
+    <row r="473" ht="65.25" customHeight="1"/>
+    <row r="474" ht="16.5" customHeight="1">
+      <c t="s" r="A474" s="10">
+        <v>459</v>
+      </c>
+      <c r="B474" s="10"/>
+      <c r="C474" s="10"/>
+      <c r="D474" s="10"/>
+      <c r="E474" s="10"/>
+      <c r="F474" s="10"/>
+      <c r="G474" s="10"/>
+      <c r="H474" s="10"/>
+      <c r="I474" s="10"/>
+      <c r="J474" s="10"/>
+      <c r="K474" s="10"/>
+      <c t="s" r="L474" s="11">
+        <v>460</v>
+      </c>
+      <c r="M474" s="11"/>
+      <c r="N474" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="936">
+  <mergeCells count="938">
     <mergeCell ref="D1:O1"/>
     <mergeCell ref="D2:O2"/>
     <mergeCell ref="D3:O4"/>
@@ -16995,9 +17039,11 @@
     <mergeCell ref="K469:L469"/>
     <mergeCell ref="C470:D470"/>
     <mergeCell ref="K470:L470"/>
-    <mergeCell ref="A471:O471"/>
-    <mergeCell ref="A473:K473"/>
-    <mergeCell ref="L473:N473"/>
+    <mergeCell ref="C471:D471"/>
+    <mergeCell ref="K471:L471"/>
+    <mergeCell ref="A472:O472"/>
+    <mergeCell ref="A474:K474"/>
+    <mergeCell ref="L474:N474"/>
   </mergeCells>
   <pageMargins left="0.196666672825813" right="0.219999998807907" top="0.280000001192093" bottom="0.230000004172325" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape"/>

--- a/Data/FlightPlan/FPL_19AUG26.xlsx
+++ b/Data/FlightPlan/FPL_19AUG26.xlsx
@@ -398,6 +398,9 @@
     <t>11:20</t>
   </si>
   <si>
+    <t>12:32</t>
+  </si>
+  <si>
     <t>20:35</t>
   </si>
   <si>
@@ -428,6 +431,9 @@
     <t>11:55</t>
   </si>
   <si>
+    <t>12:21</t>
+  </si>
+  <si>
     <t>12:25</t>
   </si>
   <si>
@@ -860,9 +866,6 @@
     <t>12:35</t>
   </si>
   <si>
-    <t>12:34</t>
-  </si>
-  <si>
     <t>VN-A630</t>
   </si>
   <si>
@@ -875,6 +878,9 @@
     <t>12:15</t>
   </si>
   <si>
+    <t>12:36</t>
+  </si>
+  <si>
     <t>UIH</t>
   </si>
   <si>
@@ -956,7 +962,7 @@
     <t>07:01</t>
   </si>
   <si>
-    <t>12:31</t>
+    <t>12:51</t>
   </si>
   <si>
     <t>20:55</t>
@@ -1085,15 +1091,15 @@
     <t>14:15</t>
   </si>
   <si>
+    <t>14:56</t>
+  </si>
+  <si>
     <t>PER</t>
   </si>
   <si>
     <t>VN-A647</t>
   </si>
   <si>
-    <t>12:51</t>
-  </si>
-  <si>
     <t>22:45</t>
   </si>
   <si>
@@ -1178,9 +1184,6 @@
     <t>07:37</t>
   </si>
   <si>
-    <t>12:32</t>
-  </si>
-  <si>
     <t>VN-A663</t>
   </si>
   <si>
@@ -1304,6 +1307,9 @@
     <t>10:45</t>
   </si>
   <si>
+    <t>12:39</t>
+  </si>
+  <si>
     <t>18:30</t>
   </si>
   <si>
@@ -1352,7 +1358,7 @@
     <t>VN-A685</t>
   </si>
   <si>
-    <t>15:07</t>
+    <t>15:29</t>
   </si>
   <si>
     <t>01:05</t>
@@ -1364,6 +1370,9 @@
     <t>08:57</t>
   </si>
   <si>
+    <t>12:18</t>
+  </si>
+  <si>
     <t>VN-A689</t>
   </si>
   <si>
@@ -1394,7 +1403,7 @@
     <t>10:38</t>
   </si>
   <si>
-    <t>12:38</t>
+    <t>13:03</t>
   </si>
   <si>
     <t>P</t>
@@ -1412,6 +1421,9 @@
     <t>SYD</t>
   </si>
   <si>
+    <t>16:27</t>
+  </si>
+  <si>
     <t>VN-A814</t>
   </si>
   <si>
@@ -1457,7 +1469,7 @@
     <t>Total Record(s): 386</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 19, 2026 11:05</t>
+    <t xml:space="preserve">Generated on  Aug 19, 2026 11:34</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3785,7 +3797,9 @@
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
-      <c r="M65" s="7"/>
+      <c t="s" r="M65" s="7">
+        <v>129</v>
+      </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c t="s" r="A66" s="6">
@@ -3811,10 +3825,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3847,7 +3861,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3859,7 +3873,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J68" s="7">
         <v>125</v>
@@ -3867,7 +3881,7 @@
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -3882,7 +3896,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3894,7 +3908,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J69" s="7">
         <v>55</v>
@@ -3902,7 +3916,7 @@
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -3917,7 +3931,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3926,17 +3940,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
-      <c r="M70" s="7"/>
+      <c t="s" r="M70" s="7">
+        <v>140</v>
+      </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
       <c t="s" r="A71" s="6">
@@ -3950,22 +3966,22 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="H71" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3983,7 +3999,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3992,13 +4008,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -4016,13 +4032,13 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c t="s" r="H73" s="8">
         <v>16</v>
@@ -4031,7 +4047,7 @@
         <v>86</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -4064,7 +4080,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4073,7 +4089,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H75" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="I75" s="7">
         <v>124</v>
@@ -4084,7 +4100,7 @@
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4099,19 +4115,19 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G76" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="H76" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J76" s="7">
         <v>53</v>
@@ -4119,7 +4135,7 @@
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4134,7 +4150,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4149,12 +4165,12 @@
         <v>92</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4169,7 +4185,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4181,7 +4197,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="J78" s="7">
         <v>117</v>
@@ -4206,7 +4222,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4215,10 +4231,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J79" s="7">
         <v>49</v>
@@ -4239,13 +4255,13 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="H80" s="8">
         <v>16</v>
@@ -4272,7 +4288,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4284,10 +4300,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4305,7 +4321,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4317,10 +4333,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4353,7 +4369,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4388,7 +4404,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4408,7 +4424,7 @@
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4423,7 +4439,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4435,10 +4451,10 @@
         <v>123</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4456,7 +4472,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4489,7 +4505,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4501,10 +4517,10 @@
         <v>123</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4522,7 +4538,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4534,10 +4550,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4570,7 +4586,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4585,12 +4601,12 @@
         <v>63</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4605,7 +4621,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4617,10 +4633,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4638,7 +4654,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4671,7 +4687,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4686,7 +4702,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4704,7 +4720,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4716,10 +4732,10 @@
         <v>48</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4752,7 +4768,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4764,7 +4780,7 @@
         <v>45</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J97" s="7">
         <v>56</v>
@@ -4772,7 +4788,7 @@
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -4787,7 +4803,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4799,7 +4815,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J98" s="7">
         <v>84</v>
@@ -4820,7 +4836,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4832,10 +4848,10 @@
         <v>115</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4853,7 +4869,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4865,7 +4881,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="J100" s="7">
         <v>69</v>
@@ -4886,7 +4902,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4895,13 +4911,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4919,13 +4935,13 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>30</v>
@@ -4934,7 +4950,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4967,7 +4983,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4976,18 +4992,18 @@
         <v>91</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5002,13 +5018,13 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>91</v>
@@ -5017,12 +5033,12 @@
         <v>110</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -5037,7 +5053,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5057,7 +5073,7 @@
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c t="s" r="M106" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -5072,7 +5088,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5084,10 +5100,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -5105,7 +5121,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5117,10 +5133,10 @@
         <v>45</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5138,7 +5154,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5186,7 +5202,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5201,12 +5217,12 @@
         <v>94</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5221,7 +5237,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5233,10 +5249,10 @@
         <v>79</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5254,7 +5270,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5266,10 +5282,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5287,7 +5303,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5299,7 +5315,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c t="s" r="J114" s="7">
         <v>76</v>
@@ -5335,7 +5351,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5344,10 +5360,10 @@
         <v>48</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>77</v>
@@ -5370,27 +5386,27 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>123</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5405,7 +5421,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5414,10 +5430,10 @@
         <v>123</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>35</v>
@@ -5438,22 +5454,22 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5471,7 +5487,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5480,13 +5496,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H120" s="8">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5504,22 +5520,22 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c t="s" r="H121" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5552,7 +5568,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5561,18 +5577,18 @@
         <v>72</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5587,22 +5603,22 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5620,7 +5636,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5629,13 +5645,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="I125" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5653,22 +5669,22 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5701,7 +5717,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5721,7 +5737,7 @@
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5736,7 +5752,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5745,7 +5761,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="I129" s="7">
         <v>68</v>
@@ -5769,22 +5785,22 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5802,7 +5818,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5811,13 +5827,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5835,19 +5851,19 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G132" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="H132" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>25</v>
@@ -5883,7 +5899,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5895,7 +5911,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>77</v>
@@ -5903,7 +5919,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -5918,7 +5934,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5930,7 +5946,7 @@
         <v>119</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>46</v>
@@ -5951,7 +5967,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5960,13 +5976,13 @@
         <v>119</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5984,13 +6000,13 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="H137" s="8">
         <v>119</v>
@@ -5999,7 +6015,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -6017,7 +6033,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6029,10 +6045,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -6065,7 +6081,7 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
@@ -6080,12 +6096,12 @@
         <v>27</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6100,7 +6116,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6109,18 +6125,18 @@
         <v>115</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="I141" s="7">
         <v>57</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6135,22 +6151,22 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>115</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -6168,7 +6184,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6180,10 +6196,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6201,7 +6217,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6213,10 +6229,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6234,7 +6250,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6243,13 +6259,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="I145" s="7">
         <v>99</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6267,22 +6283,22 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6315,7 +6331,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6327,15 +6343,15 @@
         <v>65</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6350,7 +6366,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6383,7 +6399,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6392,13 +6408,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6416,22 +6432,22 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6460,11 +6476,11 @@
         <v>2986</v>
       </c>
       <c t="s" r="C153" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6476,10 +6492,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6493,11 +6509,11 @@
         <v>2986</v>
       </c>
       <c t="s" r="C154" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6506,13 +6522,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6526,26 +6542,26 @@
         <v>2987</v>
       </c>
       <c t="s" r="C155" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6578,7 +6594,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6590,15 +6606,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6613,7 +6629,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6625,15 +6641,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6648,7 +6664,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6663,7 +6679,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6681,7 +6697,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6693,10 +6709,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6714,7 +6730,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6729,7 +6745,7 @@
         <v>106</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6758,11 +6774,11 @@
         <v>5069</v>
       </c>
       <c t="s" r="C163" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6771,18 +6787,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I163" s="7">
+        <v>261</v>
+      </c>
+      <c t="s" r="J163" s="7">
         <v>259</v>
-      </c>
-      <c t="s" r="J163" s="7">
-        <v>257</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -6793,26 +6809,26 @@
         <v>7620</v>
       </c>
       <c t="s" r="C164" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -6826,11 +6842,11 @@
         <v>7620</v>
       </c>
       <c t="s" r="C165" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6839,13 +6855,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6859,26 +6875,26 @@
         <v>7621</v>
       </c>
       <c t="s" r="C166" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6911,7 +6927,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6920,13 +6936,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6946,22 +6962,22 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6979,7 +6995,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6988,13 +7004,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="I170" s="7">
         <v>60</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -7012,22 +7028,22 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -7056,17 +7072,17 @@
         <v>7707</v>
       </c>
       <c t="s" r="C173" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>30</v>
@@ -7075,12 +7091,12 @@
         <v>128</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7091,11 +7107,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C174" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7104,10 +7120,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>120</v>
@@ -7132,22 +7148,22 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G175" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H175" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7180,7 +7196,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7192,10 +7208,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7215,7 +7231,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7227,10 +7243,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7248,7 +7264,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7260,7 +7276,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>36</v>
@@ -7281,7 +7297,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7293,7 +7309,7 @@
         <v>29</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>110</v>
@@ -7329,7 +7345,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7341,15 +7357,15 @@
         <v>123</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7364,7 +7380,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7373,18 +7389,18 @@
         <v>123</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>283</v>
+        <v>103</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7399,13 +7415,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>123</v>
@@ -7432,7 +7448,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7447,7 +7463,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7480,7 +7496,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7492,15 +7508,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -7515,7 +7531,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7530,12 +7546,12 @@
         <v>77</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7550,7 +7566,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7562,14 +7578,16 @@
         <v>30</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
-      <c r="M189" s="7"/>
+      <c t="s" r="M189" s="7">
+        <v>289</v>
+      </c>
     </row>
     <row r="190" ht="15" customHeight="1">
       <c t="s" r="A190" s="6">
@@ -7583,7 +7601,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7592,13 +7610,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7616,29 +7634,29 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="K191" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -7653,7 +7671,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7662,20 +7680,20 @@
         <v>30</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c t="s" r="K192" s="7">
         <v>69</v>
       </c>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -7690,29 +7708,29 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="K193" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -7742,7 +7760,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7751,10 +7769,10 @@
         <v>91</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J195" s="7">
         <v>46</v>
@@ -7775,13 +7793,13 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>91</v>
@@ -7790,7 +7808,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7808,7 +7826,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7817,13 +7835,13 @@
         <v>91</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="I197" s="7">
         <v>69</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7841,22 +7859,22 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>91</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7889,7 +7907,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7898,18 +7916,18 @@
         <v>48</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -7924,19 +7942,19 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="J201" s="7">
         <v>85</v>
@@ -7957,22 +7975,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I202" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7990,19 +8008,19 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>55</v>
@@ -8038,7 +8056,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8047,13 +8065,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8073,13 +8091,13 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>16</v>
@@ -8088,12 +8106,12 @@
         <v>66</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8108,7 +8126,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8120,10 +8138,10 @@
         <v>79</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8141,7 +8159,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8153,10 +8171,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8174,7 +8192,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8183,13 +8201,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="I209" s="7">
         <v>120</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -8207,22 +8225,22 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -8255,7 +8273,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8267,15 +8285,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8290,7 +8308,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8299,7 +8317,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="I213" s="7">
         <v>40</v>
@@ -8325,13 +8343,13 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="H214" s="8">
         <v>16</v>
@@ -8345,7 +8363,7 @@
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -8360,7 +8378,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8393,7 +8411,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8405,7 +8423,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>120</v>
@@ -8426,7 +8444,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8438,10 +8456,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8459,7 +8477,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8471,10 +8489,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8507,7 +8525,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8519,7 +8537,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>118</v>
@@ -8540,7 +8558,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8552,10 +8570,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8573,7 +8591,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8585,7 +8603,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>69</v>
@@ -8606,7 +8624,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8618,10 +8636,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8639,7 +8657,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8654,7 +8672,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8687,7 +8705,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8696,18 +8714,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="I226" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -8722,22 +8740,22 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8755,7 +8773,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8764,13 +8782,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8788,22 +8806,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8836,7 +8854,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8848,7 +8866,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>63</v>
@@ -8856,7 +8874,7 @@
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -8871,7 +8889,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8880,13 +8898,13 @@
         <v>91</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8904,19 +8922,19 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>36</v>
@@ -8937,7 +8955,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8946,10 +8964,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>106</v>
@@ -8970,19 +8988,19 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>52</v>
@@ -9018,7 +9036,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9038,7 +9056,7 @@
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9053,7 +9071,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9068,12 +9086,12 @@
         <v>82</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9088,7 +9106,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9103,10 +9121,10 @@
         <v>80</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="K239" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
@@ -9125,7 +9143,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9140,7 +9158,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9158,7 +9176,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9170,10 +9188,10 @@
         <v>45</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -9191,7 +9209,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9203,10 +9221,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9224,7 +9242,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9236,10 +9254,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9257,7 +9275,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9269,10 +9287,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9305,7 +9323,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9317,15 +9335,15 @@
         <v>91</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9340,7 +9358,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9360,7 +9378,7 @@
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9375,7 +9393,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9384,18 +9402,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="I248" s="7">
         <v>82</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9410,29 +9428,29 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>59</v>
       </c>
       <c t="s" r="K249" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9447,7 +9465,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9456,13 +9474,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9480,13 +9498,13 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>30</v>
@@ -9495,7 +9513,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9513,7 +9531,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9546,7 +9564,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9558,10 +9576,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9594,7 +9612,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9603,7 +9621,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="I255" s="7">
         <v>74</v>
@@ -9614,7 +9632,7 @@
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -9629,19 +9647,19 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>31</v>
@@ -9649,7 +9667,7 @@
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -9664,7 +9682,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9673,10 +9691,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>84</v>
@@ -9684,7 +9702,7 @@
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9699,13 +9717,13 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>16</v>
@@ -9714,7 +9732,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9732,7 +9750,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9741,13 +9759,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9765,13 +9783,13 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>16</v>
@@ -9780,7 +9798,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9798,7 +9816,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9810,10 +9828,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9846,7 +9864,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9861,12 +9879,12 @@
         <v>27</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -9881,7 +9899,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9893,10 +9911,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9916,7 +9934,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9925,13 +9943,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9949,19 +9967,19 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>121</v>
@@ -9982,19 +10000,19 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>98</v>
@@ -10015,22 +10033,22 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>48</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -10063,7 +10081,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10072,17 +10090,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="I270" s="7">
         <v>80</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
-      <c r="M270" s="7"/>
+      <c t="s" r="M270" s="7">
+        <v>360</v>
+      </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
       <c t="s" r="A271" s="6">
@@ -10096,13 +10116,13 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>16</v>
@@ -10129,7 +10149,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10138,13 +10158,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>106</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10177,7 +10197,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10186,18 +10206,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10212,27 +10232,27 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>91</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>360</v>
+        <v>317</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10247,7 +10267,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10280,7 +10300,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10292,10 +10312,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10328,7 +10348,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10340,15 +10360,15 @@
         <v>91</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10363,7 +10383,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10375,15 +10395,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10398,7 +10418,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10410,7 +10430,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>21</v>
@@ -10431,7 +10451,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10440,13 +10460,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10464,19 +10484,19 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>98</v>
@@ -10497,7 +10517,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10509,10 +10529,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10545,7 +10565,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10554,10 +10574,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>53</v>
@@ -10565,7 +10585,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -10580,13 +10600,13 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>30</v>
@@ -10595,12 +10615,12 @@
         <v>92</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -10615,7 +10635,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -10627,10 +10647,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10648,7 +10668,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -10660,10 +10680,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10681,7 +10701,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10690,13 +10710,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10714,13 +10734,13 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>30</v>
@@ -10729,7 +10749,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10762,7 +10782,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10777,12 +10797,12 @@
         <v>124</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -10797,7 +10817,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10817,90 +10837,94 @@
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
-      <c t="s" r="A295" s="6">
-        <v>13</v>
-      </c>
-      <c r="B295" s="7">
-        <v>133</v>
-      </c>
-      <c t="s" r="C295" s="7">
-        <v>14</v>
-      </c>
+      <c r="A295" s="6"/>
+      <c r="B295" s="7"/>
+      <c r="C295" s="7"/>
       <c r="D295" s="7"/>
-      <c t="s" r="E295" s="7">
-        <v>372</v>
-      </c>
-      <c r="F295" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G295" s="8">
-        <v>30</v>
-      </c>
-      <c t="s" r="H295" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I295" s="7">
-        <v>128</v>
-      </c>
-      <c t="s" r="J295" s="7">
-        <v>84</v>
-      </c>
+      <c r="E295" s="7"/>
+      <c r="F295" s="7"/>
+      <c r="G295" s="8"/>
+      <c r="H295" s="8"/>
+      <c r="I295" s="7"/>
+      <c r="J295" s="7"/>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c r="M295" s="7"/>
     </row>
     <row r="296" ht="14.25" customHeight="1">
-      <c r="A296" s="6"/>
-      <c r="B296" s="7"/>
-      <c r="C296" s="7"/>
+      <c t="s" r="A296" s="6">
+        <v>13</v>
+      </c>
+      <c r="B296" s="7">
+        <v>156</v>
+      </c>
+      <c t="s" r="C296" s="7">
+        <v>14</v>
+      </c>
       <c r="D296" s="7"/>
-      <c r="E296" s="7"/>
-      <c r="F296" s="7"/>
-      <c r="G296" s="8"/>
-      <c r="H296" s="8"/>
-      <c r="I296" s="7"/>
-      <c r="J296" s="7"/>
+      <c t="s" r="E296" s="7">
+        <v>376</v>
+      </c>
+      <c r="F296" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G296" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H296" s="8">
+        <v>30</v>
+      </c>
+      <c t="s" r="I296" s="7">
+        <v>377</v>
+      </c>
+      <c t="s" r="J296" s="7">
+        <v>185</v>
+      </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
-      <c r="M296" s="7"/>
+      <c t="s" r="M296" s="7">
+        <v>378</v>
+      </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
       <c t="s" r="A297" s="6">
         <v>13</v>
       </c>
       <c r="B297" s="7">
-        <v>156</v>
+        <v>133</v>
       </c>
       <c t="s" r="C297" s="7">
         <v>14</v>
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>375</v>
+        <v>128</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>183</v>
-      </c>
-      <c r="K297" s="7"/>
+        <v>84</v>
+      </c>
+      <c t="s" r="K297" s="7">
+        <v>232</v>
+      </c>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>376</v>
+        <v>19</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -10930,7 +10954,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -10939,18 +10963,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c t="s" r="I299" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -10965,22 +10989,22 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10998,7 +11022,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
@@ -11007,10 +11031,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>85</v>
@@ -11031,22 +11055,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11079,7 +11103,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11091,15 +11115,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11114,7 +11138,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11126,15 +11150,15 @@
         <v>123</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11149,7 +11173,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11158,13 +11182,13 @@
         <v>123</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11182,22 +11206,22 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>123</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11215,7 +11239,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11227,7 +11251,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>86</v>
@@ -11263,7 +11287,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11272,18 +11296,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11298,13 +11322,13 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>30</v>
@@ -11333,7 +11357,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11342,13 +11366,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c t="s" r="I312" s="7">
         <v>117</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11366,13 +11390,13 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>30</v>
@@ -11381,7 +11405,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11399,7 +11423,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11411,10 +11435,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11447,7 +11471,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11456,18 +11480,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11482,19 +11506,19 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="H317" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>55</v>
@@ -11502,7 +11526,7 @@
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11517,7 +11541,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11532,12 +11556,12 @@
         <v>57</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>389</v>
+        <v>129</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -11552,7 +11576,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11567,7 +11591,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11585,7 +11609,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11594,13 +11618,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11618,13 +11642,13 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>30</v>
@@ -11633,7 +11657,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11651,7 +11675,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11666,7 +11690,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11684,7 +11708,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11696,7 +11720,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>25</v>
@@ -11732,7 +11756,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11741,10 +11765,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>125</v>
@@ -11767,27 +11791,27 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -11802,7 +11826,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11811,13 +11835,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11835,19 +11859,19 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>19</v>
@@ -11868,7 +11892,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11880,7 +11904,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>49</v>
@@ -11901,7 +11925,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11913,10 +11937,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11934,7 +11958,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11943,10 +11967,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>31</v>
@@ -11982,7 +12006,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11994,7 +12018,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>57</v>
@@ -12002,7 +12026,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12017,7 +12041,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -12029,10 +12053,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12050,7 +12074,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12062,10 +12086,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12083,7 +12107,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12116,7 +12140,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12128,7 +12152,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>71</v>
@@ -12164,7 +12188,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -12176,10 +12200,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -12197,7 +12221,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12209,10 +12233,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12245,7 +12269,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12254,18 +12278,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12280,19 +12304,19 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>126</v>
@@ -12300,7 +12324,7 @@
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12315,7 +12339,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12324,18 +12348,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12350,19 +12374,19 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>19</v>
@@ -12383,7 +12407,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12392,13 +12416,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12416,22 +12440,22 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G347" s="8">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c t="s" r="H347" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12449,7 +12473,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12458,10 +12482,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>99</v>
@@ -12482,22 +12506,22 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12530,7 +12554,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12539,10 +12563,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>74</v>
@@ -12550,7 +12574,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12565,27 +12589,27 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -12600,7 +12624,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12609,18 +12633,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="I353" s="7">
         <v>82</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -12635,13 +12659,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>16</v>
@@ -12650,7 +12674,7 @@
         <v>80</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12668,7 +12692,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12680,10 +12704,10 @@
         <v>45</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12701,7 +12725,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12713,10 +12737,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12734,7 +12758,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12743,7 +12767,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>22</v>
@@ -12767,22 +12791,22 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12815,7 +12839,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12827,15 +12851,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -12850,7 +12874,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12883,7 +12907,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12895,10 +12919,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12916,7 +12940,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12949,7 +12973,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12964,7 +12988,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12982,7 +13006,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12991,10 +13015,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>110</v>
@@ -13030,7 +13054,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13039,18 +13063,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13065,19 +13089,19 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>80</v>
@@ -13085,7 +13109,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13100,7 +13124,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13109,10 +13133,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>118</v>
@@ -13133,22 +13157,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13166,7 +13190,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -13175,13 +13199,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -13199,22 +13223,22 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13232,7 +13256,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -13241,13 +13265,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13265,22 +13289,22 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13313,7 +13337,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13322,7 +13346,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I376" s="7">
         <v>126</v>
@@ -13333,7 +13357,7 @@
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13348,22 +13372,22 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13381,7 +13405,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13390,13 +13414,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13414,13 +13438,13 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>30</v>
@@ -13447,7 +13471,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -13456,13 +13480,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="I380" s="7">
         <v>61</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13480,22 +13504,22 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13528,7 +13552,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13540,15 +13564,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -13563,7 +13587,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13575,7 +13599,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>57</v>
@@ -13583,7 +13607,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -13598,7 +13622,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13613,14 +13637,14 @@
         <v>56</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="K385" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>303</v>
+        <v>160</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -13635,7 +13659,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13650,14 +13674,14 @@
         <v>43</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="K386" s="7">
         <v>84</v>
       </c>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -13672,7 +13696,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13684,10 +13708,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13720,7 +13744,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13729,18 +13753,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -13755,27 +13779,27 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -13790,7 +13814,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13799,18 +13823,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -13825,26 +13849,28 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>117</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
-      <c r="M392" s="7"/>
+      <c t="s" r="M392" s="7">
+        <v>432</v>
+      </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
       <c t="s" r="A393" s="6">
@@ -13858,7 +13884,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -13870,7 +13896,7 @@
         <v>79</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>35</v>
@@ -13891,7 +13917,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13903,10 +13929,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13924,7 +13950,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13936,7 +13962,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>86</v>
@@ -13972,7 +13998,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13984,15 +14010,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14007,7 +14033,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -14027,7 +14053,7 @@
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14042,7 +14068,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -14057,7 +14083,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14075,7 +14101,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -14087,7 +14113,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>49</v>
@@ -14108,7 +14134,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -14117,7 +14143,7 @@
         <v>30</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I401" s="7">
         <v>69</v>
@@ -14141,22 +14167,22 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -14189,7 +14215,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -14201,7 +14227,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>18</v>
@@ -14209,7 +14235,7 @@
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -14224,7 +14250,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -14236,10 +14262,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14257,7 +14283,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14266,13 +14292,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14290,13 +14316,13 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>30</v>
@@ -14305,7 +14331,7 @@
         <v>97</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14323,7 +14349,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14332,10 +14358,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>50</v>
@@ -14356,22 +14382,22 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14404,7 +14430,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14413,10 +14439,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>53</v>
@@ -14424,7 +14450,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14439,13 +14465,13 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>16</v>
@@ -14459,7 +14485,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -14474,7 +14500,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -14483,7 +14509,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>84</v>
@@ -14507,13 +14533,13 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>16</v>
@@ -14522,7 +14548,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14540,22 +14566,22 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
+        <v>442</v>
+      </c>
+      <c r="F415" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G415" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H415" s="8">
+        <v>445</v>
+      </c>
+      <c t="s" r="I415" s="7">
+        <v>437</v>
+      </c>
+      <c t="s" r="J415" s="7">
         <v>440</v>
-      </c>
-      <c r="F415" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G415" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H415" s="8">
-        <v>443</v>
-      </c>
-      <c t="s" r="I415" s="7">
-        <v>435</v>
-      </c>
-      <c t="s" r="J415" s="7">
-        <v>438</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14573,22 +14599,22 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14621,7 +14647,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14633,15 +14659,15 @@
         <v>30</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -14656,7 +14682,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14665,20 +14691,20 @@
         <v>30</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="K419" s="7">
         <v>56</v>
       </c>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -14693,29 +14719,29 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c t="s" r="K420" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -14730,7 +14756,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -14742,10 +14768,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14778,7 +14804,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -14787,7 +14813,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="I423" s="7">
         <v>27</v>
@@ -14798,7 +14824,7 @@
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -14813,13 +14839,13 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>16</v>
@@ -14828,12 +14854,12 @@
         <v>40</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -14848,7 +14874,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -14860,7 +14886,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>83</v>
@@ -14868,7 +14894,7 @@
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>102</v>
+        <v>453</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -14883,7 +14909,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -14916,7 +14942,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -14928,10 +14954,10 @@
         <v>91</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14949,7 +14975,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -14982,7 +15008,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -14994,7 +15020,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c t="s" r="J429" s="7">
         <v>25</v>
@@ -15030,7 +15056,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -15039,13 +15065,13 @@
         <v>30</v>
       </c>
       <c t="s" r="H431" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -15063,22 +15089,22 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -15111,7 +15137,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -15123,7 +15149,7 @@
         <v>30</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="J434" s="7">
         <v>43</v>
@@ -15131,7 +15157,7 @@
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
       <c t="s" r="M434" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1">
@@ -15146,7 +15172,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -15155,10 +15181,10 @@
         <v>30</v>
       </c>
       <c t="s" r="H435" s="8">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>22</v>
@@ -15179,13 +15205,13 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="H436" s="8">
         <v>30</v>
@@ -15194,7 +15220,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -15212,7 +15238,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -15224,7 +15250,7 @@
         <v>48</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c t="s" r="J437" s="7">
         <v>124</v>
@@ -15260,7 +15286,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -15272,15 +15298,15 @@
         <v>79</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -15295,7 +15321,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -15307,14 +15333,16 @@
         <v>16</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c t="s" r="J440" s="7">
         <v>43</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
-      <c r="M440" s="7"/>
+      <c t="s" r="M440" s="7">
+        <v>325</v>
+      </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
       <c t="s" r="A441" s="6">
@@ -15328,7 +15356,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -15337,13 +15365,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -15376,7 +15404,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F443" s="7">
         <v>320</v>
@@ -15385,18 +15413,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -15411,27 +15439,27 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F444" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -15446,27 +15474,27 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F445" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c t="s" r="H445" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="I445" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
       <c t="s" r="M445" s="7">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="446" ht="14.25" customHeight="1">
@@ -15481,13 +15509,13 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G446" s="8">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="H446" s="8">
         <v>16</v>
@@ -15501,7 +15529,7 @@
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -15516,7 +15544,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
@@ -15528,7 +15556,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c t="s" r="J447" s="7">
         <v>21</v>
@@ -15549,7 +15577,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
@@ -15561,10 +15589,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
@@ -15582,7 +15610,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
@@ -15591,13 +15619,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -15615,22 +15643,22 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c t="s" r="H450" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15659,11 +15687,11 @@
         <v>34</v>
       </c>
       <c t="s" r="C452" s="7">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
@@ -15672,18 +15700,18 @@
         <v>91</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c t="s" r="I452" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
       <c t="s" r="M452" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="453" ht="14.25" customHeight="1">
@@ -15713,19 +15741,19 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c t="s" r="H454" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>96</v>
@@ -15733,7 +15761,7 @@
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>105</v>
+        <v>470</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
@@ -15748,7 +15776,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
@@ -15757,13 +15785,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15796,13 +15824,13 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F457" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G457" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H457" s="8">
         <v>91</v>
@@ -15816,7 +15844,7 @@
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
       <c t="s" r="M457" s="7">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="458" ht="14.25" customHeight="1">
@@ -15831,7 +15859,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
@@ -15840,13 +15868,13 @@
         <v>91</v>
       </c>
       <c t="s" r="H458" s="8">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -15864,22 +15892,22 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G459" s="8">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c t="s" r="H459" s="8">
         <v>91</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
@@ -15912,22 +15940,22 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F461" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c t="s" r="H461" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15962,13 +15990,13 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G463" s="8">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="H463" s="8">
         <v>91</v>
@@ -15977,7 +16005,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
@@ -15995,7 +16023,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
@@ -16004,13 +16032,13 @@
         <v>91</v>
       </c>
       <c t="s" r="H464" s="8">
+        <v>478</v>
+      </c>
+      <c t="s" r="I464" s="7">
+        <v>225</v>
+      </c>
+      <c t="s" r="J464" s="7">
         <v>474</v>
-      </c>
-      <c t="s" r="I464" s="7">
-        <v>223</v>
-      </c>
-      <c t="s" r="J464" s="7">
-        <v>470</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -16028,19 +16056,19 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F465" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G465" s="8">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c t="s" r="H465" s="8">
         <v>91</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c t="s" r="J465" s="7">
         <v>40</v>
@@ -16072,11 +16100,11 @@
         <v>2831</v>
       </c>
       <c t="s" r="C467" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
@@ -16085,18 +16113,18 @@
         <v>91</v>
       </c>
       <c t="s" r="H467" s="8">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c t="s" r="I467" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
       <c t="s" r="M467" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="468" ht="14.25" customHeight="1">
@@ -16107,26 +16135,26 @@
         <v>2832</v>
       </c>
       <c t="s" r="C468" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="F468" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G468" s="8">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c t="s" r="H468" s="8">
         <v>91</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
@@ -16159,7 +16187,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
@@ -16168,18 +16196,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -16194,22 +16222,22 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F471" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G471" s="8">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c t="s" r="H471" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c t="s" r="J471" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
@@ -16217,7 +16245,7 @@
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c t="s" r="A472" s="9">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B472" s="9"/>
       <c r="C472" s="9"/>
@@ -16237,7 +16265,7 @@
     <row r="473" ht="65.25" customHeight="1"/>
     <row r="474" ht="16.5" customHeight="1">
       <c t="s" r="A474" s="10">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B474" s="10"/>
       <c r="C474" s="10"/>
@@ -16250,7 +16278,7 @@
       <c r="J474" s="10"/>
       <c r="K474" s="10"/>
       <c t="s" r="L474" s="11">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="M474" s="11"/>
       <c r="N474" s="11"/>

--- a/Data/FlightPlan/FPL_19AUG26.xlsx
+++ b/Data/FlightPlan/FPL_19AUG26.xlsx
@@ -686,6 +686,9 @@
     <t>22:28</t>
   </si>
   <si>
+    <t>01:06</t>
+  </si>
+  <si>
     <t>VN-A542</t>
   </si>
   <si>
@@ -755,7 +758,7 @@
     <t>22:40</t>
   </si>
   <si>
-    <t>02:25</t>
+    <t>10:31</t>
   </si>
   <si>
     <t>02:30</t>
@@ -1193,6 +1196,9 @@
     <t>00:20</t>
   </si>
   <si>
+    <t>00:22</t>
+  </si>
+  <si>
     <t>VN-A635</t>
   </si>
   <si>
@@ -1211,9 +1217,6 @@
     <t>20:10</t>
   </si>
   <si>
-    <t>23:09</t>
-  </si>
-  <si>
     <t>VN-A637</t>
   </si>
   <si>
@@ -1352,6 +1355,9 @@
     <t>00:50</t>
   </si>
   <si>
+    <t>00:57</t>
+  </si>
+  <si>
     <t>VN-A644</t>
   </si>
   <si>
@@ -1439,6 +1445,9 @@
     <t>00:55</t>
   </si>
   <si>
+    <t>01:08</t>
+  </si>
+  <si>
     <t>VN-A651</t>
   </si>
   <si>
@@ -1535,60 +1544,60 @@
     <t>20:49</t>
   </si>
   <si>
+    <t>VN-A666</t>
+  </si>
+  <si>
+    <t>10:19</t>
+  </si>
+  <si>
+    <t>14:47</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>17:52</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>19:38</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>07:52</t>
+  </si>
+  <si>
+    <t>10:13</t>
+  </si>
+  <si>
+    <t>14:31</t>
+  </si>
+  <si>
+    <t>TBB</t>
+  </si>
+  <si>
+    <t>16:59</t>
+  </si>
+  <si>
+    <t>19:24</t>
+  </si>
+  <si>
+    <t>22:24</t>
+  </si>
+  <si>
     <t>FSZ</t>
   </si>
   <si>
     <t>02:40</t>
   </si>
   <si>
-    <t>VN-A666</t>
-  </si>
-  <si>
-    <t>10:19</t>
-  </si>
-  <si>
-    <t>14:47</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>17:52</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>19:38</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>07:52</t>
-  </si>
-  <si>
-    <t>10:13</t>
-  </si>
-  <si>
-    <t>14:31</t>
-  </si>
-  <si>
-    <t>TBB</t>
-  </si>
-  <si>
-    <t>16:59</t>
-  </si>
-  <si>
-    <t>19:24</t>
-  </si>
-  <si>
-    <t>22:24</t>
-  </si>
-  <si>
     <t>VN-A669</t>
   </si>
   <si>
@@ -1721,6 +1730,9 @@
     <t>20:56</t>
   </si>
   <si>
+    <t>01:27</t>
+  </si>
+  <si>
     <t>02:10</t>
   </si>
   <si>
@@ -1745,6 +1757,9 @@
     <t>MNL</t>
   </si>
   <si>
+    <t>02:18</t>
+  </si>
+  <si>
     <t>03:00</t>
   </si>
   <si>
@@ -1889,7 +1904,7 @@
     <t>Total Record(s): 386</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 19, 2026 22:40</t>
+    <t xml:space="preserve">Generated on  Aug 19, 2026 23:12</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -5478,7 +5493,9 @@
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
-      <c r="M102" s="7"/>
+      <c t="s" r="M102" s="7">
+        <v>225</v>
+      </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
       <c r="A103" s="6"/>
@@ -5507,7 +5524,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5519,7 +5536,7 @@
         <v>181</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>175</v>
@@ -5527,7 +5544,7 @@
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5542,7 +5559,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5557,12 +5574,12 @@
         <v>135</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -5577,7 +5594,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5586,7 +5603,7 @@
         <v>107</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="I106" s="7">
         <v>70</v>
@@ -5597,7 +5614,7 @@
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c t="s" r="M106" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -5612,27 +5629,27 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>107</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5647,7 +5664,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5659,7 +5676,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>196</v>
@@ -5682,7 +5699,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5702,7 +5719,7 @@
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5717,7 +5734,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5729,10 +5746,10 @@
         <v>53</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5765,7 +5782,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5780,12 +5797,12 @@
         <v>110</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5800,7 +5817,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5820,7 +5837,7 @@
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5835,7 +5852,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5850,7 +5867,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5870,7 +5887,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5879,20 +5896,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="K115" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5907,29 +5924,29 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="K116" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5959,7 +5976,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5994,7 +6011,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -6006,7 +6023,7 @@
         <v>146</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J119" s="7">
         <v>164</v>
@@ -6014,7 +6031,7 @@
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -6029,7 +6046,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -6041,7 +6058,7 @@
         <v>181</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>37</v>
@@ -6049,7 +6066,7 @@
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -6064,7 +6081,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -6076,7 +6093,7 @@
         <v>93</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>61</v>
@@ -6112,7 +6129,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -6124,15 +6141,15 @@
         <v>181</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -6147,7 +6164,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -6167,7 +6184,7 @@
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -6182,7 +6199,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -6202,7 +6219,7 @@
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -6217,7 +6234,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -6229,15 +6246,15 @@
         <v>32</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6252,7 +6269,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -6300,7 +6317,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6320,7 +6337,7 @@
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6335,7 +6352,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6344,7 +6361,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="I130" s="7">
         <v>75</v>
@@ -6355,7 +6372,7 @@
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6370,13 +6387,13 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>16</v>
@@ -6385,7 +6402,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -6405,7 +6422,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6414,10 +6431,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>171</v>
@@ -6425,7 +6442,7 @@
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -6440,19 +6457,19 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J133" s="7">
         <v>26</v>
@@ -6460,7 +6477,7 @@
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -6490,7 +6507,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6502,7 +6519,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J135" s="7">
         <v>85</v>
@@ -6510,7 +6527,7 @@
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -6525,7 +6542,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6534,10 +6551,10 @@
         <v>107</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>50</v>
@@ -6545,7 +6562,7 @@
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
       <c t="s" r="M136" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
@@ -6560,27 +6577,27 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6595,19 +6612,19 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>188</v>
@@ -6615,7 +6632,7 @@
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6630,13 +6647,13 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>107</v>
@@ -6680,7 +6697,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6695,12 +6712,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6715,7 +6732,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6724,18 +6741,18 @@
         <v>139</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="I142" s="7">
         <v>63</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6750,19 +6767,19 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="H143" s="8">
         <v>139</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J143" s="7">
         <v>219</v>
@@ -6770,7 +6787,7 @@
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6785,7 +6802,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6820,7 +6837,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6832,17 +6849,17 @@
         <v>107</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>187</v>
       </c>
       <c t="s" r="K145" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6857,7 +6874,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6872,14 +6889,14 @@
         <v>198</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="K146" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6909,7 +6926,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6921,15 +6938,15 @@
         <v>72</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6944,7 +6961,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6959,12 +6976,12 @@
         <v>99</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6979,7 +6996,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6988,18 +7005,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -7014,22 +7031,22 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -7058,11 +7075,11 @@
         <v>2986</v>
       </c>
       <c t="s" r="C153" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -7074,7 +7091,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>116</v>
@@ -7082,7 +7099,7 @@
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -7093,11 +7110,11 @@
         <v>2986</v>
       </c>
       <c t="s" r="C154" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -7106,18 +7123,18 @@
         <v>32</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7128,23 +7145,23 @@
         <v>2987</v>
       </c>
       <c t="s" r="C155" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>202</v>
@@ -7180,7 +7197,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -7192,15 +7209,15 @@
         <v>32</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -7215,7 +7232,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -7230,12 +7247,12 @@
         <v>158</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -7250,7 +7267,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -7265,12 +7282,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -7285,7 +7302,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7297,7 +7314,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>187</v>
@@ -7305,7 +7322,7 @@
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7320,7 +7337,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -7335,7 +7352,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -7364,11 +7381,11 @@
         <v>5069</v>
       </c>
       <c t="s" r="C163" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -7380,15 +7397,15 @@
         <v>181</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -7399,11 +7416,11 @@
         <v>7620</v>
       </c>
       <c t="s" r="C164" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7415,15 +7432,15 @@
         <v>32</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7434,11 +7451,11 @@
         <v>7620</v>
       </c>
       <c t="s" r="C165" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7447,18 +7464,18 @@
         <v>32</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7469,26 +7486,26 @@
         <v>7621</v>
       </c>
       <c t="s" r="C166" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -7521,7 +7538,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7530,13 +7547,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I168" s="7">
         <v>158</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -7556,13 +7573,13 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>16</v>
@@ -7576,7 +7593,7 @@
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7591,7 +7608,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7600,7 +7617,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="I170" s="7">
         <v>66</v>
@@ -7611,7 +7628,7 @@
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7626,13 +7643,13 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>16</v>
@@ -7641,7 +7658,7 @@
         <v>212</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -7670,17 +7687,17 @@
         <v>7707</v>
       </c>
       <c t="s" r="C173" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="H173" s="8">
         <v>32</v>
@@ -7689,12 +7706,12 @@
         <v>151</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7705,11 +7722,11 @@
         <v>7707</v>
       </c>
       <c t="s" r="C174" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7721,10 +7738,10 @@
         <v>181</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="K174" s="7">
         <v>129</v>
@@ -7746,7 +7763,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7761,7 +7778,7 @@
         <v>211</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7794,7 +7811,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7806,10 +7823,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7829,7 +7846,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7841,7 +7858,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>116</v>
@@ -7849,7 +7866,7 @@
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7864,7 +7881,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7876,7 +7893,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>39</v>
@@ -7886,7 +7903,7 @@
       </c>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7901,7 +7918,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7913,7 +7930,7 @@
         <v>31</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>135</v>
@@ -7949,7 +7966,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7961,15 +7978,15 @@
         <v>146</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7984,7 +8001,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7993,13 +8010,13 @@
         <v>146</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -8019,13 +8036,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>146</v>
@@ -8039,7 +8056,7 @@
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -8054,7 +8071,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -8066,15 +8083,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -8089,7 +8106,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -8109,7 +8126,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8139,7 +8156,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -8151,7 +8168,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>82</v>
@@ -8159,7 +8176,7 @@
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -8174,7 +8191,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8209,7 +8226,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -8221,15 +8238,15 @@
         <v>32</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8244,7 +8261,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8253,18 +8270,18 @@
         <v>32</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8279,29 +8296,29 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="K192" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8316,7 +8333,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8325,20 +8342,20 @@
         <v>32</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="K193" s="7">
         <v>38</v>
       </c>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -8353,19 +8370,19 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J194" s="7">
         <v>170</v>
@@ -8375,7 +8392,7 @@
       </c>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -8405,7 +8422,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8414,10 +8431,10 @@
         <v>107</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>50</v>
@@ -8440,13 +8457,13 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>107</v>
@@ -8455,12 +8472,12 @@
         <v>51</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8475,7 +8492,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8484,7 +8501,7 @@
         <v>107</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="I198" s="7">
         <v>38</v>
@@ -8495,7 +8512,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8510,27 +8527,27 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>107</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8560,7 +8577,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8572,15 +8589,15 @@
         <v>181</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8595,7 +8612,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8604,10 +8621,10 @@
         <v>181</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>100</v>
@@ -8615,7 +8632,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8630,13 +8647,13 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>181</v>
@@ -8645,12 +8662,12 @@
         <v>22</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8680,7 +8697,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8692,10 +8709,10 @@
         <v>186</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8715,7 +8732,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8730,7 +8747,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8750,7 +8767,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8762,7 +8779,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>206</v>
@@ -8785,7 +8802,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8800,12 +8817,12 @@
         <v>89</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8820,7 +8837,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8829,18 +8846,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8855,19 +8872,19 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>188</v>
@@ -8875,7 +8892,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8890,7 +8907,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8902,7 +8919,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>92</v>
@@ -8910,7 +8927,7 @@
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8925,7 +8942,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8937,14 +8954,16 @@
         <v>16</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
-      <c r="M212" s="7"/>
+      <c t="s" r="M212" s="7">
+        <v>395</v>
+      </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
       <c r="A213" s="6"/>
@@ -8973,7 +8992,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8985,15 +9004,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
       <c t="s" r="M214" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1">
@@ -9008,7 +9027,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -9017,7 +9036,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="I215" s="7">
         <v>44</v>
@@ -9043,13 +9062,13 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="H216" s="8">
         <v>16</v>
@@ -9063,7 +9082,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -9078,7 +9097,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -9098,7 +9117,7 @@
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -9113,7 +9132,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -9125,10 +9144,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -9148,7 +9167,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -9160,15 +9179,15 @@
         <v>146</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -9183,7 +9202,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9195,7 +9214,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>91</v>
@@ -9203,7 +9222,7 @@
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>400</v>
+        <v>130</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9233,7 +9252,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -9245,7 +9264,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>142</v>
@@ -9268,7 +9287,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9280,7 +9299,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>221</v>
@@ -9288,7 +9307,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -9303,7 +9322,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -9315,7 +9334,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>38</v>
@@ -9338,7 +9357,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9353,14 +9372,14 @@
         <v>168</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c t="s" r="K225" s="7">
         <v>188</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9375,7 +9394,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9390,14 +9409,14 @@
         <v>40</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c t="s" r="K226" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9427,7 +9446,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9436,18 +9455,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="I228" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9462,27 +9481,27 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9497,7 +9516,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9506,18 +9525,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="I230" s="7">
         <v>116</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9532,13 +9551,13 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>16</v>
@@ -9552,7 +9571,7 @@
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9582,7 +9601,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9594,7 +9613,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>70</v>
@@ -9602,7 +9621,7 @@
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9617,7 +9636,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9626,18 +9645,18 @@
         <v>107</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9652,13 +9671,13 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>16</v>
@@ -9672,7 +9691,7 @@
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9687,7 +9706,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9696,7 +9715,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c t="s" r="I236" s="7">
         <v>190</v>
@@ -9707,7 +9726,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9722,19 +9741,19 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>58</v>
@@ -9770,7 +9789,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9790,7 +9809,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9805,7 +9824,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9820,7 +9839,7 @@
         <v>97</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9840,7 +9859,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9855,14 +9874,14 @@
         <v>88</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="K241" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9877,7 +9896,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9897,7 +9916,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9912,7 +9931,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9924,15 +9943,15 @@
         <v>49</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9947,7 +9966,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9959,7 +9978,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>190</v>
@@ -9967,7 +9986,7 @@
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9982,7 +10001,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -10002,7 +10021,7 @@
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -10017,7 +10036,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -10029,10 +10048,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -10065,7 +10084,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -10077,15 +10096,15 @@
         <v>107</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10100,7 +10119,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -10120,7 +10139,7 @@
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -10135,7 +10154,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -10150,7 +10169,7 @@
         <v>97</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -10170,7 +10189,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -10188,7 +10207,7 @@
         <v>65</v>
       </c>
       <c t="s" r="K251" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
@@ -10207,7 +10226,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -10219,17 +10238,17 @@
         <v>181</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="K252" s="7">
         <v>75</v>
       </c>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -10244,7 +10263,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -10259,14 +10278,14 @@
         <v>52</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c t="s" r="K253" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10281,7 +10300,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -10303,7 +10322,7 @@
       </c>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10318,7 +10337,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -10330,17 +10349,17 @@
         <v>32</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="K255" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10370,7 +10389,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10379,7 +10398,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="I257" s="7">
         <v>95</v>
@@ -10390,7 +10409,7 @@
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10405,19 +10424,19 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>33</v>
@@ -10425,7 +10444,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10440,7 +10459,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -10449,7 +10468,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>177</v>
@@ -10460,7 +10479,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10475,13 +10494,13 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>16</v>
@@ -10490,12 +10509,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10510,7 +10529,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10519,7 +10538,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>221</v>
@@ -10530,7 +10549,7 @@
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10545,13 +10564,13 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>16</v>
@@ -10560,12 +10579,12 @@
         <v>25</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10580,7 +10599,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10592,14 +10611,16 @@
         <v>32</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
-      <c r="M263" s="7"/>
+      <c t="s" r="M263" s="7">
+        <v>448</v>
+      </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
       <c r="A264" s="6"/>
@@ -10628,7 +10649,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10643,12 +10664,12 @@
         <v>29</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10663,7 +10684,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10675,10 +10696,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -10698,7 +10719,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -10710,15 +10731,15 @@
         <v>181</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10733,7 +10754,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10742,18 +10763,18 @@
         <v>181</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="I268" s="7">
         <v>114</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10768,27 +10789,27 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>181</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10803,7 +10824,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10815,15 +10836,15 @@
         <v>53</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10853,7 +10874,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10862,18 +10883,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10888,13 +10909,13 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>16</v>
@@ -10908,7 +10929,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10923,7 +10944,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10932,13 +10953,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>130</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -10971,7 +10992,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10980,13 +11001,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="I276" s="7">
         <v>82</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -11006,27 +11027,27 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>107</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -11056,7 +11077,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -11068,15 +11089,15 @@
         <v>107</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -11091,7 +11112,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -11103,15 +11124,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -11126,7 +11147,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -11138,7 +11159,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>21</v>
@@ -11146,7 +11167,7 @@
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -11161,7 +11182,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -11170,18 +11191,18 @@
         <v>32</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -11196,13 +11217,13 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>32</v>
@@ -11211,12 +11232,12 @@
         <v>117</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -11231,7 +11252,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -11243,15 +11264,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -11281,7 +11302,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -11293,7 +11314,7 @@
         <v>181</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>59</v>
@@ -11301,7 +11322,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11316,7 +11337,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -11331,12 +11352,12 @@
         <v>108</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11351,7 +11372,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
@@ -11366,12 +11387,12 @@
         <v>219</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11386,7 +11407,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F289" s="7">
         <v>320</v>
@@ -11398,17 +11419,17 @@
         <v>32</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c t="s" r="K289" s="7">
         <v>54</v>
       </c>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -11423,7 +11444,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -11435,14 +11456,16 @@
         <v>16</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
-      <c r="M290" s="7"/>
+      <c t="s" r="M290" s="7">
+        <v>478</v>
+      </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
       <c r="A291" s="6"/>
@@ -11471,7 +11494,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11486,12 +11509,12 @@
         <v>147</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11506,7 +11529,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11526,7 +11549,7 @@
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11556,7 +11579,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -11568,15 +11591,15 @@
         <v>32</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11591,7 +11614,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11609,11 +11632,11 @@
         <v>99</v>
       </c>
       <c t="s" r="K296" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11628,7 +11651,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -11637,10 +11660,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>187</v>
@@ -11648,7 +11671,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11663,13 +11686,13 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>16</v>
@@ -11698,7 +11721,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -11713,12 +11736,12 @@
         <v>190</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11733,7 +11756,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11745,15 +11768,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11783,7 +11806,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -11792,13 +11815,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c t="s" r="I302" s="7">
         <v>59</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11818,13 +11841,13 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>16</v>
@@ -11853,7 +11876,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11862,10 +11885,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>100</v>
@@ -11873,7 +11896,7 @@
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11888,19 +11911,19 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>168</v>
@@ -11908,7 +11931,7 @@
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11938,7 +11961,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11950,15 +11973,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11973,7 +11996,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11985,7 +12008,7 @@
         <v>146</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>178</v>
@@ -11993,7 +12016,7 @@
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -12008,7 +12031,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -12017,7 +12040,7 @@
         <v>146</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="I309" s="7">
         <v>164</v>
@@ -12043,22 +12066,22 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>146</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -12078,7 +12101,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -12090,7 +12113,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>101</v>
@@ -12130,7 +12153,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -12139,7 +12162,7 @@
         <v>32</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>82</v>
@@ -12150,7 +12173,7 @@
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -12165,13 +12188,13 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>32</v>
@@ -12200,7 +12223,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -12209,18 +12232,18 @@
         <v>32</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c t="s" r="I315" s="7">
         <v>141</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12235,13 +12258,13 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>32</v>
@@ -12250,12 +12273,12 @@
         <v>100</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12270,7 +12293,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -12279,13 +12302,13 @@
         <v>32</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -12305,13 +12328,13 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>32</v>
@@ -12320,7 +12343,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -12353,7 +12376,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -12362,18 +12385,18 @@
         <v>32</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12388,19 +12411,19 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>61</v>
@@ -12408,7 +12431,7 @@
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -12423,7 +12446,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -12432,18 +12455,18 @@
         <v>32</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>63</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12458,13 +12481,13 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>32</v>
@@ -12478,7 +12501,7 @@
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12493,7 +12516,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -12508,12 +12531,12 @@
         <v>196</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12528,7 +12551,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12540,15 +12563,15 @@
         <v>32</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12563,7 +12586,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12575,17 +12598,17 @@
         <v>107</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="K326" s="7">
         <v>191</v>
       </c>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12600,7 +12623,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12622,7 +12645,7 @@
       </c>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12652,7 +12675,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -12664,7 +12687,7 @@
         <v>181</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>148</v>
@@ -12687,7 +12710,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -12702,12 +12725,12 @@
         <v>214</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12722,7 +12745,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12742,7 +12765,7 @@
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12757,7 +12780,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -12769,7 +12792,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>19</v>
@@ -12792,7 +12815,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12804,7 +12827,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>54</v>
@@ -12827,7 +12850,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -12847,90 +12870,92 @@
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
-      <c t="s" r="A335" s="6">
-        <v>42</v>
-      </c>
-      <c r="B335" s="7">
-        <v>1980</v>
-      </c>
-      <c t="s" r="C335" s="7">
-        <v>14</v>
-      </c>
+      <c r="A335" s="6"/>
+      <c r="B335" s="7"/>
+      <c r="C335" s="7"/>
       <c r="D335" s="7"/>
-      <c t="s" r="E335" s="7">
-        <v>503</v>
-      </c>
-      <c r="F335" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G335" s="8">
-        <v>32</v>
-      </c>
-      <c t="s" r="H335" s="8">
-        <v>508</v>
-      </c>
-      <c t="s" r="I335" s="7">
-        <v>509</v>
-      </c>
-      <c t="s" r="J335" s="7">
-        <v>33</v>
-      </c>
+      <c r="E335" s="7"/>
+      <c r="F335" s="7"/>
+      <c r="G335" s="8"/>
+      <c r="H335" s="8"/>
+      <c r="I335" s="7"/>
+      <c r="J335" s="7"/>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c r="M335" s="7"/>
     </row>
     <row r="336" ht="14.25" customHeight="1">
-      <c r="A336" s="6"/>
-      <c r="B336" s="7"/>
-      <c r="C336" s="7"/>
+      <c t="s" r="A336" s="6">
+        <v>13</v>
+      </c>
+      <c r="B336" s="7">
+        <v>127</v>
+      </c>
+      <c t="s" r="C336" s="7">
+        <v>14</v>
+      </c>
       <c r="D336" s="7"/>
-      <c r="E336" s="7"/>
-      <c r="F336" s="7"/>
-      <c r="G336" s="8"/>
-      <c r="H336" s="8"/>
-      <c r="I336" s="7"/>
-      <c r="J336" s="7"/>
+      <c t="s" r="E336" s="7">
+        <v>511</v>
+      </c>
+      <c r="F336" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G336" s="8">
+        <v>32</v>
+      </c>
+      <c t="s" r="H336" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I336" s="7">
+        <v>382</v>
+      </c>
+      <c t="s" r="J336" s="7">
+        <v>63</v>
+      </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
-      <c r="M336" s="7"/>
+      <c t="s" r="M336" s="7">
+        <v>512</v>
+      </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
       <c t="s" r="A337" s="6">
         <v>13</v>
       </c>
       <c r="B337" s="7">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c t="s" r="C337" s="7">
         <v>14</v>
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H337" s="8">
         <v>32</v>
       </c>
-      <c t="s" r="H337" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I337" s="7">
-        <v>381</v>
+        <v>291</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>63</v>
+        <v>236</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12938,171 +12963,171 @@
         <v>13</v>
       </c>
       <c r="B338" s="7">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c t="s" r="C338" s="7">
         <v>14</v>
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>290</v>
+        <v>514</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>235</v>
-      </c>
-      <c r="K338" s="7"/>
+        <v>346</v>
+      </c>
+      <c t="s" r="K338" s="7">
+        <v>21</v>
+      </c>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
-      <c t="s" r="A339" s="6">
-        <v>13</v>
-      </c>
-      <c r="B339" s="7">
-        <v>145</v>
-      </c>
-      <c t="s" r="C339" s="7">
-        <v>14</v>
-      </c>
+      <c r="A339" s="6"/>
+      <c r="B339" s="7"/>
+      <c r="C339" s="7"/>
       <c r="D339" s="7"/>
-      <c t="s" r="E339" s="7">
-        <v>510</v>
-      </c>
-      <c r="F339" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G339" s="8">
+      <c r="E339" s="7"/>
+      <c r="F339" s="7"/>
+      <c r="G339" s="8"/>
+      <c r="H339" s="8"/>
+      <c r="I339" s="7"/>
+      <c r="J339" s="7"/>
+      <c r="K339" s="7"/>
+      <c r="L339" s="7"/>
+      <c r="M339" s="7"/>
+    </row>
+    <row r="340" ht="15" customHeight="1">
+      <c t="s" r="A340" s="6">
+        <v>13</v>
+      </c>
+      <c r="B340" s="7">
+        <v>193</v>
+      </c>
+      <c t="s" r="C340" s="7">
+        <v>14</v>
+      </c>
+      <c r="D340" s="7"/>
+      <c t="s" r="E340" s="7">
+        <v>516</v>
+      </c>
+      <c r="F340" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G340" s="8">
         <v>32</v>
       </c>
-      <c t="s" r="H339" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I339" s="7">
-        <v>513</v>
-      </c>
-      <c t="s" r="J339" s="7">
-        <v>345</v>
-      </c>
-      <c t="s" r="K339" s="7">
-        <v>21</v>
-      </c>
-      <c r="L339" s="7"/>
-      <c t="s" r="M339" s="7">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="340" ht="15" customHeight="1">
-      <c r="A340" s="6"/>
-      <c r="B340" s="7"/>
-      <c r="C340" s="7"/>
-      <c r="D340" s="7"/>
-      <c r="E340" s="7"/>
-      <c r="F340" s="7"/>
-      <c r="G340" s="8"/>
-      <c r="H340" s="8"/>
-      <c r="I340" s="7"/>
-      <c r="J340" s="7"/>
+      <c t="s" r="H340" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I340" s="7">
+        <v>517</v>
+      </c>
+      <c t="s" r="J340" s="7">
+        <v>296</v>
+      </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
-      <c r="M340" s="7"/>
+      <c t="s" r="M340" s="7">
+        <v>518</v>
+      </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
-      <c t="s" r="A341" s="6">
-        <v>13</v>
-      </c>
-      <c r="B341" s="7">
-        <v>193</v>
-      </c>
-      <c t="s" r="C341" s="7">
-        <v>14</v>
-      </c>
+      <c r="A341" s="6"/>
+      <c r="B341" s="7"/>
+      <c r="C341" s="7"/>
       <c r="D341" s="7"/>
-      <c t="s" r="E341" s="7">
-        <v>515</v>
-      </c>
-      <c r="F341" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G341" s="8">
-        <v>32</v>
-      </c>
-      <c t="s" r="H341" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I341" s="7">
-        <v>516</v>
-      </c>
-      <c t="s" r="J341" s="7">
-        <v>295</v>
-      </c>
+      <c r="E341" s="7"/>
+      <c r="F341" s="7"/>
+      <c r="G341" s="8"/>
+      <c r="H341" s="8"/>
+      <c r="I341" s="7"/>
+      <c r="J341" s="7"/>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
-      <c t="s" r="M341" s="7">
-        <v>517</v>
-      </c>
+      <c r="M341" s="7"/>
     </row>
     <row r="342" ht="14.25" customHeight="1">
-      <c r="A342" s="6"/>
-      <c r="B342" s="7"/>
-      <c r="C342" s="7"/>
+      <c t="s" r="A342" s="6">
+        <v>13</v>
+      </c>
+      <c r="B342" s="7">
+        <v>491</v>
+      </c>
+      <c t="s" r="C342" s="7">
+        <v>14</v>
+      </c>
       <c r="D342" s="7"/>
-      <c r="E342" s="7"/>
-      <c r="F342" s="7"/>
-      <c r="G342" s="8"/>
-      <c r="H342" s="8"/>
-      <c r="I342" s="7"/>
-      <c r="J342" s="7"/>
+      <c t="s" r="E342" s="7">
+        <v>519</v>
+      </c>
+      <c r="F342" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G342" s="8">
+        <v>32</v>
+      </c>
+      <c t="s" r="H342" s="8">
+        <v>352</v>
+      </c>
+      <c t="s" r="I342" s="7">
+        <v>239</v>
+      </c>
+      <c t="s" r="J342" s="7">
+        <v>279</v>
+      </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
-      <c r="M342" s="7"/>
+      <c t="s" r="M342" s="7">
+        <v>520</v>
+      </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
       <c t="s" r="A343" s="6">
         <v>13</v>
       </c>
       <c r="B343" s="7">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c t="s" r="C343" s="7">
         <v>14</v>
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
+        <v>352</v>
+      </c>
+      <c t="s" r="H343" s="8">
         <v>32</v>
       </c>
-      <c t="s" r="H343" s="8">
-        <v>351</v>
-      </c>
       <c t="s" r="I343" s="7">
-        <v>238</v>
+        <v>319</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>278</v>
+        <v>149</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -13110,34 +13135,34 @@
         <v>13</v>
       </c>
       <c r="B344" s="7">
-        <v>492</v>
+        <v>1491</v>
       </c>
       <c t="s" r="C344" s="7">
         <v>14</v>
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>351</v>
+        <v>32</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>32</v>
+        <v>352</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>318</v>
+        <v>161</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>149</v>
+        <v>360</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>520</v>
+        <v>256</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13145,34 +13170,34 @@
         <v>13</v>
       </c>
       <c r="B345" s="7">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c t="s" r="C345" s="7">
         <v>14</v>
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
+        <v>352</v>
+      </c>
+      <c t="s" r="H345" s="8">
         <v>32</v>
       </c>
-      <c t="s" r="H345" s="8">
-        <v>351</v>
-      </c>
       <c t="s" r="I345" s="7">
-        <v>161</v>
+        <v>206</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>359</v>
+        <v>19</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>255</v>
+        <v>522</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -13180,34 +13205,34 @@
         <v>13</v>
       </c>
       <c r="B346" s="7">
-        <v>1492</v>
+        <v>419</v>
       </c>
       <c t="s" r="C346" s="7">
         <v>14</v>
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>351</v>
+        <v>32</v>
       </c>
       <c t="s" r="H346" s="8">
-        <v>32</v>
+        <v>523</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13215,34 +13240,34 @@
         <v>13</v>
       </c>
       <c r="B347" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c t="s" r="C347" s="7">
         <v>14</v>
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G347" s="8">
+        <v>523</v>
+      </c>
+      <c t="s" r="H347" s="8">
         <v>32</v>
       </c>
-      <c t="s" r="H347" s="8">
-        <v>522</v>
-      </c>
       <c t="s" r="I347" s="7">
-        <v>167</v>
+        <v>366</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -13250,34 +13275,34 @@
         <v>13</v>
       </c>
       <c r="B348" s="7">
-        <v>420</v>
+        <v>1785</v>
       </c>
       <c t="s" r="C348" s="7">
         <v>14</v>
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>522</v>
+        <v>32</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -13285,64 +13310,64 @@
         <v>13</v>
       </c>
       <c r="B349" s="7">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c t="s" r="C349" s="7">
         <v>14</v>
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
+        <v>181</v>
+      </c>
+      <c t="s" r="H349" s="8">
         <v>32</v>
       </c>
-      <c t="s" r="H349" s="8">
-        <v>181</v>
-      </c>
       <c t="s" r="I349" s="7">
-        <v>378</v>
+        <v>223</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>525</v>
+        <v>448</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
       <c t="s" r="A350" s="6">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B350" s="7">
-        <v>1786</v>
+        <v>1980</v>
       </c>
       <c t="s" r="C350" s="7">
         <v>14</v>
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>181</v>
+        <v>32</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>32</v>
+        <v>527</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>223</v>
+        <v>528</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>212</v>
+        <v>33</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -13375,7 +13400,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -13384,10 +13409,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c t="s" r="J352" s="7">
         <v>95</v>
@@ -13395,7 +13420,7 @@
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -13410,13 +13435,13 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>16</v>
@@ -13425,12 +13450,12 @@
         <v>82</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13445,7 +13470,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -13454,13 +13479,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="I354" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -13480,13 +13505,13 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>16</v>
@@ -13495,7 +13520,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -13515,7 +13540,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -13527,7 +13552,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>182</v>
@@ -13535,7 +13560,7 @@
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c t="s" r="M356" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
@@ -13550,7 +13575,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -13565,12 +13590,12 @@
         <v>221</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13585,7 +13610,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -13605,7 +13630,7 @@
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -13620,7 +13645,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -13632,7 +13657,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>210</v>
@@ -13640,7 +13665,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13670,7 +13695,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13682,15 +13707,15 @@
         <v>32</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13705,7 +13730,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13725,7 +13750,7 @@
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13740,7 +13765,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13760,7 +13785,7 @@
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13775,7 +13800,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13795,7 +13820,7 @@
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13810,7 +13835,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13825,12 +13850,12 @@
         <v>68</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13845,7 +13870,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -13857,7 +13882,7 @@
         <v>93</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c t="s" r="J366" s="7">
         <v>82</v>
@@ -13893,7 +13918,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13902,18 +13927,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13928,19 +13953,19 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>88</v>
@@ -13948,7 +13973,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>540</v>
+        <v>543</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13963,7 +13988,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13972,10 +13997,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J370" s="7">
         <v>142</v>
@@ -13983,7 +14008,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13998,27 +14023,27 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -14033,7 +14058,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -14045,7 +14070,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>199</v>
@@ -14068,7 +14093,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -14080,15 +14105,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>543</v>
+        <v>546</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -14118,7 +14143,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -14138,7 +14163,7 @@
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>545</v>
+        <v>548</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -14153,7 +14178,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -14165,10 +14190,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -14188,7 +14213,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -14197,18 +14222,18 @@
         <v>32</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -14223,13 +14248,13 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>32</v>
@@ -14258,7 +14283,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -14267,7 +14292,7 @@
         <v>32</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c t="s" r="I379" s="7">
         <v>68</v>
@@ -14278,7 +14303,7 @@
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14293,22 +14318,22 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -14341,7 +14366,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -14356,12 +14381,12 @@
         <v>82</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -14376,7 +14401,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -14388,7 +14413,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>63</v>
@@ -14396,7 +14421,7 @@
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>551</v>
+        <v>554</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -14411,7 +14436,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14426,10 +14451,10 @@
         <v>62</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="K384" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
@@ -14448,7 +14473,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14463,7 +14488,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c t="s" r="K385" s="7">
         <v>99</v>
@@ -14485,7 +14510,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -14500,14 +14525,14 @@
         <v>21</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="K386" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14522,7 +14547,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -14534,17 +14559,17 @@
         <v>107</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c t="s" r="K387" s="7">
         <v>94</v>
       </c>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>553</v>
+        <v>556</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14574,7 +14599,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -14583,18 +14608,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>555</v>
+        <v>558</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14609,27 +14634,27 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14644,7 +14669,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14659,12 +14684,12 @@
         <v>59</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14679,7 +14704,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14691,7 +14716,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>141</v>
@@ -14699,7 +14724,7 @@
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14714,7 +14739,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14726,7 +14751,7 @@
         <v>87</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>37</v>
@@ -14734,7 +14759,7 @@
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14749,7 +14774,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -14761,15 +14786,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14784,7 +14809,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -14804,7 +14829,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14834,7 +14859,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -14846,15 +14871,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14869,7 +14894,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -14889,7 +14914,7 @@
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>562</v>
+        <v>565</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14904,7 +14929,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -14919,12 +14944,12 @@
         <v>47</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>563</v>
+        <v>566</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14939,7 +14964,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -14951,7 +14976,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>54</v>
@@ -14959,7 +14984,7 @@
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14974,7 +14999,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
@@ -15009,7 +15034,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -15024,12 +15049,12 @@
         <v>153</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -15059,7 +15084,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -15071,7 +15096,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>18</v>
@@ -15079,7 +15104,7 @@
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -15094,7 +15119,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
@@ -15106,7 +15131,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>114</v>
@@ -15129,7 +15154,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -15138,20 +15163,20 @@
         <v>32</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="I406" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="K406" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>567</v>
+        <v>570</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15166,29 +15191,29 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>101</v>
       </c>
       <c t="s" r="K407" s="7">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -15203,7 +15228,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -15212,7 +15237,7 @@
         <v>32</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="I408" s="7">
         <v>92</v>
@@ -15222,7 +15247,9 @@
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
-      <c r="M408" s="7"/>
+      <c t="s" r="M408" s="7">
+        <v>573</v>
+      </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
       <c t="s" r="A409" s="6">
@@ -15236,22 +15263,22 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -15284,7 +15311,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -15293,10 +15320,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>59</v>
@@ -15304,7 +15331,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -15319,13 +15346,13 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>16</v>
@@ -15339,7 +15366,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>574</v>
+        <v>578</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15354,7 +15381,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
@@ -15363,7 +15390,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="I413" s="7">
         <v>99</v>
@@ -15374,7 +15401,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15389,13 +15416,13 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>16</v>
@@ -15404,12 +15431,12 @@
         <v>39</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15424,7 +15451,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
@@ -15433,17 +15460,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
-      <c r="M415" s="7"/>
+      <c t="s" r="M415" s="7">
+        <v>582</v>
+      </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
       <c t="s" r="A416" s="6">
@@ -15457,22 +15486,22 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="F416" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -15505,7 +15534,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -15517,10 +15546,10 @@
         <v>32</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -15540,7 +15569,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -15549,7 +15578,7 @@
         <v>32</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="I419" s="7">
         <v>175</v>
@@ -15562,7 +15591,7 @@
       </c>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -15577,29 +15606,29 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="H420" s="8">
         <v>32</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c t="s" r="K420" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>582</v>
+        <v>587</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -15614,7 +15643,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -15623,10 +15652,10 @@
         <v>32</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>135</v>
@@ -15662,7 +15691,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
@@ -15671,7 +15700,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="I423" s="7">
         <v>29</v>
@@ -15682,7 +15711,7 @@
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15697,13 +15726,13 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F424" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>16</v>
@@ -15712,12 +15741,12 @@
         <v>44</v>
       </c>
       <c t="s" r="J424" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K424" s="7"/>
       <c r="L424" s="7"/>
       <c t="s" r="M424" s="7">
-        <v>585</v>
+        <v>590</v>
       </c>
     </row>
     <row r="425" ht="15" customHeight="1">
@@ -15732,7 +15761,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -15744,7 +15773,7 @@
         <v>107</v>
       </c>
       <c t="s" r="I425" s="7">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c t="s" r="J425" s="7">
         <v>98</v>
@@ -15752,7 +15781,7 @@
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>586</v>
+        <v>591</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15767,7 +15796,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -15787,7 +15816,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>587</v>
+        <v>592</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15802,7 +15831,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -15837,7 +15866,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -15849,7 +15878,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J428" s="7">
         <v>22</v>
@@ -15872,7 +15901,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -15887,12 +15916,12 @@
         <v>199</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -15907,7 +15936,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -15926,7 +15955,9 @@
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
-      <c r="M430" s="7"/>
+      <c t="s" r="M430" s="7">
+        <v>477</v>
+      </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
       <c r="A431" s="6"/>
@@ -15955,7 +15986,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
@@ -15967,15 +15998,15 @@
         <v>181</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>589</v>
+        <v>594</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15990,7 +16021,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="F433" s="7">
         <v>320</v>
@@ -16002,15 +16033,15 @@
         <v>32</v>
       </c>
       <c t="s" r="I433" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -16040,7 +16071,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -16052,7 +16083,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>47</v>
@@ -16060,7 +16091,7 @@
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -16075,7 +16106,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -16084,10 +16115,10 @@
         <v>32</v>
       </c>
       <c t="s" r="H436" s="8">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>22</v>
@@ -16095,7 +16126,7 @@
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -16110,13 +16141,13 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G437" s="8">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c t="s" r="H437" s="8">
         <v>32</v>
@@ -16125,12 +16156,12 @@
         <v>39</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
       <c t="s" r="M437" s="7">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="438" ht="14.25" customHeight="1">
@@ -16145,7 +16176,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -16157,7 +16188,7 @@
         <v>53</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c t="s" r="J438" s="7">
         <v>147</v>
@@ -16193,7 +16224,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -16205,15 +16236,15 @@
         <v>87</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -16228,7 +16259,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -16248,7 +16279,7 @@
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c t="s" r="M441" s="7">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
@@ -16278,7 +16309,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="F443" s="7">
         <v>320</v>
@@ -16287,18 +16318,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>598</v>
+        <v>603</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -16313,19 +16344,19 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="F444" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c t="s" r="J444" s="7">
         <v>158</v>
@@ -16333,7 +16364,7 @@
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>600</v>
+        <v>605</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -16348,27 +16379,27 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="F445" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="H445" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="I445" s="7">
         <v>60</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
       <c t="s" r="M445" s="7">
-        <v>601</v>
+        <v>606</v>
       </c>
     </row>
     <row r="446" ht="14.25" customHeight="1">
@@ -16383,13 +16414,13 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="F446" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G446" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="H446" s="8">
         <v>16</v>
@@ -16403,7 +16434,7 @@
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>602</v>
+        <v>607</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -16418,7 +16449,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="F447" s="7">
         <v>320</v>
@@ -16453,7 +16484,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
@@ -16465,15 +16496,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>603</v>
+        <v>608</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -16488,7 +16519,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
@@ -16497,7 +16528,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c t="s" r="I449" s="7">
         <v>117</v>
@@ -16508,7 +16539,7 @@
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>604</v>
+        <v>609</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -16523,22 +16554,22 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c t="s" r="H450" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -16567,11 +16598,11 @@
         <v>34</v>
       </c>
       <c t="s" r="C452" s="7">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="F452" s="7">
         <v>330</v>
@@ -16580,7 +16611,7 @@
         <v>107</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c t="s" r="I452" s="7">
         <v>33</v>
@@ -16591,7 +16622,7 @@
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
       <c t="s" r="M452" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="453" ht="14.25" customHeight="1">
@@ -16621,19 +16652,19 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="F454" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c t="s" r="H454" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>113</v>
@@ -16641,7 +16672,7 @@
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
       <c t="s" r="M454" s="7">
-        <v>603</v>
+        <v>608</v>
       </c>
     </row>
     <row r="455" ht="15" customHeight="1">
@@ -16656,7 +16687,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="F455" s="7">
         <v>330</v>
@@ -16665,13 +16696,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H455" s="8">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -16706,7 +16737,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F457" s="7">
         <v>330</v>
@@ -16726,7 +16757,7 @@
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
       <c t="s" r="M457" s="7">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
     <row r="458" ht="14.25" customHeight="1">
@@ -16741,7 +16772,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F458" s="7">
         <v>330</v>
@@ -16750,13 +16781,13 @@
         <v>107</v>
       </c>
       <c t="s" r="H458" s="8">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c t="s" r="I458" s="7">
         <v>196</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -16776,29 +16807,29 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="F459" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G459" s="8">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c t="s" r="H459" s="8">
         <v>107</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J459" s="7">
         <v>175</v>
       </c>
       <c t="s" r="K459" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L459" s="7"/>
       <c t="s" r="M459" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="460" ht="15" customHeight="1">
@@ -16828,22 +16859,22 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>614</v>
+        <v>619</v>
       </c>
       <c r="F461" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>615</v>
+        <v>620</v>
       </c>
       <c t="s" r="H461" s="8">
         <v>181</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -16878,7 +16909,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="F463" s="7">
         <v>330</v>
@@ -16898,7 +16929,7 @@
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
@@ -16913,7 +16944,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="F464" s="7">
         <v>330</v>
@@ -16922,18 +16953,18 @@
         <v>107</v>
       </c>
       <c t="s" r="H464" s="8">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>613</v>
+        <v>618</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
       <c t="s" r="M464" s="7">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="465" ht="15" customHeight="1">
@@ -16948,19 +16979,19 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="F465" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G465" s="8">
-        <v>617</v>
+        <v>622</v>
       </c>
       <c t="s" r="H465" s="8">
         <v>107</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J465" s="7">
         <v>44</v>
@@ -16992,11 +17023,11 @@
         <v>2831</v>
       </c>
       <c t="s" r="C467" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="F467" s="7">
         <v>330</v>
@@ -17005,18 +17036,18 @@
         <v>107</v>
       </c>
       <c t="s" r="H467" s="8">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c t="s" r="I467" s="7">
         <v>104</v>
       </c>
       <c t="s" r="J467" s="7">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K467" s="7"/>
       <c r="L467" s="7"/>
       <c t="s" r="M467" s="7">
-        <v>620</v>
+        <v>625</v>
       </c>
     </row>
     <row r="468" ht="14.25" customHeight="1">
@@ -17027,31 +17058,31 @@
         <v>2832</v>
       </c>
       <c t="s" r="C468" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>618</v>
+        <v>623</v>
       </c>
       <c r="F468" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G468" s="8">
-        <v>619</v>
+        <v>624</v>
       </c>
       <c t="s" r="H468" s="8">
         <v>107</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
       <c t="s" r="M468" s="7">
-        <v>621</v>
+        <v>626</v>
       </c>
     </row>
     <row r="469" ht="14.25" customHeight="1">
@@ -17081,7 +17112,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="F470" s="7">
         <v>330</v>
@@ -17090,10 +17121,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c t="s" r="J470" s="7">
         <v>170</v>
@@ -17101,7 +17132,7 @@
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -17116,32 +17147,32 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="F471" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G471" s="8">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c t="s" r="H471" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c t="s" r="J471" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
       <c t="s" r="M471" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c t="s" r="A472" s="9">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="B472" s="9"/>
       <c r="C472" s="9"/>
@@ -17161,7 +17192,7 @@
     <row r="473" ht="65.25" customHeight="1"/>
     <row r="474" ht="16.5" customHeight="1">
       <c t="s" r="A474" s="10">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="B474" s="10"/>
       <c r="C474" s="10"/>
@@ -17174,7 +17205,7 @@
       <c r="J474" s="10"/>
       <c r="K474" s="10"/>
       <c t="s" r="L474" s="11">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="M474" s="11"/>
       <c r="N474" s="11"/>
